--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -42,6 +42,123 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00710848</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMFI PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPPAS, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEVENS, HALEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRAIG, ANGIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COOPER, ROY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00799031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, KINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOWMAN, JAMAAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MASSIE, THOMAS H.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOSTETTLER, JOHN N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERRERA, BRANDON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALINOWSKI, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOMEZ, JIMMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUSH, CORI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MO</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00935809</x:t>
   </x:si>
   <x:si>
@@ -51,15 +168,6 @@
     <x:t>AHMED, JUNAID</x:t>
   </x:si>
   <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00931774</x:t>
   </x:si>
   <x:si>
@@ -69,27 +177,9 @@
     <x:t>FOUSHEE, VALERIE</x:t>
   </x:si>
   <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00799031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
-  </x:si>
-  <x:si>
     <x:t>CONYEARS-ERVIN, MELISSA</x:t>
   </x:si>
   <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00935049</x:t>
   </x:si>
   <x:si>
@@ -141,97 +231,7 @@
     <x:t>AMIWALA, BUSHRA</x:t>
   </x:si>
   <x:si>
-    <x:t>C00710848</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMFI PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>WAY, TAHESHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MALINOWSKI, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPPAS, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEVENS, HALEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRAIG, ANGIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COOPER, ROY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, KINA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOWMAN, JAMAAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MASSIE, THOMAS H.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOSTETTLER, JOHN N</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERRERA, BRANDON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOMEZ, JIMMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUSH, CORI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -720,7 +720,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>663879</x:v>
+        <x:v>1724</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -728,229 +728,229 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="D3" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
+      <x:c r="E3" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F3" s="1">
-        <x:v>600000</x:v>
+        <x:v>1351</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>4968502</x:v>
+        <x:v>1462</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>4379246</x:v>
+        <x:v>1464</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>59748</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B7" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C7" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F7" s="1">
-        <x:v>3985700</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F8" s="1">
-        <x:v>1183678</x:v>
+        <x:v>-1861</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B9" s="1" t="s">
+      <x:c r="E9" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F9" s="1">
-        <x:v>500346</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>4383749</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>149773</x:v>
+        <x:v>2283424</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>1426379</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>12</x:v>
@@ -958,91 +958,91 @@
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>104555</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>38952</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>350000</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>2326917</x:v>
+        <x:v>4968502</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>12</x:v>
@@ -1050,114 +1050,114 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>1724</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>1351</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>1462</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>1464</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>-9678</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>12</x:v>
@@ -1165,22 +1165,22 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>-31053</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>12</x:v>
@@ -1188,22 +1188,22 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>-1861</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>12</x:v>
@@ -1211,45 +1211,45 @@
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>-6917</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>-46</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>12</x:v>
@@ -1257,22 +1257,22 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>2283424</x:v>
+        <x:v>38952</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>12</x:v>
@@ -1280,48 +1280,48 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>-28160</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1370,427 +1370,427 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>-28160</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>4379246</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>-9678</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>59748</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>4968502</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>663879</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>3985700</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>1183678</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>1426379</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>104555</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>149773</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>4884095</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>-1861</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>1351</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>1462</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>-22643</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>1464</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>1724</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>2283424</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>388952</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1835,296 +1835,296 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>-28160</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>4379246</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>50070</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>4968502</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>663879</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>3985700</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>2610057</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>5138423</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>-1861</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>1351</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>1462</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>-22643</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>1464</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1724</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>2283424</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>388952</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2165,156 +2165,156 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>-28160</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>3324006</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>18471871</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>-1861</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>1351</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>1462</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>-22643</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>601464</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>1724</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>4610341</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>388952</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2351,7 +2351,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>-28160</x:v>
@@ -2359,7 +2359,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>21795877</x:v>
@@ -2367,7 +2367,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>-6917</x:v>
@@ -2375,7 +2375,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>-1861</x:v>
@@ -2383,7 +2383,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>1351</x:v>
@@ -2391,7 +2391,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>1462</x:v>
@@ -2399,7 +2399,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>-22643</x:v>
@@ -2407,7 +2407,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>601464</x:v>
@@ -2415,7 +2415,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>1724</x:v>
@@ -2423,7 +2423,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>4999293</x:v>
@@ -2431,7 +2431,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>-31053</x:v>
@@ -2439,7 +2439,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>-46</x:v>
@@ -2483,10 +2483,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>-28160</x:v>
@@ -2494,10 +2494,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>4379246</x:v>
@@ -2505,10 +2505,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>1952112</x:v>
@@ -2516,10 +2516,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>500346</x:v>
@@ -2527,10 +2527,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>9795828</x:v>
@@ -2538,10 +2538,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>149773</x:v>
@@ -2549,10 +2549,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>5018572</x:v>
@@ -2560,10 +2560,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>-6917</x:v>
@@ -2571,10 +2571,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>-1861</x:v>
@@ -2582,10 +2582,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>1351</x:v>
@@ -2593,10 +2593,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>1462</x:v>
@@ -2604,10 +2604,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>-22643</x:v>
@@ -2615,10 +2615,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>600000</x:v>
@@ -2626,10 +2626,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>1464</x:v>
@@ -2637,10 +2637,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>1724</x:v>
@@ -2648,10 +2648,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>350000</x:v>
@@ -2659,10 +2659,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>38952</x:v>
@@ -2670,10 +2670,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>4610341</x:v>
@@ -2681,10 +2681,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>-31053</x:v>
@@ -2692,10 +2692,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>-46</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -159,6 +159,57 @@
     <x:t>MO</x:t>
   </x:si>
   <x:si>
+    <x:t>WAY, TAHESHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIEDMAN, JASON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FOUSHEE, VALERIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLER, DONNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00935809</x:t>
   </x:si>
   <x:si>
@@ -168,31 +219,10 @@
     <x:t>AHMED, JUNAID</x:t>
   </x:si>
   <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FOUSHEE, VALERIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIEDMAN, JASON</x:t>
+    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMIWALA, BUSHRA</x:t>
   </x:si>
   <x:si>
     <x:t>C00936724</x:t>
@@ -202,36 +232,6 @@
   </x:si>
   <x:si>
     <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BISS, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMIWALA, BUSHRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAY, TAHESHA</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -981,45 +981,45 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>663879</x:v>
+        <x:v>38952</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>600000</x:v>
+        <x:v>4968502</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>12</x:v>
@@ -1033,7 +1033,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>23</x:v>
@@ -1042,76 +1042,76 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>4968502</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>4379246</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>59748</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>3985700</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>12</x:v>
@@ -1119,45 +1119,45 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>1183678</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>500346</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>12</x:v>
@@ -1165,13 +1165,13 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>62</x:v>
@@ -1180,7 +1180,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>4383749</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>12</x:v>
@@ -1188,45 +1188,45 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>149773</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>1426379</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>25</x:v>
@@ -1234,16 +1234,16 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>24</x:v>
@@ -1257,22 +1257,22 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>38952</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>12</x:v>
@@ -1280,22 +1280,22 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>350000</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>12</x:v>
@@ -1303,22 +1303,22 @@
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>2326917</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>25</x:v>
@@ -1387,10 +1387,10 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>24</x:v>
@@ -1421,7 +1421,7 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>23</x:v>
@@ -1438,7 +1438,7 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>23</x:v>
@@ -1455,7 +1455,7 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>33</x:v>
@@ -1472,7 +1472,7 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>33</x:v>
@@ -1489,10 +1489,10 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>24</x:v>
@@ -1506,10 +1506,10 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>24</x:v>
@@ -1523,10 +1523,10 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>24</x:v>
@@ -1540,10 +1540,10 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>24</x:v>
@@ -1557,10 +1557,10 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>24</x:v>
@@ -1676,7 +1676,7 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>30</x:v>
@@ -1744,7 +1744,7 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>39</x:v>
@@ -1849,7 +1849,7 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>24</x:v>
@@ -1919,7 +1919,7 @@
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>24</x:v>
@@ -1933,7 +1933,7 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>24</x:v>
@@ -2494,7 +2494,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>24</x:v>
@@ -2505,7 +2505,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>24</x:v>
@@ -2516,7 +2516,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>24</x:v>
@@ -2527,7 +2527,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>24</x:v>
@@ -2538,7 +2538,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>24</x:v>
@@ -2615,7 +2615,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>19</x:v>
@@ -2648,7 +2648,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>40</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -48,6 +48,18 @@
     <x:t>DMFI PAC</x:t>
   </x:si>
   <x:si>
+    <x:t>WAY, TAHESHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
     <x:t>PAPPAS, CHRIS</x:t>
   </x:si>
   <x:si>
@@ -57,9 +69,6 @@
     <x:t>NH</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
     <x:t>STEVENS, HALEY</x:t>
   </x:si>
   <x:si>
@@ -138,12 +147,6 @@
     <x:t>MALINOWSKI, TOM</x:t>
   </x:si>
   <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
     <x:t>GOMEZ, JIMMY</x:t>
   </x:si>
   <x:si>
@@ -159,15 +162,66 @@
     <x:t>MO</x:t>
   </x:si>
   <x:si>
-    <x:t>WAY, TAHESHA</x:t>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHMED, JUNAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FOUSHEE, VALERIE</x:t>
   </x:si>
   <x:si>
     <x:t>CONYEARS-ERVIN, MELISSA</x:t>
   </x:si>
   <x:si>
+    <x:t>C00935049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLER, DONNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
     <x:t>FRIEDMAN, JASON</x:t>
   </x:si>
   <x:si>
+    <x:t>C00936724</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00815753</x:t>
   </x:si>
   <x:si>
@@ -177,61 +231,7 @@
     <x:t>BISS, DANIEL</x:t>
   </x:si>
   <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FOUSHEE, VALERIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935809</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHMED, JUNAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
-  </x:si>
-  <x:si>
     <x:t>AMIWALA, BUSHRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00936724</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -302,8 +302,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G28" totalsRowShown="0">
-  <x:autoFilter ref="A1:G28"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G29" totalsRowShown="0">
+  <x:autoFilter ref="A1:G29"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -667,7 +667,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G28"/>
+  <x:dimension ref="A1:G29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -720,7 +720,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>1724</x:v>
+        <x:v>21350</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -743,7 +743,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>1351</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -760,13 +760,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>1462</x:v>
+        <x:v>1601</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -780,16 +780,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>1464</x:v>
+        <x:v>1712</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>12</x:v>
@@ -797,56 +797,56 @@
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="F6" s="1">
-        <x:v>-9678</x:v>
+        <x:v>1714</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>-31053</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>29</x:v>
@@ -858,18 +858,18 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>-1861</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>32</x:v>
@@ -881,18 +881,18 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>-6917</x:v>
+        <x:v>-1861</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>35</x:v>
@@ -904,18 +904,18 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>-46</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>38</x:v>
@@ -927,99 +927,99 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>2283424</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>-28160</x:v>
+        <x:v>2283424</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="F13" s="1">
-        <x:v>-22643</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="F14" s="1">
-        <x:v>38952</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>4968502</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>12</x:v>
@@ -1027,68 +1027,68 @@
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>59748</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>2326917</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>149773</x:v>
+        <x:v>4968502</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>12</x:v>
@@ -1096,22 +1096,22 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>500346</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>12</x:v>
@@ -1119,45 +1119,45 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>600000</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>350000</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>12</x:v>
@@ -1165,91 +1165,91 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>4379246</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B23" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C23" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>663879</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>1183678</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B25" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>104555</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>12</x:v>
@@ -1257,45 +1257,45 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="C26" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>3985700</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>4383749</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>12</x:v>
@@ -1303,25 +1303,48 @@
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F28" s="1">
+        <x:v>15130</x:v>
+      </x:c>
+      <x:c r="G28" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:7">
+      <x:c r="A29" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="F28" s="1">
-        <x:v>1426379</x:v>
-      </x:c>
-      <x:c r="G28" s="1" t="s">
-        <x:v>25</x:v>
+      <x:c r="C29" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F29" s="1">
+        <x:v>2326917</x:v>
+      </x:c>
+      <x:c r="G29" s="1" t="s">
+        <x:v>28</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1370,13 +1393,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>-28160</x:v>
@@ -1387,13 +1410,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>4379246</x:v>
@@ -1404,47 +1427,47 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>-9678</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>59748</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>4968502</x:v>
@@ -1455,30 +1478,30 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>663879</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>3985700</x:v>
@@ -1489,47 +1512,47 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>1183678</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>1426379</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>104555</x:v>
@@ -1540,13 +1563,13 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>149773</x:v>
@@ -1557,13 +1580,13 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>4884095</x:v>
@@ -1574,50 +1597,50 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>-1861</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>1351</x:v>
+        <x:v>1601</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>12</x:v>
@@ -1625,16 +1648,16 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>1462</x:v>
+        <x:v>1712</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>12</x:v>
@@ -1642,33 +1665,33 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>-22643</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>1464</x:v>
+        <x:v>1714</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>12</x:v>
@@ -1676,13 +1699,13 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>600000</x:v>
@@ -1693,16 +1716,16 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>1724</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>12</x:v>
@@ -1710,50 +1733,50 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>2283424</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>388952</x:v>
+        <x:v>386480</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>12</x:v>
@@ -1761,36 +1784,36 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1835,10 +1858,10 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>-28160</x:v>
@@ -1849,10 +1872,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>4379246</x:v>
@@ -1863,24 +1886,24 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>50070</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>4968502</x:v>
@@ -1891,24 +1914,24 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>663879</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>3985700</x:v>
@@ -1919,24 +1942,24 @@
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>2610057</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>5138423</x:v>
@@ -1947,41 +1970,41 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>-1861</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>1351</x:v>
+        <x:v>1601</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
         <x:v>12</x:v>
@@ -1989,13 +2012,13 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>1462</x:v>
+        <x:v>1712</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>12</x:v>
@@ -2003,27 +2026,27 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>-22643</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>1464</x:v>
+        <x:v>1714</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>12</x:v>
@@ -2031,10 +2054,10 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>600000</x:v>
@@ -2045,13 +2068,13 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>1724</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>12</x:v>
@@ -2059,41 +2082,41 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>2283424</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>388952</x:v>
+        <x:v>386480</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>12</x:v>
@@ -2101,30 +2124,30 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2165,7 +2188,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>-28160</x:v>
@@ -2176,18 +2199,18 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>3324006</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>18471871</x:v>
@@ -2198,32 +2221,32 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>-1861</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>1351</x:v>
+        <x:v>1601</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>12</x:v>
@@ -2231,10 +2254,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>1462</x:v>
+        <x:v>1712</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>12</x:v>
@@ -2242,21 +2265,21 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>-22643</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>601464</x:v>
+        <x:v>601714</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>12</x:v>
@@ -2264,10 +2287,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>1724</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -2275,21 +2298,21 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>4610341</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>388952</x:v>
+        <x:v>386480</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>12</x:v>
@@ -2297,24 +2320,24 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2351,7 +2374,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>-28160</x:v>
@@ -2359,7 +2382,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>21795877</x:v>
@@ -2367,7 +2390,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>-6917</x:v>
@@ -2375,7 +2398,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>-1861</x:v>
@@ -2383,23 +2406,23 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>1351</x:v>
+        <x:v>1601</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>1462</x:v>
+        <x:v>1712</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>-22643</x:v>
@@ -2407,31 +2430,31 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>601464</x:v>
+        <x:v>601714</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>1724</x:v>
+        <x:v>1974</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>4999293</x:v>
+        <x:v>4996821</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>-31053</x:v>
@@ -2439,7 +2462,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>-46</x:v>
@@ -2483,10 +2506,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>-28160</x:v>
@@ -2494,10 +2517,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>4379246</x:v>
@@ -2505,10 +2528,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>1952112</x:v>
@@ -2516,10 +2539,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>500346</x:v>
@@ -2527,10 +2550,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>9795828</x:v>
@@ -2538,10 +2561,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>149773</x:v>
@@ -2549,10 +2572,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>5018572</x:v>
@@ -2560,10 +2583,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>-6917</x:v>
@@ -2571,10 +2594,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>-1861</x:v>
@@ -2585,10 +2608,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>1351</x:v>
+        <x:v>1601</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -2596,18 +2619,18 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>1462</x:v>
+        <x:v>1712</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>-22643</x:v>
@@ -2615,10 +2638,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>600000</x:v>
@@ -2629,10 +2652,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>1464</x:v>
+        <x:v>1714</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -2640,18 +2663,18 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>1724</x:v>
+        <x:v>1974</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>350000</x:v>
@@ -2662,18 +2685,18 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>38952</x:v>
+        <x:v>36480</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>4610341</x:v>
@@ -2681,10 +2704,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>-31053</x:v>
@@ -2692,10 +2715,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>-46</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -48,36 +48,108 @@
     <x:t>DMFI PAC</x:t>
   </x:si>
   <x:si>
+    <x:t>STELSON, JANELLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIRD, SHANNON KATHLEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLER, DONNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOSS, JEREMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
     <x:t>WAY, TAHESHA</x:t>
   </x:si>
   <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
     <x:t>NJ</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
+    <x:t>CONLEY, CAIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COGNETTI, PAIGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARCIA, JOHNNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LURIA, ELAINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SULLIVAN, MAURA CORBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
   </x:si>
   <x:si>
     <x:t>PAPPAS, CHRIS</x:t>
   </x:si>
   <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
     <x:t>STEVENS, HALEY</x:t>
   </x:si>
   <x:si>
     <x:t>00</x:t>
   </x:si>
   <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
     <x:t>CRAIG, ANGIE</x:t>
   </x:si>
   <x:si>
@@ -102,9 +174,6 @@
     <x:t>07</x:t>
   </x:si>
   <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
     <x:t>OPPOSE</x:t>
   </x:si>
   <x:si>
@@ -114,9 +183,6 @@
     <x:t>16</x:t>
   </x:si>
   <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
     <x:t>MASSIE, THOMAS H.</x:t>
   </x:si>
   <x:si>
@@ -126,12 +192,12 @@
     <x:t>KY</x:t>
   </x:si>
   <x:si>
+    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>HOSTETTLER, JOHN N</x:t>
   </x:si>
   <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
     <x:t>IN</x:t>
   </x:si>
   <x:si>
@@ -141,9 +207,6 @@
     <x:t>23</x:t>
   </x:si>
   <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
     <x:t>MALINOWSKI, TOM</x:t>
   </x:si>
   <x:si>
@@ -162,12 +225,54 @@
     <x:t>MO</x:t>
   </x:si>
   <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CISNEROS, JESSICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00931774</x:t>
   </x:si>
   <x:si>
     <x:t>ARTICLE ONE PAC</x:t>
   </x:si>
   <x:si>
+    <x:t>FOUSHEE, VALERIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00936724</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00935809</x:t>
   </x:si>
   <x:si>
@@ -177,58 +282,10 @@
     <x:t>AHMED, JUNAID</x:t>
   </x:si>
   <x:si>
-    <x:t>FOUSHEE, VALERIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
     <x:t>FRIEDMAN, JASON</x:t>
   </x:si>
   <x:si>
-    <x:t>C00936724</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
     <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BISS, DANIEL</x:t>
   </x:si>
   <x:si>
     <x:t>AMIWALA, BUSHRA</x:t>
@@ -302,8 +359,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G29" totalsRowShown="0">
-  <x:autoFilter ref="A1:G29"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G49" totalsRowShown="0">
+  <x:autoFilter ref="A1:G49"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -318,8 +375,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E26" totalsRowShown="0">
-  <x:autoFilter ref="A1:E26"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E37" totalsRowShown="0">
+  <x:autoFilter ref="A1:E37"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -332,8 +389,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D22" totalsRowShown="0">
-  <x:autoFilter ref="A1:D22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D32" totalsRowShown="0">
+  <x:autoFilter ref="A1:D32"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -345,8 +402,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C15" totalsRowShown="0">
-  <x:autoFilter ref="A1:C15"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C21" totalsRowShown="0">
+  <x:autoFilter ref="A1:C21"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -357,8 +414,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B13" totalsRowShown="0">
-  <x:autoFilter ref="A1:B13"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B17" totalsRowShown="0">
+  <x:autoFilter ref="A1:B17"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -368,8 +425,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C21" totalsRowShown="0">
-  <x:autoFilter ref="A1:C21"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C29" totalsRowShown="0">
+  <x:autoFilter ref="A1:C29"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -667,7 +724,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G29"/>
+  <x:dimension ref="A1:G49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -720,7 +777,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>21350</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -743,7 +800,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>1974</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -766,7 +823,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>1601</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -783,13 +840,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>1712</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>12</x:v>
@@ -803,16 +860,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>17</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>1714</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
         <x:v>12</x:v>
@@ -820,160 +877,160 @@
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B7" s="1" t="s">
+      <x:c r="D7" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C7" s="1" t="s">
+      <x:c r="E7" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="F7" s="1">
-        <x:v>-9678</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>-31053</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>-1861</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>-6917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>2283424</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>-28160</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>12</x:v>
@@ -981,45 +1038,45 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>-22643</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>350000</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>12</x:v>
@@ -1027,45 +1084,45 @@
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>663879</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1073,22 +1130,22 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>4968502</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>12</x:v>
@@ -1096,229 +1153,229 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>4379246</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>59748</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>3985700</x:v>
+        <x:v>-1861</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C22" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>1183678</x:v>
+        <x:v>2322515</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>500346</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C24" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>4383749</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>149773</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>1426379</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>104555</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>15130</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>12</x:v>
@@ -1326,25 +1383,485 @@
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F29" s="1">
+        <x:v>500346</x:v>
+      </x:c>
+      <x:c r="G29" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:7">
+      <x:c r="A30" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F30" s="1">
+        <x:v>600000</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:7">
+      <x:c r="A31" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D29" s="1" t="s">
+      <x:c r="E31" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F31" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G31" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:7">
+      <x:c r="A32" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F32" s="1">
+        <x:v>2359443</x:v>
+      </x:c>
+      <x:c r="G32" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:7">
+      <x:c r="A33" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F33" s="1">
+        <x:v>2893782</x:v>
+      </x:c>
+      <x:c r="G33" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:7">
+      <x:c r="A34" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E34" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F34" s="1">
+        <x:v>2845686</x:v>
+      </x:c>
+      <x:c r="G34" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:7">
+      <x:c r="A35" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E35" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F35" s="1">
+        <x:v>1314739</x:v>
+      </x:c>
+      <x:c r="G35" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:7">
+      <x:c r="A36" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F36" s="1">
+        <x:v>663879</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:7">
+      <x:c r="A37" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F37" s="1">
+        <x:v>600000</x:v>
+      </x:c>
+      <x:c r="G37" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:7">
+      <x:c r="A38" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F38" s="1">
+        <x:v>4968502</x:v>
+      </x:c>
+      <x:c r="G38" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:7">
+      <x:c r="A39" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E39" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F39" s="1">
+        <x:v>4379246</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:7">
+      <x:c r="A40" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F40" s="1">
+        <x:v>59748</x:v>
+      </x:c>
+      <x:c r="G40" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:7">
+      <x:c r="A41" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F41" s="1">
+        <x:v>3985700</x:v>
+      </x:c>
+      <x:c r="G41" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:7">
+      <x:c r="A42" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B42" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E42" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F42" s="1">
+        <x:v>1183678</x:v>
+      </x:c>
+      <x:c r="G42" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:7">
+      <x:c r="A43" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F43" s="1">
+        <x:v>500346</x:v>
+      </x:c>
+      <x:c r="G43" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:7">
+      <x:c r="A44" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E44" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F44" s="1">
+        <x:v>4383749</x:v>
+      </x:c>
+      <x:c r="G44" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:7">
+      <x:c r="A45" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E45" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F45" s="1">
+        <x:v>149773</x:v>
+      </x:c>
+      <x:c r="G45" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:7">
+      <x:c r="A46" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F46" s="1">
+        <x:v>1426379</x:v>
+      </x:c>
+      <x:c r="G46" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:7">
+      <x:c r="A47" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B47" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C47" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E47" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F47" s="1">
+        <x:v>104555</x:v>
+      </x:c>
+      <x:c r="G47" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:7">
+      <x:c r="A48" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F29" s="1">
+      <x:c r="D48" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F48" s="1">
+        <x:v>15130</x:v>
+      </x:c>
+      <x:c r="G48" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:7">
+      <x:c r="A49" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E49" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F49" s="1">
         <x:v>2326917</x:v>
       </x:c>
-      <x:c r="G29" s="1" t="s">
-        <x:v>28</x:v>
+      <x:c r="G49" s="1" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1363,7 +1880,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E26"/>
+  <x:dimension ref="A1:E37"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1393,13 +1910,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>-28160</x:v>
@@ -1410,16 +1927,16 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D3" s="1">
-        <x:v>4379246</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
         <x:v>12</x:v>
@@ -1427,152 +1944,152 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D4" s="1">
-        <x:v>-9678</x:v>
+        <x:v>6739071</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D5" s="1">
-        <x:v>59748</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>4968502</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>663879</x:v>
+        <x:v>7291017</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>3985700</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>1183678</x:v>
+        <x:v>6879864</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>1426379</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>104555</x:v>
+        <x:v>2741118</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>149773</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>12</x:v>
@@ -1580,16 +2097,16 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>4884095</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>12</x:v>
@@ -1597,67 +2114,67 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>-6917</x:v>
+        <x:v>8230127</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>-1861</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>1601</x:v>
+        <x:v>-1861</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>1712</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>12</x:v>
@@ -1665,33 +2182,33 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>1714</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>12</x:v>
@@ -1699,16 +2216,16 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>600000</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>12</x:v>
@@ -1716,67 +2233,67 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>1974</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>2326917</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>2283424</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>386480</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>12</x:v>
@@ -1784,36 +2301,223 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>-31053</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B26" s="1" t="s">
+      <x:c r="C26" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C26" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="D26" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:5">
+      <x:c r="A27" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D27" s="1">
+        <x:v>2326917</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:5">
+      <x:c r="A28" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D28" s="1">
+        <x:v>2326917</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:5">
+      <x:c r="A29" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D29" s="1">
+        <x:v>423571</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:5">
+      <x:c r="A30" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D30" s="1">
+        <x:v>-31053</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:5">
+      <x:c r="A31" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D31" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:5">
+      <x:c r="A32" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D32" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:5">
+      <x:c r="A33" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D33" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:5">
+      <x:c r="A34" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D34" s="1">
         <x:v>-46</x:v>
       </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>28</x:v>
+      <x:c r="E34" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:5">
+      <x:c r="A35" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D35" s="1">
+        <x:v>39386</x:v>
+      </x:c>
+      <x:c r="E35" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:5">
+      <x:c r="A36" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D36" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:5">
+      <x:c r="A37" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D37" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1832,7 +2536,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D22"/>
+  <x:dimension ref="A1:D32"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1858,10 +2562,10 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>-28160</x:v>
@@ -1872,13 +2576,13 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>4379246</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
         <x:v>12</x:v>
@@ -1886,139 +2590,139 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>50070</x:v>
+        <x:v>6739071</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>4968502</x:v>
+        <x:v>50070</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>663879</x:v>
+        <x:v>7291017</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>3985700</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>2610057</x:v>
+        <x:v>6879864</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>5138423</x:v>
+        <x:v>3924796</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>-6917</x:v>
+        <x:v>8484455</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>-1861</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>1601</x:v>
+        <x:v>-1861</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>1712</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>12</x:v>
@@ -2026,27 +2730,27 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>1714</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>12</x:v>
@@ -2054,13 +2758,13 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>600000</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>12</x:v>
@@ -2068,55 +2772,55 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>1974</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>2326917</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>2283424</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>386480</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>12</x:v>
@@ -2124,30 +2828,170 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>-31053</x:v>
+        <x:v>2356</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C22" s="1">
+        <x:v>2326917</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:4">
+      <x:c r="A23" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C23" s="1">
+        <x:v>2326917</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:4">
+      <x:c r="A24" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C24" s="1">
+        <x:v>423571</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:4">
+      <x:c r="A25" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C25" s="1">
+        <x:v>-31053</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:4">
+      <x:c r="A26" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C26" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:4">
+      <x:c r="A27" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C27" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:4">
+      <x:c r="A28" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C28" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:4">
+      <x:c r="A29" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C29" s="1">
         <x:v>-46</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>28</x:v>
+      <x:c r="D29" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:4">
+      <x:c r="A30" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C30" s="1">
+        <x:v>39386</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:4">
+      <x:c r="A31" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C31" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:4">
+      <x:c r="A32" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C32" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2166,7 +3010,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C15"/>
+  <x:dimension ref="A1:C21"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2188,7 +3032,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>-28160</x:v>
@@ -2199,65 +3043,65 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>3324006</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>18471871</x:v>
+        <x:v>4638745</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>-6917</x:v>
+        <x:v>29394407</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>-1861</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>1601</x:v>
+        <x:v>-1861</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>1712</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>12</x:v>
@@ -2265,21 +3109,21 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2920</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>601714</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>12</x:v>
@@ -2287,32 +3131,32 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>1974</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>4610341</x:v>
+        <x:v>1202651</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>386480</x:v>
+        <x:v>3294</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>12</x:v>
@@ -2320,24 +3164,90 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>-31053</x:v>
+        <x:v>4653834</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B15" s="1">
+        <x:v>423571</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:3">
+      <x:c r="A16" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B16" s="1">
+        <x:v>-31053</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:3">
+      <x:c r="A17" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B17" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:3">
+      <x:c r="A18" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B18" s="1">
+        <x:v>764</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:3">
+      <x:c r="A19" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B19" s="1">
         <x:v>-46</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>28</x:v>
+      <x:c r="C19" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:3">
+      <x:c r="A20" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B20" s="1">
+        <x:v>39768</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B21" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2356,7 +3266,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B13"/>
+  <x:dimension ref="A1:B17"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2374,7 +3284,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>-28160</x:v>
@@ -2382,90 +3292,122 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>21795877</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>-6917</x:v>
+        <x:v>34033152</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>-1861</x:v>
+        <x:v>-6917</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>1601</x:v>
+        <x:v>-1861</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>1712</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2920</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>601714</x:v>
+        <x:v>2649</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>1974</x:v>
+        <x:v>-22643</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>4996821</x:v>
+        <x:v>1202651</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>-31053</x:v>
+        <x:v>3294</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>-46</x:v>
+        <x:v>5077405</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:2">
+      <x:c r="A14" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B14" s="1">
+        <x:v>-30671</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:2">
+      <x:c r="A15" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B15" s="1">
+        <x:v>764</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:2">
+      <x:c r="A16" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B16" s="1">
+        <x:v>39722</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:2">
+      <x:c r="A17" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B17" s="1">
+        <x:v>382</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2484,7 +3426,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C21"/>
+  <x:dimension ref="A1:C29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2506,10 +3448,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>-28160</x:v>
@@ -2517,134 +3459,134 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>4379246</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>1952112</x:v>
+        <x:v>6738689</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>500346</x:v>
+        <x:v>1952112</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>9795828</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>149773</x:v>
+        <x:v>1000692</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>5018572</x:v>
+        <x:v>16850035</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>-6917</x:v>
+        <x:v>149773</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>-1861</x:v>
+        <x:v>7341087</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>1601</x:v>
+        <x:v>-6917</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>1712</x:v>
+        <x:v>-1861</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>-22643</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>600000</x:v>
+        <x:v>2920</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -2652,32 +3594,32 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>1714</x:v>
+        <x:v>2649</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>1974</x:v>
+        <x:v>-22643</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>350000</x:v>
+        <x:v>1200000</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -2685,43 +3627,131 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>36480</x:v>
+        <x:v>2651</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>4610341</x:v>
+        <x:v>3294</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>-31053</x:v>
+        <x:v>350000</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C21" s="1">
+        <x:v>73571</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C22" s="1">
+        <x:v>4653834</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C23" s="1">
+        <x:v>382</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C24" s="1">
+        <x:v>-31053</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C25" s="1">
+        <x:v>764</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C26" s="1">
+        <x:v>382</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C27" s="1">
+        <x:v>39386</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C28" s="1">
         <x:v>-46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C29" s="1">
+        <x:v>382</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -359,8 +359,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G49" totalsRowShown="0">
-  <x:autoFilter ref="A1:G49"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G46" totalsRowShown="0">
+  <x:autoFilter ref="A1:G46"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -724,7 +724,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G49"/>
+  <x:dimension ref="A1:G46"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1567,22 +1567,22 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>600000</x:v>
+        <x:v>2645986</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>12</x:v>
@@ -1590,22 +1590,22 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>4968502</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>12</x:v>
@@ -1613,82 +1613,82 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>4379246</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>59748</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>3985700</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
         <x:v>75</x:v>
@@ -1697,21 +1697,21 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>1183678</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
         <x:v>75</x:v>
@@ -1720,7 +1720,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>500346</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1734,7 +1734,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
         <x:v>75</x:v>
@@ -1743,21 +1743,21 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>4383749</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
         <x:v>75</x:v>
@@ -1766,7 +1766,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>149773</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>12</x:v>
@@ -1774,93 +1774,24 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>1426379</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:7">
-      <x:c r="A47" s="1" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="B47" s="1" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C47" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D47" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E47" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F47" s="1">
-        <x:v>104555</x:v>
-      </x:c>
-      <x:c r="G47" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:7">
-      <x:c r="A48" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B48" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C48" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D48" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E48" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F48" s="1">
-        <x:v>15130</x:v>
-      </x:c>
-      <x:c r="G48" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:7">
-      <x:c r="A49" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B49" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C49" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D49" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E49" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F49" s="1">
-        <x:v>2326917</x:v>
-      </x:c>
-      <x:c r="G49" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
@@ -2004,7 +1935,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>7291017</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>12</x:v>
@@ -2123,7 +2054,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>8230127</x:v>
+        <x:v>7729781</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>12</x:v>
@@ -2276,7 +2207,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>1200000</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>12</x:v>
@@ -2378,7 +2309,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>423571</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>12</x:v>
@@ -2624,7 +2555,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>7291017</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>12</x:v>
@@ -2680,7 +2611,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>8484455</x:v>
+        <x:v>7984109</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
         <x:v>12</x:v>
@@ -2806,7 +2737,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>1200000</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
         <x:v>12</x:v>
@@ -2876,7 +2807,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>423571</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>12</x:v>
@@ -3068,7 +2999,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>29394407</x:v>
+        <x:v>26571545</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>12</x:v>
@@ -3145,7 +3076,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>1202651</x:v>
+        <x:v>602651</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>12</x:v>
@@ -3178,7 +3109,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>423571</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>12</x:v>
@@ -3303,7 +3234,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>34033152</x:v>
+        <x:v>31210290</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
@@ -3359,7 +3290,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>1202651</x:v>
+        <x:v>602651</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
@@ -3375,7 +3306,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>5077405</x:v>
+        <x:v>5062275</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -3509,7 +3440,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>1000692</x:v>
+        <x:v>500346</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -3542,7 +3473,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>7341087</x:v>
+        <x:v>5018571</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -3619,7 +3550,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>1200000</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -3663,7 +3594,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>73571</x:v>
+        <x:v>58441</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -289,6 +289,12 @@
   </x:si>
   <x:si>
     <x:t>AMIWALA, BUSHRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -359,8 +365,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G46" totalsRowShown="0">
-  <x:autoFilter ref="A1:G46"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G47" totalsRowShown="0">
+  <x:autoFilter ref="A1:G47"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -375,8 +381,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E37" totalsRowShown="0">
-  <x:autoFilter ref="A1:E37"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E38" totalsRowShown="0">
+  <x:autoFilter ref="A1:E38"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -389,8 +395,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D32" totalsRowShown="0">
-  <x:autoFilter ref="A1:D32"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D33" totalsRowShown="0">
+  <x:autoFilter ref="A1:D33"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -402,8 +408,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C21" totalsRowShown="0">
-  <x:autoFilter ref="A1:C21"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C22" totalsRowShown="0">
+  <x:autoFilter ref="A1:C22"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -425,8 +431,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C29" totalsRowShown="0">
-  <x:autoFilter ref="A1:C29"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C30" totalsRowShown="0">
+  <x:autoFilter ref="A1:C30"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -724,7 +730,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G46"/>
+  <x:dimension ref="A1:G47"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1774,24 +1780,47 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F46" s="1">
+        <x:v>750000</x:v>
+      </x:c>
+      <x:c r="G46" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:7">
+      <x:c r="A47" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B46" s="1" t="s">
+      <x:c r="B47" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C46" s="1" t="s">
+      <x:c r="C47" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D46" s="1" t="s">
+      <x:c r="D47" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E46" s="1" t="s">
+      <x:c r="E47" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F46" s="1">
+      <x:c r="F47" s="1">
         <x:v>2326917</x:v>
       </x:c>
-      <x:c r="G46" s="1" t="s">
+      <x:c r="G47" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
@@ -1811,7 +1840,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E37"/>
+  <x:dimension ref="A1:E38"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1858,33 +1887,33 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D3" s="1">
-        <x:v>382</x:v>
+        <x:v>750000</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D4" s="1">
-        <x:v>6739071</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
         <x:v>12</x:v>
@@ -1892,24 +1921,24 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D5" s="1">
-        <x:v>-9678</x:v>
+        <x:v>6739071</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>50</x:v>
@@ -1918,7 +1947,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>59748</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>51</x:v>
@@ -1926,7 +1955,7 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>50</x:v>
@@ -1935,32 +1964,32 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>4968501</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>663879</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>14</x:v>
@@ -1969,32 +1998,32 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>6879864</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>1183678</x:v>
+        <x:v>6879864</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>75</x:v>
@@ -2003,7 +2032,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>2741118</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>51</x:v>
@@ -2011,7 +2040,7 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>75</x:v>
@@ -2020,15 +2049,15 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>104555</x:v>
+        <x:v>2741118</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>75</x:v>
@@ -2037,7 +2066,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>149773</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>12</x:v>
@@ -2045,7 +2074,7 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>75</x:v>
@@ -2054,7 +2083,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>7729781</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>12</x:v>
@@ -2062,33 +2091,33 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>-6917</x:v>
+        <x:v>7729781</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>-1861</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>51</x:v>
@@ -2096,33 +2125,33 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>382</x:v>
+        <x:v>-1861</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>2538</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>12</x:v>
@@ -2130,16 +2159,16 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>382</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>12</x:v>
@@ -2147,16 +2176,16 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>12</x:v>
@@ -2164,50 +2193,50 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>2651</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>12</x:v>
@@ -2215,16 +2244,16 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>938</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>12</x:v>
@@ -2235,13 +2264,13 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>1974</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>12</x:v>
@@ -2249,7 +2278,7 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
         <x:v>38</x:v>
@@ -2258,7 +2287,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>382</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -2266,19 +2295,19 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
@@ -2286,7 +2315,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>27</x:v>
@@ -2300,7 +2329,7 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>24</x:v>
@@ -2309,55 +2338,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>382</x:v>
@@ -2368,10 +2397,10 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>11</x:v>
@@ -2385,50 +2414,50 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>382</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>12</x:v>
@@ -2436,18 +2465,35 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D37" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:5">
+      <x:c r="A38" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B37" s="1" t="s">
+      <x:c r="B38" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C37" s="1" t="s">
+      <x:c r="C38" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D37" s="1">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="E37" s="1" t="s">
+      <x:c r="D38" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -2467,7 +2513,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D32"/>
+  <x:dimension ref="A1:D33"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2507,27 +2553,27 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>382</x:v>
+        <x:v>750000</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>6739071</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
         <x:v>12</x:v>
@@ -2535,16 +2581,16 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>50070</x:v>
+        <x:v>6739071</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
@@ -2555,24 +2601,24 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>4968501</x:v>
+        <x:v>50070</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>663879</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
@@ -2583,24 +2629,24 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>6879864</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>3924796</x:v>
+        <x:v>6879864</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
@@ -2611,35 +2657,35 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>7984109</x:v>
+        <x:v>3924796</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>-6917</x:v>
+        <x:v>7984109</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>-1861</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
         <x:v>51</x:v>
@@ -2647,27 +2693,27 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>382</x:v>
+        <x:v>-1861</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>2538</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>12</x:v>
@@ -2675,13 +2721,13 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>382</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>12</x:v>
@@ -2689,13 +2735,13 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>12</x:v>
@@ -2703,41 +2749,41 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>2651</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
         <x:v>12</x:v>
@@ -2745,13 +2791,13 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>938</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>12</x:v>
@@ -2759,13 +2805,13 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>2356</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>12</x:v>
@@ -2773,21 +2819,21 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>2326917</x:v>
+        <x:v>2356</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>27</x:v>
@@ -2807,46 +2853,46 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>382</x:v>
@@ -2857,7 +2903,7 @@
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>11</x:v>
@@ -2871,41 +2917,41 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>382</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>12</x:v>
@@ -2913,15 +2959,29 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C32" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:4">
+      <x:c r="A33" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B32" s="1" t="s">
+      <x:c r="B33" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C32" s="1">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="D32" s="1" t="s">
+      <x:c r="C33" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -2941,7 +3001,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C21"/>
+  <x:dimension ref="A1:C22"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2966,18 +3026,18 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>-28160</x:v>
+        <x:v>750000</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>382</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>12</x:v>
@@ -2985,13 +3045,13 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>4638745</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
@@ -2999,29 +3059,29 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>26571545</x:v>
+        <x:v>4638745</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>-6917</x:v>
+        <x:v>26571545</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>-1861</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>51</x:v>
@@ -3029,21 +3089,21 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>382</x:v>
+        <x:v>-1861</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>2920</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>12</x:v>
@@ -3051,10 +3111,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>2649</x:v>
+        <x:v>2920</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>12</x:v>
@@ -3062,32 +3122,32 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>602651</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>3294</x:v>
+        <x:v>602651</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>12</x:v>
@@ -3095,13 +3155,13 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>4653834</x:v>
+        <x:v>3294</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -3109,21 +3169,21 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>408441</x:v>
+        <x:v>4653834</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -3131,18 +3191,18 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>764</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>12</x:v>
@@ -3150,13 +3210,13 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>-46</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -3164,20 +3224,31 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>39768</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B21" s="1">
+        <x:v>39768</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B21" s="1">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="C21" s="1" t="s">
+      <x:c r="B22" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -3218,7 +3289,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>-28160</x:v>
+        <x:v>721840</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -3357,7 +3428,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C29"/>
+  <x:dimension ref="A1:C30"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3379,101 +3450,101 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>-28160</x:v>
+        <x:v>750000</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>382</x:v>
+        <x:v>-28160</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>6738689</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>1952112</x:v>
+        <x:v>6738689</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>764</x:v>
+        <x:v>1952112</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>500346</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>16850035</x:v>
+        <x:v>500346</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>149773</x:v>
+        <x:v>16850035</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>5018571</x:v>
+        <x:v>149773</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -3481,10 +3552,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>-6917</x:v>
+        <x:v>5018571</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -3492,21 +3563,21 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>-1861</x:v>
+        <x:v>-6917</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>382</x:v>
+        <x:v>-1861</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -3514,10 +3585,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>2920</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -3525,43 +3596,43 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>2649</x:v>
+        <x:v>2920</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>600000</x:v>
+        <x:v>-22643</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>2651</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -3569,76 +3640,76 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>3294</x:v>
+        <x:v>2651</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>350000</x:v>
+        <x:v>3294</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>58441</x:v>
+        <x:v>350000</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>4653834</x:v>
+        <x:v>58441</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>382</x:v>
+        <x:v>4653834</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>-31053</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>764</x:v>
+        <x:v>-31053</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -3646,42 +3717,53 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>382</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>39386</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>-46</x:v>
+        <x:v>39386</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C29" s="1">
+        <x:v>-46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:3">
+      <x:c r="A30" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B29" s="1" t="s">
+      <x:c r="B30" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C29" s="1">
+      <x:c r="C30" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -273,6 +273,15 @@
     <x:t>BISS, DANIEL</x:t>
   </x:si>
   <x:si>
+    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIEDMAN, JASON</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00935809</x:t>
   </x:si>
   <x:si>
@@ -282,19 +291,10 @@
     <x:t>AHMED, JUNAID</x:t>
   </x:si>
   <x:si>
-    <x:t>FRIEDMAN, JASON</x:t>
-  </x:si>
-  <x:si>
     <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
   </x:si>
   <x:si>
     <x:t>AMIWALA, BUSHRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1550,22 +1550,22 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="B36" s="1" t="s">
+      <x:c r="D36" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="C36" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D36" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>663879</x:v>
+        <x:v>750000</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>51</x:v>
@@ -1596,25 +1596,25 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>4379246</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
@@ -1625,16 +1625,16 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>59748</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>51</x:v>
@@ -1642,22 +1642,22 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>3985700</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>12</x:v>
@@ -1665,59 +1665,59 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>1183678</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>4383749</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
         <x:v>75</x:v>
@@ -1726,21 +1726,21 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>149773</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
         <x:v>75</x:v>
@@ -1749,30 +1749,30 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>1426379</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>104555</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>12</x:v>
@@ -1780,45 +1780,45 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>750000</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>2326917</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>51</x:v>
@@ -1887,10 +1887,10 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>65</x:v>
@@ -1955,7 +1955,7 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>50</x:v>
@@ -1989,7 +1989,7 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>14</x:v>
@@ -2023,7 +2023,7 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>75</x:v>
@@ -2057,7 +2057,7 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>75</x:v>
@@ -2553,7 +2553,7 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>65</x:v>
@@ -3494,7 +3494,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>18</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -280,6 +280,15 @@
   </x:si>
   <x:si>
     <x:t>FRIEDMAN, JASON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POWELL, DENISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAVANAUGH, JOHN</x:t>
   </x:si>
   <x:si>
     <x:t>C00935809</x:t>
@@ -365,8 +374,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G47" totalsRowShown="0">
-  <x:autoFilter ref="A1:G47"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G49" totalsRowShown="0">
+  <x:autoFilter ref="A1:G49"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -381,8 +390,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E38" totalsRowShown="0">
-  <x:autoFilter ref="A1:E38"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E40" totalsRowShown="0">
+  <x:autoFilter ref="A1:E40"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -395,8 +404,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D33" totalsRowShown="0">
-  <x:autoFilter ref="A1:D33"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D35" totalsRowShown="0">
+  <x:autoFilter ref="A1:D35"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -408,8 +417,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C22" totalsRowShown="0">
-  <x:autoFilter ref="A1:C22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C24" totalsRowShown="0">
+  <x:autoFilter ref="A1:C24"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -420,8 +429,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B17" totalsRowShown="0">
-  <x:autoFilter ref="A1:B17"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B18" totalsRowShown="0">
+  <x:autoFilter ref="A1:B18"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -431,8 +440,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C30" totalsRowShown="0">
-  <x:autoFilter ref="A1:C30"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C31" totalsRowShown="0">
+  <x:autoFilter ref="A1:C31"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -730,7 +739,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G47"/>
+  <x:dimension ref="A1:G49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1665,22 +1674,22 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>4379246</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1688,22 +1697,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
         <x:v>89</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>663879</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>51</x:v>
@@ -1711,82 +1720,82 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>1183678</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>104555</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>3985700</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
         <x:v>75</x:v>
@@ -1795,7 +1804,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>4383749</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>12</x:v>
@@ -1809,18 +1818,64 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E47" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F47" s="1">
+        <x:v>3985700</x:v>
+      </x:c>
+      <x:c r="G47" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:7">
+      <x:c r="A48" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F48" s="1">
+        <x:v>4383749</x:v>
+      </x:c>
+      <x:c r="G48" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:7">
+      <x:c r="A49" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="D47" s="1" t="s">
+      <x:c r="D49" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="E47" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F47" s="1">
+      <x:c r="E49" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F49" s="1">
         <x:v>1426379</x:v>
       </x:c>
-      <x:c r="G47" s="1" t="s">
+      <x:c r="G49" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
@@ -1840,7 +1895,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E38"/>
+  <x:dimension ref="A1:E40"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1989,7 +2044,7 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>14</x:v>
@@ -2023,7 +2078,7 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>75</x:v>
@@ -2057,7 +2112,7 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>75</x:v>
@@ -2261,33 +2316,33 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>938</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>1974</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -2295,16 +2350,16 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>382</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>12</x:v>
@@ -2312,67 +2367,67 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>2326917</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>-31053</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>51</x:v>
@@ -2380,16 +2435,16 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>382</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>12</x:v>
@@ -2397,30 +2452,30 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>382</x:v>
@@ -2431,33 +2486,33 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>39386</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>12</x:v>
@@ -2465,35 +2520,69 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>382</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D38" s="1">
+        <x:v>39386</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:5">
+      <x:c r="A39" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D39" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="E39" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:5">
+      <x:c r="A40" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B38" s="1" t="s">
+      <x:c r="B40" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C38" s="1" t="s">
+      <x:c r="C40" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D38" s="1">
+      <x:c r="D40" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="E38" s="1" t="s">
+      <x:c r="E40" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -2513,7 +2602,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D33"/>
+  <x:dimension ref="A1:D35"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2805,27 +2894,27 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>938</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>2356</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -2833,55 +2922,55 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>2326917</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>2326917</x:v>
+        <x:v>2356</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>-31053</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>51</x:v>
@@ -2889,13 +2978,13 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>382</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>12</x:v>
@@ -2903,24 +2992,24 @@
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>382</x:v>
@@ -2931,27 +3020,27 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>39386</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>12</x:v>
@@ -2959,29 +3048,57 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>382</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C33" s="1">
+        <x:v>39386</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:4">
+      <x:c r="A34" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C34" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:4">
+      <x:c r="A35" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B33" s="1" t="s">
+      <x:c r="B35" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C33" s="1">
+      <x:c r="C35" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="D33" s="1" t="s">
+      <x:c r="D35" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -3001,7 +3118,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C22"/>
+  <x:dimension ref="A1:C24"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3155,32 +3272,32 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>3294</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>4653834</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>408441</x:v>
+        <x:v>3294</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>12</x:v>
@@ -3188,10 +3305,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>-31053</x:v>
+        <x:v>4653834</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>51</x:v>
@@ -3199,10 +3316,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>382</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>12</x:v>
@@ -3210,32 +3327,32 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>764</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B21" s="1">
-        <x:v>39768</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>12</x:v>
@@ -3243,12 +3360,34 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B22" s="1">
+        <x:v>-46</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B23" s="1">
+        <x:v>39768</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B22" s="1">
+      <x:c r="B24" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="C22" s="1" t="s">
+      <x:c r="C24" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -3268,7 +3407,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B17"/>
+  <x:dimension ref="A1:B18"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3366,49 +3505,57 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>3294</x:v>
+        <x:v>300000</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>5062275</x:v>
+        <x:v>3294</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>-30671</x:v>
+        <x:v>5062275</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>764</x:v>
+        <x:v>-30671</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>39722</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B17" s="1">
+        <x:v>39722</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:2">
+      <x:c r="A18" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B17" s="1">
+      <x:c r="B18" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>
@@ -3428,7 +3575,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C30"/>
+  <x:dimension ref="A1:C31"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3494,7 +3641,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>18</x:v>
@@ -3648,79 +3795,79 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>3294</x:v>
+        <x:v>300000</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>350000</x:v>
+        <x:v>3294</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>58441</x:v>
+        <x:v>350000</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>4653834</x:v>
+        <x:v>58441</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>382</x:v>
+        <x:v>4653834</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>-31053</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>764</x:v>
+        <x:v>-31053</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
@@ -3728,42 +3875,53 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>382</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>39386</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>-46</x:v>
+        <x:v>39386</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C30" s="1">
+        <x:v>-46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B30" s="1" t="s">
+      <x:c r="B31" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C30" s="1">
+      <x:c r="C31" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -280,6 +280,9 @@
   </x:si>
   <x:si>
     <x:t>FRIEDMAN, JASON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALLREIN, ED</x:t>
   </x:si>
   <x:si>
     <x:t>POWELL, DENISE</x:t>
@@ -374,8 +377,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G49" totalsRowShown="0">
-  <x:autoFilter ref="A1:G49"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G51" totalsRowShown="0">
+  <x:autoFilter ref="A1:G51"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -390,8 +393,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E40" totalsRowShown="0">
-  <x:autoFilter ref="A1:E40"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E41" totalsRowShown="0">
+  <x:autoFilter ref="A1:E41"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -404,8 +407,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D35" totalsRowShown="0">
-  <x:autoFilter ref="A1:D35"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D36" totalsRowShown="0">
+  <x:autoFilter ref="A1:D36"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -417,8 +420,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C24" totalsRowShown="0">
-  <x:autoFilter ref="A1:C24"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C25" totalsRowShown="0">
+  <x:autoFilter ref="A1:C25"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -739,7 +742,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G49"/>
+  <x:dimension ref="A1:G51"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1588,19 +1591,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>2645986</x:v>
+        <x:v>623905</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
@@ -1611,7 +1614,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
         <x:v>50</x:v>
@@ -1620,10 +1623,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>59748</x:v>
+        <x:v>2645986</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
@@ -1634,16 +1637,16 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>2326917</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>51</x:v>
@@ -1651,22 +1654,22 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>149773</x:v>
+        <x:v>110101</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>12</x:v>
@@ -1674,68 +1677,68 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>150000</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>150000</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>4379246</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1743,22 +1746,22 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B44" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C44" s="1" t="s">
-        <x:v>92</x:v>
-      </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>663879</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>51</x:v>
@@ -1766,82 +1769,82 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>1183678</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>104555</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>3985700</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
         <x:v>75</x:v>
@@ -1850,7 +1853,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>4383749</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>12</x:v>
@@ -1864,18 +1867,64 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E49" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F49" s="1">
+        <x:v>3985700</x:v>
+      </x:c>
+      <x:c r="G49" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:7">
+      <x:c r="A50" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F50" s="1">
+        <x:v>4383749</x:v>
+      </x:c>
+      <x:c r="G50" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:7">
+      <x:c r="A51" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B51" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C51" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="D49" s="1" t="s">
+      <x:c r="D51" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="E49" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F49" s="1">
+      <x:c r="E51" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F51" s="1">
         <x:v>1426379</x:v>
       </x:c>
-      <x:c r="G49" s="1" t="s">
+      <x:c r="G51" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
@@ -1895,7 +1944,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E40"/>
+  <x:dimension ref="A1:E41"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2044,7 +2093,7 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>14</x:v>
@@ -2078,7 +2127,7 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>75</x:v>
@@ -2112,7 +2161,7 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>75</x:v>
@@ -2189,7 +2238,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>-1861</x:v>
+        <x:v>622044</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>51</x:v>
@@ -2197,16 +2246,16 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>382</x:v>
+        <x:v>110101</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>12</x:v>
@@ -2214,16 +2263,16 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>2538</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>12</x:v>
@@ -2231,16 +2280,16 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>382</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>12</x:v>
@@ -2248,16 +2297,16 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>12</x:v>
@@ -2265,50 +2314,50 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>2651</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>12</x:v>
@@ -2316,50 +2365,50 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>150000</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>938</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>12</x:v>
@@ -2370,13 +2419,13 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>1974</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>12</x:v>
@@ -2384,7 +2433,7 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>38</x:v>
@@ -2393,7 +2442,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>382</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>12</x:v>
@@ -2401,19 +2450,19 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
@@ -2421,7 +2470,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>27</x:v>
@@ -2435,7 +2484,7 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>24</x:v>
@@ -2444,55 +2493,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>382</x:v>
@@ -2503,10 +2552,10 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>11</x:v>
@@ -2520,50 +2569,50 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>382</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>12</x:v>
@@ -2571,18 +2620,35 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:5">
+      <x:c r="A41" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D41" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -2602,7 +2668,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D35"/>
+  <x:dimension ref="A1:D36"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2788,7 +2854,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>-1861</x:v>
+        <x:v>622044</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>51</x:v>
@@ -2796,13 +2862,13 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>382</x:v>
+        <x:v>110101</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>12</x:v>
@@ -2810,13 +2876,13 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>2538</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>12</x:v>
@@ -2824,13 +2890,13 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>382</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>12</x:v>
@@ -2838,13 +2904,13 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>12</x:v>
@@ -2852,41 +2918,41 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>2651</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>12</x:v>
@@ -2894,16 +2960,16 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>150000</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
@@ -2911,24 +2977,24 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>938</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>12</x:v>
@@ -2936,13 +3002,13 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>2356</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>12</x:v>
@@ -2950,21 +3016,21 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>2326917</x:v>
+        <x:v>2356</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
         <x:v>27</x:v>
@@ -2984,46 +3050,46 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>382</x:v>
@@ -3034,7 +3100,7 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>11</x:v>
@@ -3048,41 +3114,41 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>382</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
         <x:v>12</x:v>
@@ -3090,15 +3156,29 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:4">
+      <x:c r="A36" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C36" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -3118,7 +3198,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C24"/>
+  <x:dimension ref="A1:C25"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3209,7 +3289,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>-1861</x:v>
+        <x:v>622044</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>51</x:v>
@@ -3217,10 +3297,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>382</x:v>
+        <x:v>110101</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>12</x:v>
@@ -3228,10 +3308,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>2920</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>12</x:v>
@@ -3239,10 +3319,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>2649</x:v>
+        <x:v>2920</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -3250,54 +3330,54 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>602651</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>150000</x:v>
+        <x:v>602651</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>3294</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>12</x:v>
@@ -3305,13 +3385,13 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>4653834</x:v>
+        <x:v>3294</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -3319,21 +3399,21 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>408441</x:v>
+        <x:v>4653834</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -3341,18 +3421,18 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B21" s="1">
-        <x:v>764</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>12</x:v>
@@ -3360,13 +3440,13 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B22" s="1">
-        <x:v>-46</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -3374,20 +3454,31 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B23" s="1">
-        <x:v>39768</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B24" s="1">
+        <x:v>39768</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B24" s="1">
+      <x:c r="B25" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="C24" s="1" t="s">
+      <x:c r="C25" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -3460,7 +3551,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>-1861</x:v>
+        <x:v>732145</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
@@ -3505,7 +3596,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>300000</x:v>
@@ -3641,7 +3732,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>18</x:v>
@@ -3724,7 +3815,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>-1861</x:v>
+        <x:v>732145</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -3798,7 +3889,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>300000</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -207,6 +207,9 @@
     <x:t>23</x:t>
   </x:si>
   <x:si>
+    <x:t>FRIEDMAN, JASON</x:t>
+  </x:si>
+  <x:si>
     <x:t>MALINOWSKI, TOM</x:t>
   </x:si>
   <x:si>
@@ -277,9 +280,6 @@
   </x:si>
   <x:si>
     <x:t>48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIEDMAN, JASON</x:t>
   </x:si>
   <x:si>
     <x:t>GALLREIN, ED</x:t>
@@ -377,8 +377,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G51" totalsRowShown="0">
-  <x:autoFilter ref="A1:G51"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G50" totalsRowShown="0">
+  <x:autoFilter ref="A1:G50"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -742,7 +742,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G51"/>
+  <x:dimension ref="A1:G50"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1255,7 +1255,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>2322515</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>12</x:v>
@@ -1318,13 +1318,13 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>2326917</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>51</x:v>
@@ -1341,16 +1341,16 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>-28160</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
@@ -1361,62 +1361,62 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E27" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="F27" s="1">
-        <x:v>-22643</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B28" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C28" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="F28" s="1">
-        <x:v>39386</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B29" s="1" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>500346</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>12</x:v>
@@ -1424,22 +1424,22 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B30" s="1" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C30" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>600000</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>12</x:v>
@@ -1447,22 +1447,22 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>350000</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>12</x:v>
@@ -1470,22 +1470,22 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>2359443</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1493,22 +1493,22 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="B33" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>2893782</x:v>
+        <x:v>2359443</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>12</x:v>
@@ -1516,22 +1516,22 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>2845686</x:v>
+        <x:v>2893782</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1539,45 +1539,45 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>1314739</x:v>
+        <x:v>2845686</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>750000</x:v>
+        <x:v>1314739</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>51</x:v>
@@ -1585,22 +1585,22 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>623905</x:v>
+        <x:v>750000</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>51</x:v>
@@ -1614,19 +1614,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>2645986</x:v>
+        <x:v>623905</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
@@ -1637,19 +1637,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>59748</x:v>
+        <x:v>110101</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
@@ -1660,62 +1660,62 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>110101</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>2326917</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>149773</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1723,13 +1723,13 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
         <x:v>17</x:v>
@@ -1741,53 +1741,53 @@
         <x:v>150000</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>150000</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>4379246</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
@@ -1798,16 +1798,16 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>663879</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>51</x:v>
@@ -1821,39 +1821,39 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>1183678</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>104555</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>12</x:v>
@@ -1861,22 +1861,22 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>3985700</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -1884,47 +1884,24 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>4383749</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:7">
-      <x:c r="A51" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B51" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C51" s="1" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D51" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E51" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F51" s="1">
-        <x:v>1426379</x:v>
-      </x:c>
-      <x:c r="G51" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
@@ -1974,13 +1951,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>-28160</x:v>
@@ -1991,13 +1968,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>750000</x:v>
@@ -2059,7 +2036,7 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>50</x:v>
@@ -2130,7 +2107,7 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>18</x:v>
@@ -2144,10 +2121,10 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>18</x:v>
@@ -2164,7 +2141,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>18</x:v>
@@ -2178,10 +2155,10 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>18</x:v>
@@ -2195,10 +2172,10 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>18</x:v>
@@ -2331,13 +2308,13 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>-22643</x:v>
@@ -2365,7 +2342,7 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>55</x:v>
@@ -2467,7 +2444,7 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>50</x:v>
@@ -2484,7 +2461,7 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>24</x:v>
@@ -2603,10 +2580,10 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>34</x:v>
@@ -2694,10 +2671,10 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>-28160</x:v>
@@ -2708,10 +2685,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>750000</x:v>
@@ -2806,7 +2783,7 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>18</x:v>
@@ -2820,7 +2797,7 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>18</x:v>
@@ -2935,7 +2912,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>-22643</x:v>
@@ -3142,7 +3119,7 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>34</x:v>
@@ -3220,7 +3197,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>750000</x:v>
@@ -3231,7 +3208,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>-28160</x:v>
@@ -3341,7 +3318,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>-22643</x:v>
@@ -3516,7 +3493,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>721840</x:v>
@@ -3580,7 +3557,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>-22643</x:v>
@@ -3691,7 +3668,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>750000</x:v>
@@ -3702,7 +3679,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>-28160</x:v>
@@ -3721,7 +3698,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>18</x:v>
@@ -3754,7 +3731,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>18</x:v>
@@ -3765,7 +3742,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>18</x:v>
@@ -3776,7 +3753,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>18</x:v>
@@ -3856,7 +3833,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>-22643</x:v>
@@ -3864,7 +3841,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>46</x:v>
@@ -3886,7 +3863,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>89</x:v>
@@ -3908,7 +3885,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>27</x:v>
@@ -3985,7 +3962,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>34</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -276,6 +276,12 @@
     <x:t>BISS, DANIEL</x:t>
   </x:si>
   <x:si>
+    <x:t>CAVANAUGH, JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
     <x:t>CAMPA-NAJJAR, AMMAR</x:t>
   </x:si>
   <x:si>
@@ -286,12 +292,6 @@
   </x:si>
   <x:si>
     <x:t>POWELL, DENISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAVANAUGH, JOHN</x:t>
   </x:si>
   <x:si>
     <x:t>C00935809</x:t>
@@ -377,8 +377,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G50" totalsRowShown="0">
-  <x:autoFilter ref="A1:G50"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G51" totalsRowShown="0">
+  <x:autoFilter ref="A1:G51"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -443,8 +443,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C31" totalsRowShown="0">
-  <x:autoFilter ref="A1:C31"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C32" totalsRowShown="0">
+  <x:autoFilter ref="A1:C32"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -742,7 +742,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G50"/>
+  <x:dimension ref="A1:G51"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1594,13 +1594,13 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="E37" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="F37" s="1">
-        <x:v>750000</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>51</x:v>
@@ -1608,22 +1608,22 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>623905</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>51</x:v>
@@ -1637,7 +1637,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
         <x:v>55</x:v>
@@ -1646,10 +1646,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>110101</x:v>
+        <x:v>623905</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
@@ -1660,62 +1660,62 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>2326917</x:v>
+        <x:v>110101</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>149773</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>150000</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1735,59 +1735,59 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F43" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>4379246</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>663879</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
@@ -1798,16 +1798,16 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>1183678</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>51</x:v>
@@ -1821,7 +1821,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
         <x:v>76</x:v>
@@ -1830,30 +1830,30 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>104555</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>3985700</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>12</x:v>
@@ -1867,16 +1867,16 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>4383749</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -1890,7 +1890,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
         <x:v>76</x:v>
@@ -1899,9 +1899,32 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F50" s="1">
+        <x:v>4383749</x:v>
+      </x:c>
+      <x:c r="G50" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:7">
+      <x:c r="A51" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B51" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C51" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D51" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E51" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F51" s="1">
         <x:v>1426379</x:v>
       </x:c>
-      <x:c r="G50" s="1" t="s">
+      <x:c r="G51" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
@@ -1968,16 +1991,16 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="D3" s="1">
-        <x:v>750000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
         <x:v>51</x:v>
@@ -2223,7 +2246,7 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>55</x:v>
@@ -2359,16 +2382,16 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>150000</x:v>
+        <x:v>151870</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>51</x:v>
@@ -2376,13 +2399,13 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>150000</x:v>
@@ -2685,13 +2708,13 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>750000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
         <x:v>51</x:v>
@@ -2954,10 +2977,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>150000</x:v>
+        <x:v>151870</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>51</x:v>
@@ -2968,7 +2991,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>150000</x:v>
@@ -3200,7 +3223,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>750000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
         <x:v>51</x:v>
@@ -3340,10 +3363,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>150000</x:v>
+        <x:v>151870</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>51</x:v>
@@ -3351,7 +3374,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>150000</x:v>
@@ -3496,7 +3519,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>721840</x:v>
+        <x:v>971840</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -3573,10 +3596,10 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>300000</x:v>
+        <x:v>301870</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
@@ -3643,7 +3666,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C31"/>
+  <x:dimension ref="A1:C32"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3671,7 +3694,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>750000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -3863,90 +3886,90 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>300000</x:v>
+        <x:v>1870</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>3294</x:v>
+        <x:v>300000</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>350000</x:v>
+        <x:v>3294</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>58441</x:v>
+        <x:v>350000</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>4653834</x:v>
+        <x:v>58441</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>382</x:v>
+        <x:v>4653834</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>-31053</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>764</x:v>
+        <x:v>-31053</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
@@ -3954,42 +3977,53 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>382</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>39386</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>-46</x:v>
+        <x:v>39386</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C31" s="1">
+        <x:v>-46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B31" s="1" t="s">
+      <x:c r="B32" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C31" s="1">
+      <x:c r="C32" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -1738,7 +1738,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>150000</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1761,7 +1761,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>150000</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>51</x:v>
@@ -2391,7 +2391,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>151870</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>51</x:v>
@@ -2408,7 +2408,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>150000</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>12</x:v>
@@ -2980,7 +2980,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>151870</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>51</x:v>
@@ -2994,7 +2994,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>150000</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>12</x:v>
@@ -3366,7 +3366,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>151870</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>51</x:v>
@@ -3377,7 +3377,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>150000</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>12</x:v>
@@ -3599,7 +3599,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>301870</x:v>
+        <x:v>399814</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
@@ -3903,7 +3903,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>300000</x:v>
+        <x:v>397944</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -276,37 +276,40 @@
     <x:t>BISS, DANIEL</x:t>
   </x:si>
   <x:si>
+    <x:t>C00935809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHMED, JUNAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMIWALA, BUSHRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POWELL, DENISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
     <x:t>CAVANAUGH, JOHN</x:t>
   </x:si>
   <x:si>
-    <x:t>NE</x:t>
+    <x:t>THOMPSON, MIKE MR.</x:t>
   </x:si>
   <x:si>
     <x:t>CAMPA-NAJJAR, AMMAR</x:t>
   </x:si>
   <x:si>
     <x:t>48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALLREIN, ED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POWELL, DENISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935809</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHMED, JUNAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMIWALA, BUSHRA</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -377,8 +380,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G51" totalsRowShown="0">
-  <x:autoFilter ref="A1:G51"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G52" totalsRowShown="0">
+  <x:autoFilter ref="A1:G52"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -393,8 +396,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E41" totalsRowShown="0">
-  <x:autoFilter ref="A1:E41"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E42" totalsRowShown="0">
+  <x:autoFilter ref="A1:E42"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -407,8 +410,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D36" totalsRowShown="0">
-  <x:autoFilter ref="A1:D36"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D37" totalsRowShown="0">
+  <x:autoFilter ref="A1:D37"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -443,8 +446,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C32" totalsRowShown="0">
-  <x:autoFilter ref="A1:C32"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C33" totalsRowShown="0">
+  <x:autoFilter ref="A1:C33"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -742,7 +745,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G51"/>
+  <x:dimension ref="A1:G52"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1585,22 +1588,22 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>1870</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>51</x:v>
@@ -1608,22 +1611,22 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>1000000</x:v>
+        <x:v>1241841</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>51</x:v>
@@ -1631,45 +1634,45 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>623905</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>110101</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>12</x:v>
@@ -1677,22 +1680,22 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>2326917</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>51</x:v>
@@ -1700,13 +1703,13 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
         <x:v>76</x:v>
@@ -1715,7 +1718,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>149773</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1723,22 +1726,22 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>198972</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1746,22 +1749,22 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>198972</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>51</x:v>
@@ -1769,22 +1772,22 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>4379246</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>12</x:v>
@@ -1792,114 +1795,114 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>663879</x:v>
+        <x:v>219149</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B47" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C47" s="1" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="B47" s="1" t="s">
+      <x:c r="D47" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E47" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C47" s="1" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D47" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="E47" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="F47" s="1">
-        <x:v>1183678</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C48" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D48" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="E48" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="F48" s="1">
-        <x:v>104555</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>3985700</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>4383749</x:v>
+        <x:v>30801</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>12</x:v>
@@ -1907,24 +1910,47 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>1426379</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:7">
+      <x:c r="A52" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B52" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C52" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F52" s="1">
+        <x:v>2326917</x:v>
+      </x:c>
+      <x:c r="G52" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
@@ -1944,7 +1970,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E41"/>
+  <x:dimension ref="A1:E42"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1974,16 +2000,16 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="D2" s="1">
-        <x:v>-28160</x:v>
+        <x:v>30801</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
         <x:v>12</x:v>
@@ -1991,50 +2017,50 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="D3" s="1">
-        <x:v>1000000</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D4" s="1">
-        <x:v>382</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D5" s="1">
-        <x:v>6739071</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>12</x:v>
@@ -2042,24 +2068,24 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>-9678</x:v>
+        <x:v>6739071</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>50</x:v>
@@ -2068,7 +2094,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>59748</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>51</x:v>
@@ -2076,7 +2102,7 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>50</x:v>
@@ -2085,32 +2111,32 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>4968501</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>663879</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>14</x:v>
@@ -2119,32 +2145,32 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>6879864</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>1183678</x:v>
+        <x:v>6879864</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>76</x:v>
@@ -2153,7 +2179,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>2741118</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>51</x:v>
@@ -2161,7 +2187,7 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>76</x:v>
@@ -2170,15 +2196,15 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>104555</x:v>
+        <x:v>2741118</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>76</x:v>
@@ -2187,7 +2213,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>149773</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>12</x:v>
@@ -2195,7 +2221,7 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>76</x:v>
@@ -2204,7 +2230,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>7729781</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>12</x:v>
@@ -2212,33 +2238,33 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>-6917</x:v>
+        <x:v>7729781</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>622044</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>51</x:v>
@@ -2246,7 +2272,7 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>55</x:v>
@@ -2255,24 +2281,24 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>110101</x:v>
+        <x:v>1239980</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>382</x:v>
+        <x:v>219149</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>12</x:v>
@@ -2280,16 +2306,16 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>2538</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>12</x:v>
@@ -2297,16 +2323,16 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>382</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>12</x:v>
@@ -2314,16 +2340,16 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>12</x:v>
@@ -2331,50 +2357,50 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>2651</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>12</x:v>
@@ -2382,50 +2408,50 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>938</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>12</x:v>
@@ -2436,13 +2462,13 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>1974</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>12</x:v>
@@ -2450,7 +2476,7 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>38</x:v>
@@ -2459,7 +2485,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>382</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>12</x:v>
@@ -2467,19 +2493,19 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
@@ -2487,7 +2513,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>27</x:v>
@@ -2501,7 +2527,7 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>24</x:v>
@@ -2510,55 +2536,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>382</x:v>
@@ -2569,10 +2595,10 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>11</x:v>
@@ -2586,50 +2612,50 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="D40" s="1">
-        <x:v>382</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>12</x:v>
@@ -2637,18 +2663,35 @@
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:5">
+      <x:c r="A42" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B42" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D42" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="E42" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -2668,7 +2711,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D36"/>
+  <x:dimension ref="A1:D37"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2694,13 +2737,13 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>-28160</x:v>
+        <x:v>30801</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
         <x:v>12</x:v>
@@ -2708,41 +2751,41 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>1000000</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>382</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>6739071</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
         <x:v>12</x:v>
@@ -2750,16 +2793,16 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>50070</x:v>
+        <x:v>6739071</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
@@ -2770,24 +2813,24 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>4968501</x:v>
+        <x:v>50070</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>663879</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
@@ -2798,24 +2841,24 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>6879864</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>3924796</x:v>
+        <x:v>6879864</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
@@ -2826,35 +2869,35 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>7984109</x:v>
+        <x:v>3924796</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>-6917</x:v>
+        <x:v>7984109</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>622044</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>51</x:v>
@@ -2868,21 +2911,21 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>110101</x:v>
+        <x:v>1239980</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>382</x:v>
+        <x:v>219149</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>12</x:v>
@@ -2890,13 +2933,13 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>2538</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>12</x:v>
@@ -2904,13 +2947,13 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>382</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>12</x:v>
@@ -2918,13 +2961,13 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
         <x:v>12</x:v>
@@ -2932,41 +2975,41 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>2651</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>12</x:v>
@@ -2974,16 +3017,16 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
@@ -2991,24 +3034,24 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>938</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>12</x:v>
@@ -3016,13 +3059,13 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>2356</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
         <x:v>12</x:v>
@@ -3030,21 +3073,21 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>2326917</x:v>
+        <x:v>2356</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>27</x:v>
@@ -3064,46 +3107,46 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>382</x:v>
@@ -3114,7 +3157,7 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>11</x:v>
@@ -3128,41 +3171,41 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>382</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
         <x:v>12</x:v>
@@ -3170,15 +3213,29 @@
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:4">
+      <x:c r="A37" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C37" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -3234,7 +3291,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>-28160</x:v>
+        <x:v>2641</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>12</x:v>
@@ -3289,7 +3346,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>622044</x:v>
+        <x:v>1239980</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>51</x:v>
@@ -3300,7 +3357,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>110101</x:v>
+        <x:v>219149</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>12</x:v>
@@ -3363,7 +3420,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>200842</x:v>
@@ -3374,7 +3431,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>198972</x:v>
@@ -3519,7 +3576,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>971840</x:v>
+        <x:v>1002641</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -3551,7 +3608,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>732145</x:v>
+        <x:v>1459129</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
@@ -3596,7 +3653,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>399814</x:v>
@@ -3666,7 +3723,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C32"/>
+  <x:dimension ref="A1:C33"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3688,112 +3745,112 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>1000000</x:v>
+        <x:v>30801</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>-28160</x:v>
+        <x:v>1000000</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>382</x:v>
+        <x:v>-28160</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>6738689</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>1952112</x:v>
+        <x:v>6738689</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>764</x:v>
+        <x:v>1952112</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>500346</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>16850035</x:v>
+        <x:v>500346</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>149773</x:v>
+        <x:v>16850035</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>5018571</x:v>
+        <x:v>149773</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -3801,10 +3858,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>-6917</x:v>
+        <x:v>5018571</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -3812,21 +3869,21 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>732145</x:v>
+        <x:v>-6917</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>382</x:v>
+        <x:v>1459129</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -3834,10 +3891,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>2920</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -3845,43 +3902,43 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>2649</x:v>
+        <x:v>2920</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>600000</x:v>
+        <x:v>-22643</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>2651</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -3889,98 +3946,98 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>1870</x:v>
+        <x:v>2651</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>397944</x:v>
+        <x:v>1870</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>3294</x:v>
+        <x:v>397944</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>350000</x:v>
+        <x:v>3294</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>58441</x:v>
+        <x:v>350000</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>4653834</x:v>
+        <x:v>58441</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>382</x:v>
+        <x:v>4653834</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>-31053</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>764</x:v>
+        <x:v>-31053</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
@@ -3988,42 +4045,53 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>382</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>39386</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>-46</x:v>
+        <x:v>39386</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C32" s="1">
+        <x:v>-46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B32" s="1" t="s">
+      <x:c r="B33" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C32" s="1">
+      <x:c r="C33" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -276,6 +276,27 @@
     <x:t>BISS, DANIEL</x:t>
   </x:si>
   <x:si>
+    <x:t>CAVANAUGH, JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POWELL, DENISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THOMPSON, MIKE MR.</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00935809</x:t>
   </x:si>
   <x:si>
@@ -289,27 +310,6 @@
   </x:si>
   <x:si>
     <x:t>AMIWALA, BUSHRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALLREIN, ED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POWELL, DENISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAVANAUGH, JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THOMPSON, MIKE MR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1588,22 +1588,22 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="B37" s="1" t="s">
+      <x:c r="D37" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="C37" s="1" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D37" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E37" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="F37" s="1">
-        <x:v>663879</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>51</x:v>
@@ -1611,22 +1611,22 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>1241841</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>51</x:v>
@@ -1634,45 +1634,45 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>4379246</x:v>
+        <x:v>1241841</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>3985700</x:v>
+        <x:v>219149</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>12</x:v>
@@ -1680,22 +1680,22 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>1183678</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>51</x:v>
@@ -1703,13 +1703,13 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
         <x:v>76</x:v>
@@ -1718,7 +1718,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>4383749</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1726,22 +1726,22 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>149773</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1749,22 +1749,22 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>1426379</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>51</x:v>
@@ -1772,22 +1772,22 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>104555</x:v>
+        <x:v>30801</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>12</x:v>
@@ -1795,22 +1795,22 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>219149</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>12</x:v>
@@ -1818,45 +1818,45 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>198972</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>1870</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>51</x:v>
@@ -1864,45 +1864,45 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>198972</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>30801</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>12</x:v>
@@ -1910,45 +1910,45 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>1000000</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>2326917</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>51</x:v>
@@ -2000,7 +2000,7 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>55</x:v>
@@ -2034,10 +2034,10 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>66</x:v>
@@ -2136,7 +2136,7 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>14</x:v>
@@ -2170,7 +2170,7 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>76</x:v>
@@ -2204,7 +2204,7 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>76</x:v>
@@ -2289,7 +2289,7 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>55</x:v>
@@ -2425,13 +2425,13 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>200842</x:v>
@@ -2442,13 +2442,13 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>198972</x:v>
@@ -2765,7 +2765,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>66</x:v>
@@ -3034,7 +3034,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>200842</x:v>
@@ -3048,7 +3048,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>198972</x:v>
@@ -3420,7 +3420,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>200842</x:v>
@@ -3431,7 +3431,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>198972</x:v>
@@ -3653,7 +3653,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>399814</x:v>
@@ -3800,7 +3800,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>18</x:v>
@@ -3957,7 +3957,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1870</x:v>
@@ -3968,7 +3968,7 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>397944</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -267,6 +267,21 @@
     <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
   </x:si>
   <x:si>
+    <x:t>C00935809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHMED, JUNAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMIWALA, BUSHRA</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00936724</x:t>
   </x:si>
   <x:si>
@@ -295,21 +310,6 @@
   </x:si>
   <x:si>
     <x:t>THOMPSON, MIKE MR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935809</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHMED, JUNAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMIWALA, BUSHRA</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -380,8 +380,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G52" totalsRowShown="0">
-  <x:autoFilter ref="A1:G52"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G55" totalsRowShown="0">
+  <x:autoFilter ref="A1:G55"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -745,7 +745,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G52"/>
+  <x:dimension ref="A1:G55"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1525,7 +1525,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
         <x:v>14</x:v>
@@ -1534,10 +1534,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>2893782</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
@@ -1548,7 +1548,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
         <x:v>76</x:v>
@@ -1557,10 +1557,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>2845686</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
@@ -1571,7 +1571,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
         <x:v>76</x:v>
@@ -1580,76 +1580,76 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>1314739</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>1870</x:v>
+        <x:v>2893782</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>1000000</x:v>
+        <x:v>2845686</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>1241841</x:v>
+        <x:v>1314739</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>51</x:v>
@@ -1657,45 +1657,45 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>219149</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>2326917</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>51</x:v>
@@ -1703,45 +1703,45 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>149773</x:v>
+        <x:v>1250481</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>198972</x:v>
+        <x:v>221309</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1749,22 +1749,22 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>198972</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>51</x:v>
@@ -1772,22 +1772,22 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>30801</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>12</x:v>
@@ -1795,22 +1795,22 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>4379246</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>12</x:v>
@@ -1818,22 +1818,22 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>663879</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>51</x:v>
@@ -1841,45 +1841,45 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>1183678</x:v>
+        <x:v>86493</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>104555</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -1893,7 +1893,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
         <x:v>14</x:v>
@@ -1902,10 +1902,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>3985700</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
@@ -1916,7 +1916,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
         <x:v>76</x:v>
@@ -1925,10 +1925,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>4383749</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
@@ -1939,7 +1939,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
         <x:v>76</x:v>
@@ -1948,9 +1948,78 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F52" s="1">
+        <x:v>104555</x:v>
+      </x:c>
+      <x:c r="G52" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:7">
+      <x:c r="A53" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B53" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C53" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D53" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E53" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F53" s="1">
+        <x:v>3985700</x:v>
+      </x:c>
+      <x:c r="G53" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:7">
+      <x:c r="A54" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B54" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C54" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D54" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E54" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F54" s="1">
+        <x:v>4383749</x:v>
+      </x:c>
+      <x:c r="G54" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:7">
+      <x:c r="A55" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B55" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C55" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D55" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E55" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F55" s="1">
         <x:v>1426379</x:v>
       </x:c>
-      <x:c r="G52" s="1" t="s">
+      <x:c r="G55" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
@@ -2000,7 +2069,7 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>55</x:v>
@@ -2009,7 +2078,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="D2" s="1">
-        <x:v>30801</x:v>
+        <x:v>86493</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
         <x:v>12</x:v>
@@ -2034,10 +2103,10 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>66</x:v>
@@ -2136,7 +2205,7 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>14</x:v>
@@ -2145,7 +2214,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>663879</x:v>
+        <x:v>1327758</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>51</x:v>
@@ -2170,7 +2239,7 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>76</x:v>
@@ -2179,7 +2248,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>1183678</x:v>
+        <x:v>2367356</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>51</x:v>
@@ -2187,7 +2256,7 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>76</x:v>
@@ -2204,7 +2273,7 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>76</x:v>
@@ -2213,7 +2282,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>104555</x:v>
+        <x:v>209110</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>12</x:v>
@@ -2221,7 +2290,7 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>76</x:v>
@@ -2281,7 +2350,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>1239980</x:v>
+        <x:v>1248620</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>51</x:v>
@@ -2289,7 +2358,7 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>55</x:v>
@@ -2298,7 +2367,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>219149</x:v>
+        <x:v>221309</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>12</x:v>
@@ -2425,13 +2494,13 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>200842</x:v>
@@ -2442,13 +2511,13 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>198972</x:v>
@@ -2743,7 +2812,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>30801</x:v>
+        <x:v>86493</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
         <x:v>12</x:v>
@@ -2765,7 +2834,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>66</x:v>
@@ -2841,7 +2910,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>663879</x:v>
+        <x:v>1327758</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>51</x:v>
@@ -2869,7 +2938,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>3924796</x:v>
+        <x:v>5108474</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
         <x:v>51</x:v>
@@ -2883,7 +2952,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>7984109</x:v>
+        <x:v>8088664</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
         <x:v>12</x:v>
@@ -2911,7 +2980,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>1239980</x:v>
+        <x:v>1248620</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>51</x:v>
@@ -2925,7 +2994,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>219149</x:v>
+        <x:v>221309</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>12</x:v>
@@ -3034,7 +3103,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>200842</x:v>
@@ -3048,7 +3117,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>198972</x:v>
@@ -3291,7 +3360,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>2641</x:v>
+        <x:v>58333</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>12</x:v>
@@ -3313,7 +3382,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>4638745</x:v>
+        <x:v>6486302</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>51</x:v>
@@ -3324,7 +3393,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>26571545</x:v>
+        <x:v>26676100</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>12</x:v>
@@ -3346,7 +3415,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>1239980</x:v>
+        <x:v>1248620</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>51</x:v>
@@ -3357,7 +3426,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>219149</x:v>
+        <x:v>221309</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>12</x:v>
@@ -3420,7 +3489,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>200842</x:v>
@@ -3431,7 +3500,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>198972</x:v>
@@ -3576,7 +3645,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>1002641</x:v>
+        <x:v>1058333</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -3592,7 +3661,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>31210290</x:v>
+        <x:v>33162402</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
@@ -3608,7 +3677,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>1459129</x:v>
+        <x:v>1469929</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
@@ -3653,7 +3722,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>399814</x:v>
@@ -3751,7 +3820,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>30801</x:v>
+        <x:v>86493</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -3800,13 +3869,13 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>1952112</x:v>
+        <x:v>3904224</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -3833,7 +3902,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>18</x:v>
@@ -3883,7 +3952,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>1459129</x:v>
+        <x:v>1469929</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -3957,7 +4026,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1870</x:v>
@@ -3968,7 +4037,7 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>397944</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -1718,7 +1718,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>1250481</x:v>
+        <x:v>1830265</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>51</x:v>
@@ -1741,7 +1741,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>221309</x:v>
+        <x:v>374487</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -2350,7 +2350,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>1248620</x:v>
+        <x:v>1828404</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>51</x:v>
@@ -2367,7 +2367,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>221309</x:v>
+        <x:v>374487</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>12</x:v>
@@ -2980,7 +2980,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>1248620</x:v>
+        <x:v>1828404</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>51</x:v>
@@ -2994,7 +2994,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>221309</x:v>
+        <x:v>374487</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>12</x:v>
@@ -3415,7 +3415,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>1248620</x:v>
+        <x:v>1828404</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>51</x:v>
@@ -3426,7 +3426,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>221309</x:v>
+        <x:v>374487</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>12</x:v>
@@ -3677,7 +3677,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>1469929</x:v>
+        <x:v>2202891</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
@@ -3952,7 +3952,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>1469929</x:v>
+        <x:v>2202891</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -307,6 +307,9 @@
   </x:si>
   <x:si>
     <x:t>POWELL, DENISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BENNETT, REBECCA</x:t>
   </x:si>
   <x:si>
     <x:t>THOMPSON, MIKE MR.</x:t>
@@ -380,8 +383,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G55" totalsRowShown="0">
-  <x:autoFilter ref="A1:G55"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G56" totalsRowShown="0">
+  <x:autoFilter ref="A1:G56"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -396,8 +399,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E42" totalsRowShown="0">
-  <x:autoFilter ref="A1:E42"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E43" totalsRowShown="0">
+  <x:autoFilter ref="A1:E43"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -410,8 +413,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D37" totalsRowShown="0">
-  <x:autoFilter ref="A1:D37"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D38" totalsRowShown="0">
+  <x:autoFilter ref="A1:D38"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -745,7 +748,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G55"/>
+  <x:dimension ref="A1:G56"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1850,13 +1853,13 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>86493</x:v>
+        <x:v>25305</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>12</x:v>
@@ -1864,22 +1867,22 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>4379246</x:v>
+        <x:v>414981</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -1887,25 +1890,25 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>663879</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
@@ -1916,16 +1919,16 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>1183678</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>51</x:v>
@@ -1939,7 +1942,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
         <x:v>76</x:v>
@@ -1948,30 +1951,30 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>104555</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>3985700</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -1985,16 +1988,16 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>4383749</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -2008,7 +2011,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
         <x:v>76</x:v>
@@ -2017,9 +2020,32 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F55" s="1">
+        <x:v>4383749</x:v>
+      </x:c>
+      <x:c r="G55" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:7">
+      <x:c r="A56" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B56" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C56" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D56" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E56" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F56" s="1">
         <x:v>1426379</x:v>
       </x:c>
-      <x:c r="G55" s="1" t="s">
+      <x:c r="G56" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
@@ -2039,7 +2065,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E42"/>
+  <x:dimension ref="A1:E43"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2069,7 +2095,7 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>55</x:v>
@@ -2078,7 +2104,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="D2" s="1">
-        <x:v>86493</x:v>
+        <x:v>414981</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
         <x:v>12</x:v>
@@ -2596,24 +2622,24 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>2326917</x:v>
+        <x:v>25305</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>24</x:v>
@@ -2622,55 +2648,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>382</x:v>
@@ -2681,10 +2707,10 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>11</x:v>
@@ -2698,50 +2724,50 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="D40" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>382</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>12</x:v>
@@ -2749,18 +2775,35 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:5">
+      <x:c r="A43" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D43" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -2780,7 +2823,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D37"/>
+  <x:dimension ref="A1:D38"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2812,7 +2855,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>86493</x:v>
+        <x:v>414981</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
         <x:v>12</x:v>
@@ -3170,16 +3213,16 @@
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>2326917</x:v>
+        <x:v>25305</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
@@ -3190,46 +3233,46 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>382</x:v>
@@ -3240,7 +3283,7 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>11</x:v>
@@ -3254,41 +3297,41 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>382</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
         <x:v>12</x:v>
@@ -3296,15 +3339,29 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:4">
+      <x:c r="A38" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C38" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -3360,7 +3417,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>58333</x:v>
+        <x:v>386821</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>12</x:v>
@@ -3536,7 +3593,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>408441</x:v>
+        <x:v>433746</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>12</x:v>
@@ -3645,7 +3702,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>1058333</x:v>
+        <x:v>1386821</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -3741,7 +3798,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>5062275</x:v>
+        <x:v>5087580</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
@@ -3820,7 +3877,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>86493</x:v>
+        <x:v>414981</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -4062,7 +4119,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>350000</x:v>
+        <x:v>375305</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -289,6 +289,12 @@
   </x:si>
   <x:si>
     <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VILLEGAS, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
   </x:si>
   <x:si>
     <x:t>CAVANAUGH, JOHN</x:t>
@@ -383,8 +389,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G56" totalsRowShown="0">
-  <x:autoFilter ref="A1:G56"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G57" totalsRowShown="0">
+  <x:autoFilter ref="A1:G57"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -399,8 +405,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E43" totalsRowShown="0">
-  <x:autoFilter ref="A1:E43"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E44" totalsRowShown="0">
+  <x:autoFilter ref="A1:E44"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -413,8 +419,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D38" totalsRowShown="0">
-  <x:autoFilter ref="A1:D38"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D39" totalsRowShown="0">
+  <x:autoFilter ref="A1:D39"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -748,7 +754,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G56"/>
+  <x:dimension ref="A1:G57"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1669,13 +1675,13 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>1870</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>51</x:v>
@@ -1692,13 +1698,13 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="E41" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="F41" s="1">
-        <x:v>1000000</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>51</x:v>
@@ -1706,22 +1712,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>1830265</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>51</x:v>
@@ -1735,7 +1741,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
         <x:v>55</x:v>
@@ -1744,10 +1750,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>374487</x:v>
+        <x:v>1830265</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
@@ -1758,62 +1764,62 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>2326917</x:v>
+        <x:v>374487</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>149773</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>198972</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>12</x:v>
@@ -1827,42 +1833,42 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F47" s="1">
         <x:v>198972</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>25305</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
@@ -1873,16 +1879,16 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>414981</x:v>
+        <x:v>25305</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -1890,22 +1896,22 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>4379246</x:v>
+        <x:v>414981</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>12</x:v>
@@ -1913,25 +1919,25 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>663879</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
@@ -1942,16 +1948,16 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>1183678</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>51</x:v>
@@ -1965,7 +1971,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
         <x:v>76</x:v>
@@ -1974,30 +1980,30 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>104555</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>3985700</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -2011,16 +2017,16 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>4383749</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>12</x:v>
@@ -2034,7 +2040,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
         <x:v>76</x:v>
@@ -2043,9 +2049,32 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F56" s="1">
+        <x:v>4383749</x:v>
+      </x:c>
+      <x:c r="G56" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:7">
+      <x:c r="A57" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B57" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C57" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D57" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E57" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F57" s="1">
         <x:v>1426379</x:v>
       </x:c>
-      <x:c r="G56" s="1" t="s">
+      <x:c r="G57" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
@@ -2065,7 +2094,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E43"/>
+  <x:dimension ref="A1:E44"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2095,7 +2124,7 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>55</x:v>
@@ -2112,67 +2141,67 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="D3" s="1">
-        <x:v>-28160</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="D4" s="1">
-        <x:v>1000000</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D5" s="1">
-        <x:v>382</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>6739071</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>12</x:v>
@@ -2180,24 +2209,24 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>-9678</x:v>
+        <x:v>6739071</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>50</x:v>
@@ -2206,7 +2235,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>59748</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>51</x:v>
@@ -2214,7 +2243,7 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>50</x:v>
@@ -2223,32 +2252,32 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>4968501</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>1327758</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>14</x:v>
@@ -2257,32 +2286,32 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>6879864</x:v>
+        <x:v>1327758</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>2367356</x:v>
+        <x:v>6879864</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>76</x:v>
@@ -2291,7 +2320,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>2741118</x:v>
+        <x:v>2367356</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>51</x:v>
@@ -2299,7 +2328,7 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>76</x:v>
@@ -2308,15 +2337,15 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>209110</x:v>
+        <x:v>2741118</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>76</x:v>
@@ -2325,7 +2354,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>149773</x:v>
+        <x:v>209110</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>12</x:v>
@@ -2333,7 +2362,7 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>76</x:v>
@@ -2342,7 +2371,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>7729781</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>12</x:v>
@@ -2350,33 +2379,33 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>-6917</x:v>
+        <x:v>7729781</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>1828404</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>51</x:v>
@@ -2384,7 +2413,7 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>55</x:v>
@@ -2393,24 +2422,24 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>374487</x:v>
+        <x:v>1828404</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>382</x:v>
+        <x:v>374487</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>12</x:v>
@@ -2418,16 +2447,16 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>2538</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>12</x:v>
@@ -2435,16 +2464,16 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>382</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>12</x:v>
@@ -2452,16 +2481,16 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>12</x:v>
@@ -2469,50 +2498,50 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>2651</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -2520,50 +2549,50 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>938</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>12</x:v>
@@ -2574,13 +2603,13 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>1974</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>12</x:v>
@@ -2588,7 +2617,7 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>38</x:v>
@@ -2597,7 +2626,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>382</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>12</x:v>
@@ -2605,24 +2634,24 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>50</x:v>
@@ -2631,32 +2660,32 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>25305</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>2326917</x:v>
+        <x:v>25305</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>24</x:v>
@@ -2665,55 +2694,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>382</x:v>
@@ -2724,10 +2753,10 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>11</x:v>
@@ -2741,50 +2770,50 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D40" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="D42" s="1">
-        <x:v>382</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>12</x:v>
@@ -2792,18 +2821,35 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:5">
+      <x:c r="A44" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D44" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="E44" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -2823,7 +2869,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D38"/>
+  <x:dimension ref="A1:D39"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2863,55 +2909,55 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>-28160</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>1000000</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>382</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>6739071</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>12</x:v>
@@ -2919,16 +2965,16 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>50070</x:v>
+        <x:v>6739071</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
@@ -2939,24 +2985,24 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>4968501</x:v>
+        <x:v>50070</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>1327758</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
@@ -2967,24 +3013,24 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>6879864</x:v>
+        <x:v>1327758</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>5108474</x:v>
+        <x:v>6879864</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
@@ -2995,35 +3041,35 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>8088664</x:v>
+        <x:v>5108474</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>-6917</x:v>
+        <x:v>8088664</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>1828404</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>51</x:v>
@@ -3037,21 +3083,21 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>374487</x:v>
+        <x:v>1828404</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>382</x:v>
+        <x:v>374487</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>12</x:v>
@@ -3059,13 +3105,13 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>2538</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>12</x:v>
@@ -3073,13 +3119,13 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>382</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
         <x:v>12</x:v>
@@ -3087,13 +3133,13 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
         <x:v>12</x:v>
@@ -3101,41 +3147,41 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>2651</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -3143,16 +3189,16 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
@@ -3160,24 +3206,24 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>938</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
         <x:v>12</x:v>
@@ -3185,13 +3231,13 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>2356</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>12</x:v>
@@ -3199,16 +3245,16 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>2326917</x:v>
+        <x:v>2356</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
@@ -3219,24 +3265,24 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>25305</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>2326917</x:v>
+        <x:v>25305</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
@@ -3247,46 +3293,46 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>382</x:v>
@@ -3297,7 +3343,7 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>11</x:v>
@@ -3311,41 +3357,41 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>382</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
         <x:v>12</x:v>
@@ -3353,15 +3399,29 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:4">
+      <x:c r="A39" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C39" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -3406,7 +3466,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>1000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
         <x:v>51</x:v>
@@ -3546,7 +3606,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>200842</x:v>
@@ -3557,7 +3617,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>198972</x:v>
@@ -3702,7 +3762,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>1386821</x:v>
+        <x:v>2386821</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -3779,7 +3839,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>399814</x:v>
@@ -3888,7 +3948,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>1000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
@@ -4083,7 +4143,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1870</x:v>
@@ -4094,7 +4154,7 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>397944</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -136,6 +136,9 @@
   </x:si>
   <x:si>
     <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAINS, JASMEET</x:t>
   </x:si>
   <x:si>
     <x:t>FINE, LAURA</x:t>
@@ -266,8 +269,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G25" totalsRowShown="0">
-  <x:autoFilter ref="A1:G25"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G26" totalsRowShown="0">
+  <x:autoFilter ref="A1:G26"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -282,8 +285,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E22" totalsRowShown="0">
-  <x:autoFilter ref="A1:E22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E23" totalsRowShown="0">
+  <x:autoFilter ref="A1:E23"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -296,8 +299,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D19" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D20" totalsRowShown="0">
+  <x:autoFilter ref="A1:D20"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -332,8 +335,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C16" totalsRowShown="0">
-  <x:autoFilter ref="A1:C16"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C17" totalsRowShown="0">
+  <x:autoFilter ref="A1:C17"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -631,7 +634,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G25"/>
+  <x:dimension ref="A1:G26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -908,13 +911,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>500346</x:v>
+        <x:v>30683</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>19</x:v>
@@ -931,13 +934,13 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>198972</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>19</x:v>
@@ -951,7 +954,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>14</x:v>
@@ -963,50 +966,50 @@
         <x:v>198972</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>600000</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="F16" s="1">
-        <x:v>50710</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>19</x:v>
@@ -1014,22 +1017,22 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>350000</x:v>
+        <x:v>50710</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>19</x:v>
@@ -1037,22 +1040,22 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>414981</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>19</x:v>
@@ -1060,22 +1063,22 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B19" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C19" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>4379246</x:v>
+        <x:v>414981</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>19</x:v>
@@ -1083,45 +1086,45 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B20" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C20" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>663879</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>1183678</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>12</x:v>
@@ -1129,10 +1132,10 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>55</x:v>
@@ -1144,30 +1147,30 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>104555</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B23" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C23" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>3985700</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>19</x:v>
@@ -1175,22 +1178,22 @@
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>4383749</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>19</x:v>
@@ -1198,13 +1201,13 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
         <x:v>36</x:v>
@@ -1213,9 +1216,32 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="F25" s="1">
+        <x:v>4383749</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:7">
+      <x:c r="A26" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F26" s="1">
         <x:v>1426379</x:v>
       </x:c>
-      <x:c r="G25" s="1" t="s">
+      <x:c r="G26" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -1235,7 +1261,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E22"/>
+  <x:dimension ref="A1:E23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1265,7 +1291,7 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>25</x:v>
@@ -1299,58 +1325,58 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D4" s="1">
-        <x:v>1500000</x:v>
+        <x:v>30683</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D5" s="1">
-        <x:v>4379246</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>59748</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>28</x:v>
@@ -1359,66 +1385,66 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>4968502</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>663879</x:v>
+        <x:v>4968502</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>3985700</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>1183678</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>36</x:v>
@@ -1427,7 +1453,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>1426379</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>12</x:v>
@@ -1435,7 +1461,7 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>36</x:v>
@@ -1444,15 +1470,15 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>104555</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>36</x:v>
@@ -1461,7 +1487,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>149773</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>19</x:v>
@@ -1469,7 +1495,7 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>36</x:v>
@@ -1478,7 +1504,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>4884095</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>19</x:v>
@@ -1486,24 +1512,24 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>1830265</x:v>
+        <x:v>4884095</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>25</x:v>
@@ -1512,24 +1538,24 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>374487</x:v>
+        <x:v>1830265</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>600000</x:v>
+        <x:v>374487</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>19</x:v>
@@ -1537,24 +1563,24 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>14</x:v>
@@ -1563,32 +1589,32 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>2326917</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>28</x:v>
@@ -1597,26 +1623,43 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>50710</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D22" s="1">
+        <x:v>50710</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:5">
+      <x:c r="A23" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D23" s="1">
         <x:v>388952</x:v>
       </x:c>
-      <x:c r="E22" s="1" t="s">
+      <x:c r="E23" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
@@ -1636,7 +1679,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D19"/>
+  <x:dimension ref="A1:D20"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1690,44 +1733,44 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>1500000</x:v>
+        <x:v>30683</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>4379246</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>59748</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
@@ -1738,52 +1781,52 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>4968502</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>663879</x:v>
+        <x:v>4968502</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>3985700</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>2610057</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
@@ -1794,24 +1837,24 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>5138423</x:v>
+        <x:v>2610057</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>1830265</x:v>
+        <x:v>5138423</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
@@ -1822,10 +1865,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>374487</x:v>
+        <x:v>1830265</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
@@ -1833,10 +1876,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>600000</x:v>
+        <x:v>374487</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>19</x:v>
@@ -1844,16 +1887,16 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
@@ -1864,24 +1907,24 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>2326917</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
@@ -1892,23 +1935,37 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>50710</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C19" s="1">
+        <x:v>50710</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:4">
+      <x:c r="A20" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C20" s="1">
         <x:v>388952</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
+      <x:c r="D20" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
@@ -1964,7 +2021,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>414981</x:v>
+        <x:v>445664</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>19</x:v>
@@ -2016,7 +2073,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>600000</x:v>
@@ -2106,7 +2163,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>2414981</x:v>
+        <x:v>2445664</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -2127,7 +2184,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>600000</x:v>
@@ -2165,7 +2222,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C16"/>
+  <x:dimension ref="A1:C17"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2187,7 +2244,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>11</x:v>
@@ -2209,68 +2266,68 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>4379246</x:v>
+        <x:v>30683</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>1952112</x:v>
+        <x:v>4379246</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>500346</x:v>
+        <x:v>1952112</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>9795828</x:v>
+        <x:v>500346</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>149773</x:v>
+        <x:v>9795828</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>5028250</x:v>
+        <x:v>149773</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -2278,75 +2335,86 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>2204752</x:v>
+        <x:v>5028250</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>600000</x:v>
+        <x:v>2204752</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>1870</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>397944</x:v>
+        <x:v>1870</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>400710</x:v>
+        <x:v>397944</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>38952</x:v>
+        <x:v>400710</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C16" s="1">
+        <x:v>38952</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:3">
+      <x:c r="A17" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C17" s="1">
         <x:v>2326917</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -79,6 +79,15 @@
   </x:si>
   <x:si>
     <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARCIA, JOHNNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
   </x:si>
   <x:si>
     <x:t>CAMPA-NAJJAR, AMMAR</x:t>
@@ -269,8 +278,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G26" totalsRowShown="0">
-  <x:autoFilter ref="A1:G26"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G27" totalsRowShown="0">
+  <x:autoFilter ref="A1:G27"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -285,8 +294,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E23" totalsRowShown="0">
-  <x:autoFilter ref="A1:E23"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E24" totalsRowShown="0">
+  <x:autoFilter ref="A1:E24"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -299,8 +308,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D20" totalsRowShown="0">
-  <x:autoFilter ref="A1:D20"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D21" totalsRowShown="0">
+  <x:autoFilter ref="A1:D21"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -312,8 +321,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C12" totalsRowShown="0">
-  <x:autoFilter ref="A1:C12"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C13" totalsRowShown="0">
+  <x:autoFilter ref="A1:C13"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -324,8 +333,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B7" totalsRowShown="0">
-  <x:autoFilter ref="A1:B7"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B8" totalsRowShown="0">
+  <x:autoFilter ref="A1:B8"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -335,8 +344,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C17" totalsRowShown="0">
-  <x:autoFilter ref="A1:C17"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C18" totalsRowShown="0">
+  <x:autoFilter ref="A1:C18"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -634,7 +643,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G26"/>
+  <x:dimension ref="A1:G27"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -753,33 +762,33 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>1500000</x:v>
+        <x:v>43455</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>1830265</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
         <x:v>12</x:v>
@@ -787,10 +796,10 @@
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>27</x:v>
@@ -802,122 +811,122 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>4968502</x:v>
+        <x:v>2618033</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>59748</x:v>
+        <x:v>4968502</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>374487</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>2326917</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>149773</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B12" s="1" t="s">
+      <x:c r="C12" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C12" s="1" t="s">
+      <x:c r="D12" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>30683</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>19</x:v>
@@ -925,22 +934,22 @@
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>500346</x:v>
+        <x:v>30683</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>19</x:v>
@@ -948,22 +957,22 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>198972</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>19</x:v>
@@ -971,13 +980,13 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>14</x:v>
@@ -989,50 +998,50 @@
         <x:v>198972</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>600000</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>50710</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>19</x:v>
@@ -1040,22 +1049,22 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>350000</x:v>
+        <x:v>50710</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>19</x:v>
@@ -1063,22 +1072,22 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>414981</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>19</x:v>
@@ -1086,22 +1095,22 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>4379246</x:v>
+        <x:v>414981</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>19</x:v>
@@ -1118,36 +1127,36 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>663879</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>1183678</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>12</x:v>
@@ -1155,45 +1164,45 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>104555</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>3985700</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>19</x:v>
@@ -1201,22 +1210,22 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B25" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>4383749</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>19</x:v>
@@ -1224,24 +1233,47 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F26" s="1">
+        <x:v>4383749</x:v>
+      </x:c>
+      <x:c r="G26" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:7">
+      <x:c r="A27" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F27" s="1">
         <x:v>1426379</x:v>
       </x:c>
-      <x:c r="G26" s="1" t="s">
+      <x:c r="G27" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -1261,7 +1293,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E23"/>
+  <x:dimension ref="A1:E24"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1291,10 +1323,10 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
         <x:v>11</x:v>
@@ -1325,7 +1357,7 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>10</x:v>
@@ -1342,10 +1374,10 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>11</x:v>
@@ -1359,13 +1391,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>4379246</x:v>
@@ -1376,13 +1408,13 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>59748</x:v>
@@ -1393,13 +1425,13 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>4968502</x:v>
@@ -1410,13 +1442,13 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>663879</x:v>
@@ -1427,13 +1459,13 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>3985700</x:v>
@@ -1444,13 +1476,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>1183678</x:v>
@@ -1461,13 +1493,13 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>1426379</x:v>
@@ -1478,13 +1510,13 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>104555</x:v>
@@ -1495,13 +1527,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>149773</x:v>
@@ -1512,13 +1544,13 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>4884095</x:v>
@@ -1529,16 +1561,16 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>1830265</x:v>
+        <x:v>2618033</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>12</x:v>
@@ -1546,16 +1578,16 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>374487</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>19</x:v>
@@ -1563,13 +1595,13 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>600000</x:v>
@@ -1597,7 +1629,7 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>14</x:v>
@@ -1614,10 +1646,10 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>18</x:v>
@@ -1631,10 +1663,10 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>18</x:v>
@@ -1660,6 +1692,23 @@
         <x:v>388952</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:5">
+      <x:c r="A24" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D24" s="1">
+        <x:v>43455</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
@@ -1679,7 +1728,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D20"/>
+  <x:dimension ref="A1:D21"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1705,7 +1754,7 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>11</x:v>
@@ -1747,7 +1796,7 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>11</x:v>
@@ -1764,7 +1813,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>4379246</x:v>
@@ -1775,10 +1824,10 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>59748</x:v>
@@ -1789,10 +1838,10 @@
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>4968502</x:v>
@@ -1803,10 +1852,10 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>663879</x:v>
@@ -1817,10 +1866,10 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>3985700</x:v>
@@ -1831,10 +1880,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>2610057</x:v>
@@ -1845,10 +1894,10 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>5138423</x:v>
@@ -1859,13 +1908,13 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>1830265</x:v>
+        <x:v>2618033</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>12</x:v>
@@ -1873,13 +1922,13 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>374487</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>19</x:v>
@@ -1887,10 +1936,10 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>600000</x:v>
@@ -1929,7 +1978,7 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>18</x:v>
@@ -1943,7 +1992,7 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>18</x:v>
@@ -1966,6 +2015,20 @@
         <x:v>388952</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:4">
+      <x:c r="A21" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C21" s="1">
+        <x:v>43455</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
@@ -1985,7 +2048,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C12"/>
+  <x:dimension ref="A1:C13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2029,7 +2092,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>3333684</x:v>
@@ -2040,7 +2103,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>18471871</x:v>
@@ -2051,10 +2114,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>1830265</x:v>
+        <x:v>2618033</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>12</x:v>
@@ -2062,10 +2125,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>374487</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>19</x:v>
@@ -2073,7 +2136,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>600000</x:v>
@@ -2123,6 +2186,17 @@
         <x:v>439662</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:3">
+      <x:c r="A13" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B13" s="1">
+        <x:v>43455</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
@@ -2142,7 +2216,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B7"/>
+  <x:dimension ref="A1:B8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2168,7 +2242,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>21805555</x:v>
@@ -2176,15 +2250,15 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>2204752</x:v>
+        <x:v>3197352</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>600000</x:v>
@@ -2204,6 +2278,14 @@
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2766579</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:2">
+      <x:c r="A8" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B8" s="1">
+        <x:v>43455</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2222,7 +2304,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C17"/>
+  <x:dimension ref="A1:C18"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2244,7 +2326,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>11</x:v>
@@ -2266,7 +2348,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>11</x:v>
@@ -2277,10 +2359,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>4379246</x:v>
@@ -2288,10 +2370,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>1952112</x:v>
@@ -2299,10 +2381,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>500346</x:v>
@@ -2310,10 +2392,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>9795828</x:v>
@@ -2321,10 +2403,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>149773</x:v>
@@ -2332,10 +2414,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>5028250</x:v>
@@ -2343,21 +2425,21 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>2204752</x:v>
+        <x:v>3197352</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>600000</x:v>
@@ -2376,7 +2458,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>15</x:v>
@@ -2387,7 +2469,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>18</x:v>
@@ -2409,13 +2491,24 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>2326917</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:3">
+      <x:c r="A18" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C18" s="1">
+        <x:v>43455</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -145,6 +145,12 @@
   </x:si>
   <x:si>
     <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BABB TOMLINSON, LAUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
   </x:si>
   <x:si>
     <x:t>BAINS, JASMEET</x:t>
@@ -278,8 +284,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G27" totalsRowShown="0">
-  <x:autoFilter ref="A1:G27"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G28" totalsRowShown="0">
+  <x:autoFilter ref="A1:G28"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -294,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E24" totalsRowShown="0">
-  <x:autoFilter ref="A1:E24"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E25" totalsRowShown="0">
+  <x:autoFilter ref="A1:E25"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -308,8 +314,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D21" totalsRowShown="0">
-  <x:autoFilter ref="A1:D21"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D22" totalsRowShown="0">
+  <x:autoFilter ref="A1:D22"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -643,7 +649,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G27"/>
+  <x:dimension ref="A1:G28"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -943,13 +949,13 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>30683</x:v>
+        <x:v>15206</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>19</x:v>
@@ -963,16 +969,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>500346</x:v>
+        <x:v>61446</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>19</x:v>
@@ -986,16 +992,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>198972</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>19</x:v>
@@ -1009,7 +1015,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>14</x:v>
@@ -1021,50 +1027,50 @@
         <x:v>198972</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>600000</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>50710</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>19</x:v>
@@ -1072,22 +1078,22 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>350000</x:v>
+        <x:v>140153</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>19</x:v>
@@ -1095,22 +1101,22 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>414981</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>19</x:v>
@@ -1118,22 +1124,22 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C21" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>4379246</x:v>
+        <x:v>443469</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>19</x:v>
@@ -1141,45 +1147,45 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B22" s="1" t="s">
+      <x:c r="C22" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="C22" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>663879</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>1183678</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>12</x:v>
@@ -1187,13 +1193,13 @@
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>39</x:v>
@@ -1202,30 +1208,30 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>104555</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>3985700</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>19</x:v>
@@ -1233,22 +1239,22 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>4383749</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>19</x:v>
@@ -1256,13 +1262,13 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>39</x:v>
@@ -1271,9 +1277,32 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F27" s="1">
+        <x:v>4383749</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:7">
+      <x:c r="A28" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F28" s="1">
         <x:v>1426379</x:v>
       </x:c>
-      <x:c r="G27" s="1" t="s">
+      <x:c r="G28" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -1293,7 +1322,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E24"/>
+  <x:dimension ref="A1:E25"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1323,7 +1352,7 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>28</x:v>
@@ -1332,7 +1361,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D2" s="1">
-        <x:v>414981</x:v>
+        <x:v>443469</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
         <x:v>19</x:v>
@@ -1340,24 +1369,24 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D3" s="1">
-        <x:v>500000</x:v>
+        <x:v>15206</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>10</x:v>
@@ -1366,66 +1395,66 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D4" s="1">
-        <x:v>30683</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D5" s="1">
-        <x:v>1500000</x:v>
+        <x:v>61446</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>4379246</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>59748</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>31</x:v>
@@ -1434,66 +1463,66 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>4968502</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>663879</x:v>
+        <x:v>4968502</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>3985700</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>1183678</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>39</x:v>
@@ -1502,7 +1531,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>1426379</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>12</x:v>
@@ -1510,7 +1539,7 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>39</x:v>
@@ -1519,15 +1548,15 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>104555</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>39</x:v>
@@ -1536,7 +1565,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>149773</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>19</x:v>
@@ -1544,7 +1573,7 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>39</x:v>
@@ -1553,7 +1582,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>4884095</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>19</x:v>
@@ -1561,24 +1590,24 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>2618033</x:v>
+        <x:v>4884095</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>28</x:v>
@@ -1587,24 +1616,24 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>579319</x:v>
+        <x:v>2618033</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>600000</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>19</x:v>
@@ -1612,24 +1641,24 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>14</x:v>
@@ -1638,32 +1667,32 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>2326917</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>31</x:v>
@@ -1672,24 +1701,24 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>50710</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>388952</x:v>
+        <x:v>140153</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>19</x:v>
@@ -1697,18 +1726,35 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D24" s="1">
+        <x:v>388952</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:5">
+      <x:c r="A25" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B24" s="1" t="s">
+      <x:c r="B25" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C24" s="1" t="s">
+      <x:c r="C25" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D24" s="1">
+      <x:c r="D25" s="1">
         <x:v>43455</x:v>
       </x:c>
-      <x:c r="E24" s="1" t="s">
+      <x:c r="E25" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
@@ -1728,7 +1774,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D21"/>
+  <x:dimension ref="A1:D22"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1760,7 +1806,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>414981</x:v>
+        <x:v>443469</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
         <x:v>19</x:v>
@@ -1768,16 +1814,16 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>500000</x:v>
+        <x:v>15206</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
@@ -1788,52 +1834,52 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>30683</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>1500000</x:v>
+        <x:v>61446</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>4379246</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>59748</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
@@ -1844,52 +1890,52 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>4968502</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>663879</x:v>
+        <x:v>4968502</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>3985700</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>2610057</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
@@ -1900,24 +1946,24 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>5138423</x:v>
+        <x:v>2610057</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>2618033</x:v>
+        <x:v>5138423</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
@@ -1928,10 +1974,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>579319</x:v>
+        <x:v>2618033</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
@@ -1939,10 +1985,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>600000</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>19</x:v>
@@ -1950,16 +1996,16 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
@@ -1970,24 +2016,24 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>2326917</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
@@ -1998,21 +2044,21 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>50710</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>388952</x:v>
+        <x:v>140153</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>19</x:v>
@@ -2020,15 +2066,29 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C21" s="1">
+        <x:v>388952</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:4">
+      <x:c r="A22" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B21" s="1" t="s">
+      <x:c r="B22" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C21" s="1">
+      <x:c r="C22" s="1">
         <x:v>43455</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
+      <x:c r="D22" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
@@ -2084,7 +2144,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>445664</x:v>
+        <x:v>520121</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>19</x:v>
@@ -2136,7 +2196,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>600000</x:v>
@@ -2183,7 +2243,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>439662</x:v>
+        <x:v>529105</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>19</x:v>
@@ -2237,7 +2297,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>2445664</x:v>
+        <x:v>2520121</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -2258,7 +2318,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>600000</x:v>
@@ -2277,7 +2337,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>2766579</x:v>
+        <x:v>2856022</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -2326,13 +2386,13 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>414981</x:v>
+        <x:v>443469</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -2354,12 +2414,12 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>30683</x:v>
+        <x:v>76652</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>32</x:v>
@@ -2370,7 +2430,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>32</x:v>
@@ -2392,7 +2452,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>32</x:v>
@@ -2436,10 +2496,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>600000</x:v>
@@ -2469,13 +2529,13 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>400710</x:v>
+        <x:v>490153</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -771,7 +771,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>43455</x:v>
+        <x:v>87010</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>19</x:v>
@@ -817,7 +817,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>2618033</x:v>
+        <x:v>3576967</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>12</x:v>
@@ -1616,7 +1616,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>2618033</x:v>
+        <x:v>3576967</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>12</x:v>
@@ -1752,7 +1752,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>43455</x:v>
+        <x:v>87010</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>19</x:v>
@@ -1974,7 +1974,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>2618033</x:v>
+        <x:v>3576967</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>12</x:v>
@@ -2086,7 +2086,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>43455</x:v>
+        <x:v>87010</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>19</x:v>
@@ -2177,7 +2177,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>2618033</x:v>
+        <x:v>3576967</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>12</x:v>
@@ -2254,7 +2254,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>43455</x:v>
+        <x:v>87010</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>19</x:v>
@@ -2313,7 +2313,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>3197352</x:v>
+        <x:v>4156286</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
@@ -2345,7 +2345,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>43455</x:v>
+        <x:v>87010</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2491,7 +2491,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>3197352</x:v>
+        <x:v>4156286</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -2568,7 +2568,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>43455</x:v>
+        <x:v>87010</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -48,172 +48,286 @@
     <x:t>DMFI PAC</x:t>
   </x:si>
   <x:si>
+    <x:t>STELSON, JANELLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIRD, SHANNON KATHLEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLER, DONNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOSS, JEREMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAY, TAHESHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONLEY, CAIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COGNETTI, PAIGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARCIA, JOHNNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LURIA, ELAINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SULLIVAN, MAURA CORBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPPAS, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEVENS, HALEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRAIG, ANGIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COOPER, ROY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00799031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, KINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOWMAN, JAMAAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MASSIE, THOMAS H.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOSTETTLER, JOHN N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERRERA, BRANDON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIEDMAN, JASON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALINOWSKI, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOMEZ, JIMMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUSH, CORI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CISNEROS, JESSICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FOUSHEE, VALERIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHMED, JUNAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMIWALA, BUSHRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00936724</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BABB TOMLINSON, LAUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
     <x:t>VILLEGAS, RANDY</x:t>
   </x:si>
   <x:si>
     <x:t>22</x:t>
   </x:si>
   <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
+    <x:t>BAINS, JASMEET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POWELL, DENISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
   </x:si>
   <x:si>
     <x:t>CAVANAUGH, JOHN</x:t>
   </x:si>
   <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAY, TAHESHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARCIA, JOHNNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
+    <x:t>BENNETT, REBECCA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THOMPSON, MIKE MR.</x:t>
   </x:si>
   <x:si>
     <x:t>CAMPA-NAJJAR, AMMAR</x:t>
   </x:si>
   <x:si>
     <x:t>48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00799031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MASSIE, THOMAS H.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIEDMAN, JASON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALLREIN, ED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MALINOWSKI, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BISS, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BABB TOMLINSON, LAUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAINS, JASMEET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POWELL, DENISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FOUSHEE, VALERIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BENNETT, REBECCA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THOMPSON, MIKE MR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935809</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHMED, JUNAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMIWALA, BUSHRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00936724</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -284,8 +398,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G28" totalsRowShown="0">
-  <x:autoFilter ref="A1:G28"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G60" totalsRowShown="0">
+  <x:autoFilter ref="A1:G60"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -300,8 +414,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E25" totalsRowShown="0">
-  <x:autoFilter ref="A1:E25"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E46" totalsRowShown="0">
+  <x:autoFilter ref="A1:E46"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -314,8 +428,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D22" totalsRowShown="0">
-  <x:autoFilter ref="A1:D22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D41" totalsRowShown="0">
+  <x:autoFilter ref="A1:D41"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -327,8 +441,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C13" totalsRowShown="0">
-  <x:autoFilter ref="A1:C13"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C25" totalsRowShown="0">
+  <x:autoFilter ref="A1:C25"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -339,8 +453,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B8" totalsRowShown="0">
-  <x:autoFilter ref="A1:B8"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B18" totalsRowShown="0">
+  <x:autoFilter ref="A1:B18"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -350,8 +464,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C18" totalsRowShown="0">
-  <x:autoFilter ref="A1:C18"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C34" totalsRowShown="0">
+  <x:autoFilter ref="A1:C34"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -649,7 +763,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G28"/>
+  <x:dimension ref="A1:G60"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -702,7 +816,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>500000</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -725,7 +839,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>1870</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -748,10 +862,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>38952</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
@@ -762,19 +876,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>87010</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
@@ -785,16 +899,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>1500000</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
         <x:v>12</x:v>
@@ -802,22 +916,22 @@
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B7" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C7" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="F7" s="1">
-        <x:v>3576967</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>12</x:v>
@@ -825,45 +939,45 @@
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>4968502</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>59748</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>12</x:v>
@@ -871,45 +985,45 @@
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>579319</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
         <x:v>12</x:v>
@@ -917,137 +1031,137 @@
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B12" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C12" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="F12" s="1">
-        <x:v>149773</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>15206</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>61446</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>500346</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>198972</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>198972</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1055,25 +1169,25 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>600000</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
@@ -1084,19 +1198,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>140153</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
@@ -1107,19 +1221,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>350000</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
@@ -1130,180 +1244,916 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>443469</x:v>
+        <x:v>-1861</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>4379246</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="F23" s="1">
-        <x:v>663879</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>1183678</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>104555</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C26" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>3985700</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>4383749</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F28" s="1">
+        <x:v>-22643</x:v>
+      </x:c>
+      <x:c r="G28" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:7">
+      <x:c r="A29" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F29" s="1">
+        <x:v>39386</x:v>
+      </x:c>
+      <x:c r="G29" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:7">
+      <x:c r="A30" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F30" s="1">
+        <x:v>500346</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:7">
+      <x:c r="A31" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F31" s="1">
+        <x:v>600000</x:v>
+      </x:c>
+      <x:c r="G31" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:7">
+      <x:c r="A32" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F32" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="G32" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:7">
+      <x:c r="A33" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F33" s="1">
+        <x:v>2359443</x:v>
+      </x:c>
+      <x:c r="G33" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:7">
+      <x:c r="A34" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E34" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F34" s="1">
+        <x:v>663879</x:v>
+      </x:c>
+      <x:c r="G34" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:7">
+      <x:c r="A35" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E35" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F35" s="1">
+        <x:v>1183678</x:v>
+      </x:c>
+      <x:c r="G35" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:7">
+      <x:c r="A36" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F36" s="1">
+        <x:v>104555</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:7">
+      <x:c r="A37" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F37" s="1">
+        <x:v>2893782</x:v>
+      </x:c>
+      <x:c r="G37" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:7">
+      <x:c r="A38" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F38" s="1">
+        <x:v>2845686</x:v>
+      </x:c>
+      <x:c r="G38" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:7">
+      <x:c r="A39" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E39" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F39" s="1">
+        <x:v>1314739</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:7">
+      <x:c r="A40" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F40" s="1">
+        <x:v>663879</x:v>
+      </x:c>
+      <x:c r="G40" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:7">
+      <x:c r="A41" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F41" s="1">
+        <x:v>3576967</x:v>
+      </x:c>
+      <x:c r="G41" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:7">
+      <x:c r="A42" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B42" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E42" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F42" s="1">
+        <x:v>15206</x:v>
+      </x:c>
+      <x:c r="G42" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:7">
+      <x:c r="A43" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F43" s="1">
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="G43" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:7">
+      <x:c r="A44" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="E44" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F44" s="1">
+        <x:v>61446</x:v>
+      </x:c>
+      <x:c r="G44" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:7">
+      <x:c r="A45" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E45" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F45" s="1">
+        <x:v>4379246</x:v>
+      </x:c>
+      <x:c r="G45" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:7">
+      <x:c r="A46" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F46" s="1">
+        <x:v>3985700</x:v>
+      </x:c>
+      <x:c r="G46" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:7">
+      <x:c r="A47" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B47" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C47" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E47" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F47" s="1">
+        <x:v>1183678</x:v>
+      </x:c>
+      <x:c r="G47" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:7">
+      <x:c r="A48" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F48" s="1">
+        <x:v>4383749</x:v>
+      </x:c>
+      <x:c r="G48" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:7">
+      <x:c r="A49" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E49" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F49" s="1">
+        <x:v>149773</x:v>
+      </x:c>
+      <x:c r="G49" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:7">
+      <x:c r="A50" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F50" s="1">
+        <x:v>1426379</x:v>
+      </x:c>
+      <x:c r="G50" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:7">
+      <x:c r="A51" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B51" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C51" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D51" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E51" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F51" s="1">
+        <x:v>104555</x:v>
+      </x:c>
+      <x:c r="G51" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:7">
+      <x:c r="A52" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B52" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C52" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F52" s="1">
+        <x:v>579319</x:v>
+      </x:c>
+      <x:c r="G52" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:7">
+      <x:c r="A53" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B53" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C53" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D53" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E53" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F53" s="1">
+        <x:v>198972</x:v>
+      </x:c>
+      <x:c r="G53" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:7">
+      <x:c r="A54" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B54" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C54" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D54" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E54" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F54" s="1">
+        <x:v>1870</x:v>
+      </x:c>
+      <x:c r="G54" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:7">
+      <x:c r="A55" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B55" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C55" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D55" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E55" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F55" s="1">
+        <x:v>198972</x:v>
+      </x:c>
+      <x:c r="G55" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:7">
+      <x:c r="A56" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B56" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C56" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D56" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E56" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F56" s="1">
+        <x:v>165658</x:v>
+      </x:c>
+      <x:c r="G56" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:7">
+      <x:c r="A57" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B57" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C57" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D57" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E57" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F57" s="1">
+        <x:v>87010</x:v>
+      </x:c>
+      <x:c r="G57" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:7">
+      <x:c r="A58" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B58" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C58" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D58" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E58" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F58" s="1">
+        <x:v>499161</x:v>
+      </x:c>
+      <x:c r="G58" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:7">
+      <x:c r="A59" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B59" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C59" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D59" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="E59" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F59" s="1">
+        <x:v>1500000</x:v>
+      </x:c>
+      <x:c r="G59" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:7">
+      <x:c r="A60" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B60" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C60" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C28" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F28" s="1">
-        <x:v>1426379</x:v>
-      </x:c>
-      <x:c r="G28" s="1" t="s">
-        <x:v>12</x:v>
+      <x:c r="D60" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E60" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F60" s="1">
+        <x:v>2326917</x:v>
+      </x:c>
+      <x:c r="G60" s="1" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1322,7 +2172,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E25"/>
+  <x:dimension ref="A1:E46"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1352,84 +2202,84 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D2" s="1">
-        <x:v>443469</x:v>
+        <x:v>499161</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>15206</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>61446</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>1500000</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>12</x:v>
@@ -1437,33 +2287,33 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>4379246</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>59748</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>12</x:v>
@@ -1471,67 +2321,67 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>4968502</x:v>
+        <x:v>6739071</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>663879</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>3985700</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>1183678</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>12</x:v>
@@ -1539,84 +2389,84 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>1426379</x:v>
+        <x:v>1327758</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>104555</x:v>
+        <x:v>6879864</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>149773</x:v>
+        <x:v>2367356</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>4884095</x:v>
+        <x:v>2741118</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>3576967</x:v>
+        <x:v>209110</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>12</x:v>
@@ -1624,84 +2474,84 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>579319</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>600000</x:v>
+        <x:v>7729781</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>200842</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>198972</x:v>
+        <x:v>3575106</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>2326917</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>12</x:v>
@@ -1709,53 +2559,410 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>140153</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>388952</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>87010</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:5">
+      <x:c r="A26" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D26" s="1">
+        <x:v>2649</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:5">
+      <x:c r="A27" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D27" s="1">
+        <x:v>-22643</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:5">
+      <x:c r="A28" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D28" s="1">
+        <x:v>2651</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:5">
+      <x:c r="A29" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D29" s="1">
+        <x:v>600000</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:5">
+      <x:c r="A30" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D30" s="1">
+        <x:v>200842</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:5">
+      <x:c r="A31" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D31" s="1">
+        <x:v>198972</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:5">
+      <x:c r="A32" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D32" s="1">
+        <x:v>938</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:5">
+      <x:c r="A33" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D33" s="1">
+        <x:v>1974</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:5">
+      <x:c r="A34" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D34" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="E34" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:5">
+      <x:c r="A35" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D35" s="1">
+        <x:v>2326917</x:v>
+      </x:c>
+      <x:c r="E35" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:5">
+      <x:c r="A36" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D36" s="1">
+        <x:v>165658</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:5">
+      <x:c r="A37" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D37" s="1">
+        <x:v>2326917</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:5">
+      <x:c r="A38" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D38" s="1">
+        <x:v>408441</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:5">
+      <x:c r="A39" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D39" s="1">
+        <x:v>-31053</x:v>
+      </x:c>
+      <x:c r="E39" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:5">
+      <x:c r="A40" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D40" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:5">
+      <x:c r="A41" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D41" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:5">
+      <x:c r="A42" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B42" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D42" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="E42" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:5">
+      <x:c r="A43" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D43" s="1">
+        <x:v>-46</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:5">
+      <x:c r="A44" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D44" s="1">
+        <x:v>39386</x:v>
+      </x:c>
+      <x:c r="E44" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:5">
+      <x:c r="A45" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D45" s="1">
+        <x:v>87392</x:v>
+      </x:c>
+      <x:c r="E45" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:5">
+      <x:c r="A46" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D46" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1774,7 +2981,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D22"/>
+  <x:dimension ref="A1:D41"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1800,69 +3007,69 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>443469</x:v>
+        <x:v>499161</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>15206</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>61446</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>1500000</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>12</x:v>
@@ -1870,27 +3077,27 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>4379246</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>59748</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>12</x:v>
@@ -1898,153 +3105,153 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>4968502</x:v>
+        <x:v>6739071</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>663879</x:v>
+        <x:v>50070</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>3985700</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>2610057</x:v>
+        <x:v>1327758</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>5138423</x:v>
+        <x:v>6879864</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>3576967</x:v>
+        <x:v>5108474</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>579319</x:v>
+        <x:v>8088664</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>600000</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>200842</x:v>
+        <x:v>3575106</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>198972</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
         <x:v>12</x:v>
@@ -2052,44 +3259,310 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>140153</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>388952</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>87010</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:4">
+      <x:c r="A23" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C23" s="1">
+        <x:v>-22643</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:4">
+      <x:c r="A24" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C24" s="1">
+        <x:v>2651</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:4">
+      <x:c r="A25" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C25" s="1">
+        <x:v>600000</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:4">
+      <x:c r="A26" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C26" s="1">
+        <x:v>200842</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:4">
+      <x:c r="A27" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C27" s="1">
+        <x:v>198972</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:4">
+      <x:c r="A28" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C28" s="1">
+        <x:v>938</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:4">
+      <x:c r="A29" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C29" s="1">
+        <x:v>2356</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:4">
+      <x:c r="A30" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C30" s="1">
+        <x:v>2326917</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:4">
+      <x:c r="A31" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C31" s="1">
+        <x:v>165658</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:4">
+      <x:c r="A32" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C32" s="1">
+        <x:v>2326917</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:4">
+      <x:c r="A33" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C33" s="1">
+        <x:v>408441</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:4">
+      <x:c r="A34" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C34" s="1">
+        <x:v>-31053</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:4">
+      <x:c r="A35" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C35" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:4">
+      <x:c r="A36" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C36" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:4">
+      <x:c r="A37" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C37" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:4">
+      <x:c r="A38" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C38" s="1">
+        <x:v>-46</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:4">
+      <x:c r="A39" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C39" s="1">
+        <x:v>39386</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:4">
+      <x:c r="A40" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C40" s="1">
+        <x:v>87392</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:4">
+      <x:c r="A41" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C41" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2108,7 +3581,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C13"/>
+  <x:dimension ref="A1:C25"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2130,32 +3603,32 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>520121</x:v>
+        <x:v>547653</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>3333684</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>12</x:v>
@@ -2163,21 +3636,21 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>18471871</x:v>
+        <x:v>6486302</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>3576967</x:v>
+        <x:v>26676100</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>12</x:v>
@@ -2185,32 +3658,32 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>579319</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>600000</x:v>
+        <x:v>3575106</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>200842</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>12</x:v>
@@ -2218,21 +3691,21 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>198972</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>2326917</x:v>
+        <x:v>2920</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -2240,24 +3713,156 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>529105</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>87010</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:3">
+      <x:c r="A14" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B14" s="1">
+        <x:v>602651</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:3">
+      <x:c r="A15" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B15" s="1">
+        <x:v>200842</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:3">
+      <x:c r="A16" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B16" s="1">
+        <x:v>198972</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:3">
+      <x:c r="A17" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B17" s="1">
+        <x:v>3294</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:3">
+      <x:c r="A18" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B18" s="1">
+        <x:v>4653834</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:3">
+      <x:c r="A19" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B19" s="1">
+        <x:v>574099</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:3">
+      <x:c r="A20" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B20" s="1">
+        <x:v>-31053</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B21" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B22" s="1">
+        <x:v>764</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B23" s="1">
+        <x:v>-46</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B24" s="1">
+        <x:v>126778</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B25" s="1">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2276,7 +3881,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B8"/>
+  <x:dimension ref="A1:B18"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2294,58 +3899,138 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>2520121</x:v>
+        <x:v>2547653</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>21805555</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>4156286</x:v>
+        <x:v>33162402</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>600000</x:v>
+        <x:v>-6917</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>399814</x:v>
+        <x:v>4154425</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>2856022</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>87010</x:v>
+        <x:v>2920</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:2">
+      <x:c r="A9" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B9" s="1">
+        <x:v>2649</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:2">
+      <x:c r="A10" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B10" s="1">
+        <x:v>-22643</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:2">
+      <x:c r="A11" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B11" s="1">
+        <x:v>602651</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:2">
+      <x:c r="A12" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B12" s="1">
+        <x:v>399814</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:2">
+      <x:c r="A13" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B13" s="1">
+        <x:v>3294</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:2">
+      <x:c r="A14" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B14" s="1">
+        <x:v>5227933</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:2">
+      <x:c r="A15" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B15" s="1">
+        <x:v>-30671</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:2">
+      <x:c r="A16" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B16" s="1">
+        <x:v>764</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:2">
+      <x:c r="A17" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B17" s="1">
+        <x:v>126732</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:2">
+      <x:c r="A18" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B18" s="1">
+        <x:v>382</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2364,7 +4049,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C18"/>
+  <x:dimension ref="A1:C34"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2386,13 +4071,13 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>443469</x:v>
+        <x:v>499161</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -2400,7 +4085,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>2000000</x:v>
@@ -2408,10 +4093,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>76652</x:v>
@@ -2419,112 +4104,112 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>4379246</x:v>
+        <x:v>-28160</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>1952112</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>500346</x:v>
+        <x:v>6738689</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>9795828</x:v>
+        <x:v>3904224</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>149773</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>5028250</x:v>
+        <x:v>500346</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>4156286</x:v>
+        <x:v>16850035</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>600000</x:v>
+        <x:v>149773</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>1870</x:v>
+        <x:v>5018571</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>397944</x:v>
+        <x:v>-6917</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -2532,10 +4217,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>490153</x:v>
+        <x:v>4154425</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -2543,21 +4228,21 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>38952</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>2326917</x:v>
+        <x:v>2920</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -2565,10 +4250,186 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>87010</x:v>
+        <x:v>2649</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:3">
+      <x:c r="A19" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C19" s="1">
+        <x:v>-22643</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:3">
+      <x:c r="A20" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C20" s="1">
+        <x:v>600000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:3">
+      <x:c r="A21" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C21" s="1">
+        <x:v>2651</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:3">
+      <x:c r="A22" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C22" s="1">
+        <x:v>1870</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:3">
+      <x:c r="A23" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C23" s="1">
+        <x:v>397944</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:3">
+      <x:c r="A24" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C24" s="1">
+        <x:v>3294</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:3">
+      <x:c r="A25" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C25" s="1">
+        <x:v>515658</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C26" s="1">
+        <x:v>58441</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C27" s="1">
+        <x:v>4653834</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C28" s="1">
+        <x:v>382</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C29" s="1">
+        <x:v>-31053</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:3">
+      <x:c r="A30" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C30" s="1">
+        <x:v>764</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C31" s="1">
+        <x:v>87392</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C32" s="1">
+        <x:v>39386</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C33" s="1">
+        <x:v>-46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:3">
+      <x:c r="A34" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C34" s="1">
+        <x:v>382</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -319,6 +319,9 @@
   </x:si>
   <x:si>
     <x:t>BENNETT, REBECCA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALINDO, MAUREEN</x:t>
   </x:si>
   <x:si>
     <x:t>THOMPSON, MIKE MR.</x:t>
@@ -398,8 +401,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G60" totalsRowShown="0">
-  <x:autoFilter ref="A1:G60"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G61" totalsRowShown="0">
+  <x:autoFilter ref="A1:G61"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -414,8 +417,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E46" totalsRowShown="0">
-  <x:autoFilter ref="A1:E46"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E47" totalsRowShown="0">
+  <x:autoFilter ref="A1:E47"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -428,8 +431,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D41" totalsRowShown="0">
-  <x:autoFilter ref="A1:D41"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D42" totalsRowShown="0">
+  <x:autoFilter ref="A1:D42"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -763,7 +766,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G60"/>
+  <x:dimension ref="A1:G61"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1736,7 +1739,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>15206</x:v>
+        <x:v>30412</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -2081,7 +2084,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>87010</x:v>
+        <x:v>119601</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>12</x:v>
@@ -2089,70 +2092,93 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>499161</x:v>
+        <x:v>10864</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>1500000</x:v>
+        <x:v>499161</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B60" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C60" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D60" s="1" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="E60" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F60" s="1">
+        <x:v>1750000</x:v>
+      </x:c>
+      <x:c r="G60" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:7">
+      <x:c r="A61" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B60" s="1" t="s">
+      <x:c r="B61" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C60" s="1" t="s">
+      <x:c r="C61" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D60" s="1" t="s">
+      <x:c r="D61" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E60" s="1" t="s">
+      <x:c r="E61" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F60" s="1">
+      <x:c r="F61" s="1">
         <x:v>2326917</x:v>
       </x:c>
-      <x:c r="G60" s="1" t="s">
+      <x:c r="G61" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
@@ -2172,7 +2198,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E46"/>
+  <x:dimension ref="A1:E47"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2202,7 +2228,7 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>55</x:v>
@@ -2228,7 +2254,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="D3" s="1">
-        <x:v>15206</x:v>
+        <x:v>30412</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
         <x:v>12</x:v>
@@ -2287,16 +2313,16 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>1500000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>51</x:v>
@@ -2933,7 +2959,7 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
         <x:v>33</x:v>
@@ -2942,26 +2968,43 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="D45" s="1">
-        <x:v>87392</x:v>
+        <x:v>10864</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D46" s="1">
+        <x:v>119983</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:5">
+      <x:c r="A47" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B46" s="1" t="s">
+      <x:c r="B47" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C46" s="1" t="s">
+      <x:c r="C47" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D46" s="1">
+      <x:c r="D47" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="E46" s="1" t="s">
+      <x:c r="E47" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -2981,7 +3024,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D41"/>
+  <x:dimension ref="A1:D42"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3027,7 +3070,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>15206</x:v>
+        <x:v>30412</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
         <x:v>12</x:v>
@@ -3077,13 +3120,13 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>1500000</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
         <x:v>51</x:v>
@@ -3545,23 +3588,37 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>87392</x:v>
+        <x:v>10864</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C41" s="1">
+        <x:v>119983</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:4">
+      <x:c r="A42" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B41" s="1" t="s">
+      <x:c r="B42" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C41" s="1">
+      <x:c r="C42" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="D41" s="1" t="s">
+      <x:c r="D42" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -3606,7 +3663,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>2000000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
         <x:v>51</x:v>
@@ -3617,7 +3674,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>547653</x:v>
+        <x:v>562859</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>12</x:v>
@@ -3837,7 +3894,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B23" s="1">
-        <x:v>-46</x:v>
+        <x:v>10818</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>51</x:v>
@@ -3848,7 +3905,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B24" s="1">
-        <x:v>126778</x:v>
+        <x:v>159369</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>12</x:v>
@@ -3902,7 +3959,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>2547653</x:v>
+        <x:v>2812859</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -4022,7 +4079,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>126732</x:v>
+        <x:v>170187</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
@@ -4088,7 +4145,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>2000000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
@@ -4099,7 +4156,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>76652</x:v>
+        <x:v>91858</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
@@ -4396,7 +4453,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>87392</x:v>
+        <x:v>130847</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2061,7 +2061,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>165658</x:v>
+        <x:v>209658</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>12</x:v>
@@ -2815,7 +2815,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>165658</x:v>
+        <x:v>209658</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>12</x:v>
@@ -3462,7 +3462,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>165658</x:v>
+        <x:v>209658</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>12</x:v>
@@ -3850,7 +3850,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>574099</x:v>
+        <x:v>618099</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>12</x:v>
@@ -4055,7 +4055,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>5227933</x:v>
+        <x:v>5271933</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
@@ -4387,7 +4387,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>515658</x:v>
+        <x:v>559658</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -325,6 +325,9 @@
   </x:si>
   <x:si>
     <x:t>THOMPSON, MIKE MR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WIENER, SCOTT</x:t>
   </x:si>
   <x:si>
     <x:t>CAMPA-NAJJAR, AMMAR</x:t>
@@ -401,8 +404,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G61" totalsRowShown="0">
-  <x:autoFilter ref="A1:G61"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G62" totalsRowShown="0">
+  <x:autoFilter ref="A1:G62"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -417,8 +420,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E47" totalsRowShown="0">
-  <x:autoFilter ref="A1:E47"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E48" totalsRowShown="0">
+  <x:autoFilter ref="A1:E48"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -431,8 +434,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D42" totalsRowShown="0">
-  <x:autoFilter ref="A1:D42"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D43" totalsRowShown="0">
+  <x:autoFilter ref="A1:D43"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -467,8 +470,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C34" totalsRowShown="0">
-  <x:autoFilter ref="A1:C34"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C35" totalsRowShown="0">
+  <x:autoFilter ref="A1:C35"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -766,7 +769,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G61"/>
+  <x:dimension ref="A1:G62"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1739,7 +1742,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>30412</x:v>
+        <x:v>63297</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -2107,7 +2110,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>10864</x:v>
+        <x:v>12864</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
         <x:v>51</x:v>
@@ -2138,47 +2141,70 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
         <x:v>102</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>1750000</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B61" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C61" s="1" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D61" s="1" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="E61" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F61" s="1">
+        <x:v>1750000</x:v>
+      </x:c>
+      <x:c r="G61" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:7">
+      <x:c r="A62" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B61" s="1" t="s">
+      <x:c r="B62" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C61" s="1" t="s">
+      <x:c r="C62" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D61" s="1" t="s">
+      <x:c r="D62" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E61" s="1" t="s">
+      <x:c r="E62" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F61" s="1">
+      <x:c r="F62" s="1">
         <x:v>2326917</x:v>
       </x:c>
-      <x:c r="G61" s="1" t="s">
+      <x:c r="G62" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
@@ -2198,7 +2224,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E47"/>
+  <x:dimension ref="A1:E48"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2254,7 +2280,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="D3" s="1">
-        <x:v>30412</x:v>
+        <x:v>63297</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
         <x:v>12</x:v>
@@ -2262,24 +2288,24 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="D4" s="1">
-        <x:v>500000</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>93</x:v>
@@ -2288,24 +2314,24 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="D5" s="1">
-        <x:v>61446</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>-28160</x:v>
+        <x:v>61446</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>12</x:v>
@@ -2313,50 +2339,50 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>1750000</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>382</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>6739071</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>12</x:v>
@@ -2364,24 +2390,24 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>-9678</x:v>
+        <x:v>6739071</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>50</x:v>
@@ -2390,7 +2416,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>59748</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>51</x:v>
@@ -2398,7 +2424,7 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>50</x:v>
@@ -2407,32 +2433,32 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>4968501</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>1327758</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>14</x:v>
@@ -2441,32 +2467,32 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>6879864</x:v>
+        <x:v>1327758</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>2367356</x:v>
+        <x:v>6879864</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>76</x:v>
@@ -2475,7 +2501,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>2741118</x:v>
+        <x:v>2367356</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>51</x:v>
@@ -2483,7 +2509,7 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>76</x:v>
@@ -2492,15 +2518,15 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>209110</x:v>
+        <x:v>2741118</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>76</x:v>
@@ -2509,7 +2535,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>149773</x:v>
+        <x:v>209110</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>12</x:v>
@@ -2517,7 +2543,7 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>76</x:v>
@@ -2526,7 +2552,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>7729781</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>12</x:v>
@@ -2534,33 +2560,33 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>-6917</x:v>
+        <x:v>7729781</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>3575106</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>51</x:v>
@@ -2568,7 +2594,7 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>55</x:v>
@@ -2577,24 +2603,24 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>579319</x:v>
+        <x:v>3575106</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>382</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>12</x:v>
@@ -2602,16 +2628,16 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>2538</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>12</x:v>
@@ -2619,16 +2645,16 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>382</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>12</x:v>
@@ -2636,16 +2662,16 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -2653,50 +2679,50 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>2651</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>12</x:v>
@@ -2704,24 +2730,24 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>17</x:v>
@@ -2730,24 +2756,24 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>938</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>12</x:v>
@@ -2758,13 +2784,13 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>1974</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>12</x:v>
@@ -2772,7 +2798,7 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>38</x:v>
@@ -2781,7 +2807,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>382</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>12</x:v>
@@ -2789,24 +2815,24 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
         <x:v>50</x:v>
@@ -2815,32 +2841,32 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>209658</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>2326917</x:v>
+        <x:v>209658</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
         <x:v>24</x:v>
@@ -2849,55 +2875,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D40" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>382</x:v>
@@ -2908,10 +2934,10 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
         <x:v>11</x:v>
@@ -2925,58 +2951,58 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D43" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="D44" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="D45" s="1">
-        <x:v>10864</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
         <x:v>33</x:v>
@@ -2985,26 +3011,43 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="D46" s="1">
-        <x:v>119983</x:v>
+        <x:v>12864</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B47" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C47" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D47" s="1">
+        <x:v>119983</x:v>
+      </x:c>
+      <x:c r="E47" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:5">
+      <x:c r="A48" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B47" s="1" t="s">
+      <x:c r="B48" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C47" s="1" t="s">
+      <x:c r="C48" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D47" s="1">
+      <x:c r="D48" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="E47" s="1" t="s">
+      <x:c r="E48" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -3024,7 +3067,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D42"/>
+  <x:dimension ref="A1:D43"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3070,7 +3113,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>30412</x:v>
+        <x:v>63297</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
         <x:v>12</x:v>
@@ -3078,16 +3121,16 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>500000</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
@@ -3098,21 +3141,21 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>61446</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>-28160</x:v>
+        <x:v>61446</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>12</x:v>
@@ -3120,41 +3163,41 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>1750000</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>382</x:v>
+        <x:v>1750000</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>6739071</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>12</x:v>
@@ -3162,16 +3205,16 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>50070</x:v>
+        <x:v>6739071</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
@@ -3182,24 +3225,24 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>4968501</x:v>
+        <x:v>50070</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>1327758</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
@@ -3210,24 +3253,24 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>6879864</x:v>
+        <x:v>1327758</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>5108474</x:v>
+        <x:v>6879864</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
@@ -3238,35 +3281,35 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>8088664</x:v>
+        <x:v>5108474</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>-6917</x:v>
+        <x:v>8088664</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>3575106</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>51</x:v>
@@ -3280,21 +3323,21 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>579319</x:v>
+        <x:v>3575106</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>382</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
         <x:v>12</x:v>
@@ -3302,13 +3345,13 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>2538</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>12</x:v>
@@ -3316,13 +3359,13 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>382</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>12</x:v>
@@ -3330,13 +3373,13 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -3344,41 +3387,41 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>2651</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
         <x:v>12</x:v>
@@ -3386,16 +3429,16 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
@@ -3406,21 +3449,21 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>938</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
         <x:v>12</x:v>
@@ -3428,13 +3471,13 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>2356</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
         <x:v>12</x:v>
@@ -3442,16 +3485,16 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>2326917</x:v>
+        <x:v>2356</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
@@ -3462,24 +3505,24 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>209658</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>2326917</x:v>
+        <x:v>209658</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
@@ -3490,46 +3533,46 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>382</x:v>
@@ -3540,7 +3583,7 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
         <x:v>11</x:v>
@@ -3554,44 +3597,44 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>10864</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
@@ -3602,23 +3645,37 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>119983</x:v>
+        <x:v>12864</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B42" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C42" s="1">
+        <x:v>119983</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:4">
+      <x:c r="A43" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B42" s="1" t="s">
+      <x:c r="B43" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C42" s="1">
+      <x:c r="C43" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="D42" s="1" t="s">
+      <x:c r="D43" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -3674,7 +3731,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>562859</x:v>
+        <x:v>655744</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>12</x:v>
@@ -3894,7 +3951,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B23" s="1">
-        <x:v>10818</x:v>
+        <x:v>12818</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>51</x:v>
@@ -3959,7 +4016,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>2812859</x:v>
+        <x:v>2905744</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -4079,7 +4136,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>170187</x:v>
+        <x:v>172187</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
@@ -4106,7 +4163,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C34"/>
+  <x:dimension ref="A1:C35"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4156,106 +4213,106 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>91858</x:v>
+        <x:v>124743</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>-28160</x:v>
+        <x:v>60000</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>382</x:v>
+        <x:v>-28160</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>6738689</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>3904224</x:v>
+        <x:v>6738689</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>764</x:v>
+        <x:v>3904224</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>500346</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>16850035</x:v>
+        <x:v>500346</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>149773</x:v>
+        <x:v>16850035</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>5018571</x:v>
+        <x:v>149773</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -4263,10 +4320,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>-6917</x:v>
+        <x:v>5018571</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -4274,21 +4331,21 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>4154425</x:v>
+        <x:v>-6917</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>382</x:v>
+        <x:v>4154425</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -4296,10 +4353,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>2920</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -4307,43 +4364,43 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>2649</x:v>
+        <x:v>2920</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>600000</x:v>
+        <x:v>-22643</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>2651</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
@@ -4351,98 +4408,98 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>1870</x:v>
+        <x:v>2651</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>397944</x:v>
+        <x:v>1870</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>3294</x:v>
+        <x:v>397944</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>559658</x:v>
+        <x:v>3294</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>58441</x:v>
+        <x:v>559658</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>4653834</x:v>
+        <x:v>58441</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>382</x:v>
+        <x:v>4653834</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>-31053</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>764</x:v>
+        <x:v>-31053</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
@@ -4450,42 +4507,53 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>130847</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>39386</x:v>
+        <x:v>132847</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>-46</x:v>
+        <x:v>39386</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C34" s="1">
+        <x:v>-46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:3">
+      <x:c r="A35" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B34" s="1" t="s">
+      <x:c r="B35" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C34" s="1">
+      <x:c r="C35" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -1788,7 +1788,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>61446</x:v>
+        <x:v>91433</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>12</x:v>
@@ -2087,7 +2087,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>119601</x:v>
+        <x:v>163056</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>12</x:v>
@@ -2331,7 +2331,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>61446</x:v>
+        <x:v>91433</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>12</x:v>
@@ -3028,7 +3028,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="D47" s="1">
-        <x:v>119983</x:v>
+        <x:v>163438</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>12</x:v>
@@ -3155,7 +3155,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>61446</x:v>
+        <x:v>91433</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>12</x:v>
@@ -3659,7 +3659,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>119983</x:v>
+        <x:v>163438</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
         <x:v>12</x:v>
@@ -3731,7 +3731,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>655744</x:v>
+        <x:v>685731</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>12</x:v>
@@ -3962,7 +3962,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B24" s="1">
-        <x:v>159369</x:v>
+        <x:v>202824</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>12</x:v>
@@ -4016,7 +4016,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>2905744</x:v>
+        <x:v>2935731</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -4136,7 +4136,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>172187</x:v>
+        <x:v>215642</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
@@ -4213,7 +4213,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>124743</x:v>
+        <x:v>154730</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
@@ -4521,7 +4521,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>132847</x:v>
+        <x:v>176302</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2087,7 +2087,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>163056</x:v>
+        <x:v>163756</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>12</x:v>
@@ -2110,7 +2110,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>12864</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
         <x:v>51</x:v>
@@ -3011,7 +3011,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="D46" s="1">
-        <x:v>12864</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>51</x:v>
@@ -3028,7 +3028,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="D47" s="1">
-        <x:v>163438</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>12</x:v>
@@ -3645,7 +3645,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>12864</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
         <x:v>51</x:v>
@@ -3659,7 +3659,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>163438</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
         <x:v>12</x:v>
@@ -3951,7 +3951,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B23" s="1">
-        <x:v>12818</x:v>
+        <x:v>14218</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>51</x:v>
@@ -3962,7 +3962,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B24" s="1">
-        <x:v>202824</x:v>
+        <x:v>203524</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>12</x:v>
@@ -4136,7 +4136,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>215642</x:v>
+        <x:v>217742</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
@@ -4521,7 +4521,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>176302</x:v>
+        <x:v>178402</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -404,8 +404,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G62" totalsRowShown="0">
-  <x:autoFilter ref="A1:G62"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G63" totalsRowShown="0">
+  <x:autoFilter ref="A1:G63"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -470,8 +470,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C35" totalsRowShown="0">
-  <x:autoFilter ref="A1:C35"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C36" totalsRowShown="0">
+  <x:autoFilter ref="A1:C36"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -769,7 +769,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G62"/>
+  <x:dimension ref="A1:G63"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1980,22 +1980,22 @@
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>198972</x:v>
+        <x:v>51639</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -2003,13 +2003,13 @@
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
         <x:v>17</x:v>
@@ -2018,18 +2018,18 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>1870</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
         <x:v>98</x:v>
@@ -2041,7 +2041,7 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>198972</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>51</x:v>
@@ -2049,45 +2049,45 @@
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>209658</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>163756</x:v>
+        <x:v>209658</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>12</x:v>
@@ -2101,7 +2101,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
         <x:v>33</x:v>
@@ -2110,53 +2110,53 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>14264</x:v>
+        <x:v>163756</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>499161</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>60000</x:v>
+        <x:v>499161</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>12</x:v>
@@ -2164,47 +2164,70 @@
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>1750000</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B62" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C62" s="1" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D62" s="1" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="E62" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F62" s="1">
+        <x:v>1750000</x:v>
+      </x:c>
+      <x:c r="G62" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:7">
+      <x:c r="A63" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B62" s="1" t="s">
+      <x:c r="B63" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C62" s="1" t="s">
+      <x:c r="C63" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D62" s="1" t="s">
+      <x:c r="D63" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E62" s="1" t="s">
+      <x:c r="E63" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F62" s="1">
+      <x:c r="F63" s="1">
         <x:v>2326917</x:v>
       </x:c>
-      <x:c r="G62" s="1" t="s">
+      <x:c r="G63" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
@@ -2637,7 +2660,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>382</x:v>
+        <x:v>52021</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>12</x:v>
@@ -3351,7 +3374,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>382</x:v>
+        <x:v>52021</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>12</x:v>
@@ -3808,7 +3831,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>382</x:v>
+        <x:v>52021</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>12</x:v>
@@ -4056,7 +4079,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>382</x:v>
+        <x:v>52021</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -4163,7 +4186,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C35"/>
+  <x:dimension ref="A1:C36"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4361,13 +4384,13 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>2920</x:v>
+        <x:v>51639</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -4375,43 +4398,43 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>2649</x:v>
+        <x:v>2920</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>600000</x:v>
+        <x:v>-22643</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>2651</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -4419,98 +4442,98 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>1870</x:v>
+        <x:v>2651</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>397944</x:v>
+        <x:v>1870</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>3294</x:v>
+        <x:v>397944</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>559658</x:v>
+        <x:v>3294</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>58441</x:v>
+        <x:v>559658</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>4653834</x:v>
+        <x:v>58441</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>382</x:v>
+        <x:v>4653834</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>-31053</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>764</x:v>
+        <x:v>-31053</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
@@ -4518,42 +4541,53 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>178402</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>39386</x:v>
+        <x:v>178402</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>-46</x:v>
+        <x:v>39386</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C35" s="1">
+        <x:v>-46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:3">
+      <x:c r="A36" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B35" s="1" t="s">
+      <x:c r="B36" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C35" s="1">
+      <x:c r="C36" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2087,7 +2087,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>209658</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>12</x:v>
@@ -2202,7 +2202,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>1750000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>51</x:v>
@@ -2388,7 +2388,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>1750000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>51</x:v>
@@ -2881,7 +2881,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>209658</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>12</x:v>
@@ -3206,7 +3206,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>1750000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>51</x:v>
@@ -3542,7 +3542,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>209658</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
         <x:v>12</x:v>
@@ -3743,7 +3743,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>2250000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
         <x:v>51</x:v>
@@ -3930,7 +3930,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>618099</x:v>
+        <x:v>662099</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>12</x:v>
@@ -4039,7 +4039,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>2935731</x:v>
+        <x:v>3185731</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -4135,7 +4135,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>5271933</x:v>
+        <x:v>5315933</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
@@ -4225,7 +4225,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>2250000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
@@ -4489,7 +4489,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>559658</x:v>
+        <x:v>603658</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -1788,7 +1788,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>91433</x:v>
+        <x:v>152762</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>12</x:v>
@@ -2354,7 +2354,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>91433</x:v>
+        <x:v>152762</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>12</x:v>
@@ -3178,7 +3178,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>91433</x:v>
+        <x:v>152762</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>12</x:v>
@@ -3754,7 +3754,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>685731</x:v>
+        <x:v>747060</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>12</x:v>
@@ -4039,7 +4039,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>3185731</x:v>
+        <x:v>3247060</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -4236,7 +4236,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>154730</x:v>
+        <x:v>216059</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -1995,7 +1995,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>51639</x:v>
+        <x:v>1238800</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -2660,7 +2660,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>52021</x:v>
+        <x:v>1239182</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>12</x:v>
@@ -3374,7 +3374,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>52021</x:v>
+        <x:v>1239182</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>12</x:v>
@@ -3831,7 +3831,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>52021</x:v>
+        <x:v>1239182</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>12</x:v>
@@ -4079,7 +4079,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>52021</x:v>
+        <x:v>1239182</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -4390,7 +4390,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>51639</x:v>
+        <x:v>1238800</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -1995,7 +1995,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>1238800</x:v>
+        <x:v>1290439</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -2660,7 +2660,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>1239182</x:v>
+        <x:v>1290821</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>12</x:v>
@@ -3374,7 +3374,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>1239182</x:v>
+        <x:v>1290821</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>12</x:v>
@@ -3831,7 +3831,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>1239182</x:v>
+        <x:v>1290821</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>12</x:v>
@@ -4079,7 +4079,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>1239182</x:v>
+        <x:v>1290821</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -4390,7 +4390,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>1238800</x:v>
+        <x:v>1290439</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -1995,7 +1995,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>1290439</x:v>
+        <x:v>1415439</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -2660,7 +2660,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>1290821</x:v>
+        <x:v>1415821</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>12</x:v>
@@ -3374,7 +3374,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>1290821</x:v>
+        <x:v>1415821</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>12</x:v>
@@ -3831,7 +3831,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>1290821</x:v>
+        <x:v>1415821</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>12</x:v>
@@ -4079,7 +4079,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>1290821</x:v>
+        <x:v>1415821</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -4390,7 +4390,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>1290439</x:v>
+        <x:v>1415439</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -1995,7 +1995,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>1415439</x:v>
+        <x:v>1524553</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -2660,7 +2660,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>1415821</x:v>
+        <x:v>1524935</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>12</x:v>
@@ -3374,7 +3374,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>1415821</x:v>
+        <x:v>1524935</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>12</x:v>
@@ -3831,7 +3831,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>1415821</x:v>
+        <x:v>1524935</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>12</x:v>
@@ -4079,7 +4079,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>1415821</x:v>
+        <x:v>1524935</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -4390,7 +4390,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>1415439</x:v>
+        <x:v>1524553</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -60,6 +60,21 @@
     <x:t>SUPPORT</x:t>
   </x:si>
   <x:si>
+    <x:t>BAINS, JASMEET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VON WILPERT, MARNI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
     <x:t>BIRD, SHANNON KATHLEEN</x:t>
   </x:si>
   <x:si>
@@ -219,9 +234,6 @@
     <x:t>34</x:t>
   </x:si>
   <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
     <x:t>BUSH, CORI</x:t>
   </x:si>
   <x:si>
@@ -240,6 +252,12 @@
     <x:t>28</x:t>
   </x:si>
   <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00863472</x:t>
   </x:si>
   <x:si>
@@ -249,9 +267,6 @@
     <x:t>FINE, LAURA</x:t>
   </x:si>
   <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00931774</x:t>
   </x:si>
   <x:si>
@@ -288,9 +303,6 @@
     <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
   </x:si>
   <x:si>
-    <x:t>BISS, DANIEL</x:t>
-  </x:si>
-  <x:si>
     <x:t>BABB TOMLINSON, LAUREN</x:t>
   </x:si>
   <x:si>
@@ -300,12 +312,6 @@
     <x:t>VILLEGAS, RANDY</x:t>
   </x:si>
   <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAINS, JASMEET</x:t>
-  </x:si>
-  <x:si>
     <x:t>GALLREIN, ED</x:t>
   </x:si>
   <x:si>
@@ -333,7 +339,10 @@
     <x:t>CAMPA-NAJJAR, AMMAR</x:t>
   </x:si>
   <x:si>
-    <x:t>48</x:t>
+    <x:t>MCADAMS, BEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -404,8 +413,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G63" totalsRowShown="0">
-  <x:autoFilter ref="A1:G63"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G66" totalsRowShown="0">
+  <x:autoFilter ref="A1:G66"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -420,8 +429,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E48" totalsRowShown="0">
-  <x:autoFilter ref="A1:E48"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E50" totalsRowShown="0">
+  <x:autoFilter ref="A1:E50"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -434,8 +443,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D43" totalsRowShown="0">
-  <x:autoFilter ref="A1:D43"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D45" totalsRowShown="0">
+  <x:autoFilter ref="A1:D45"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -447,8 +456,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C25" totalsRowShown="0">
-  <x:autoFilter ref="A1:C25"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C26" totalsRowShown="0">
+  <x:autoFilter ref="A1:C26"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -459,8 +468,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B18" totalsRowShown="0">
-  <x:autoFilter ref="A1:B18"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B19" totalsRowShown="0">
+  <x:autoFilter ref="A1:B19"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -470,8 +479,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C36" totalsRowShown="0">
-  <x:autoFilter ref="A1:C36"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C37" totalsRowShown="0">
+  <x:autoFilter ref="A1:C37"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -769,7 +778,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G63"/>
+  <x:dimension ref="A1:G66"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -845,7 +854,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>382</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -865,10 +874,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>382</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -882,16 +891,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>382</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>12</x:v>
@@ -905,13 +914,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>382</x:v>
@@ -928,13 +937,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>382</x:v>
@@ -951,16 +960,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>24</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>58441</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
         <x:v>12</x:v>
@@ -1000,13 +1009,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>382</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>12</x:v>
@@ -1020,13 +1029,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>382</x:v>
@@ -1043,13 +1052,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F12" s="1">
         <x:v>382</x:v>
@@ -1092,13 +1101,13 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>1974</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>12</x:v>
@@ -1112,16 +1121,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>2538</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>12</x:v>
@@ -1135,16 +1144,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>43</x:v>
-      </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>2649</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>12</x:v>
@@ -1158,16 +1167,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>2651</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1181,16 +1190,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>938</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>12</x:v>
@@ -1198,56 +1207,56 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B19" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C19" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>-9678</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B20" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C20" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>-31053</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>54</x:v>
@@ -1256,194 +1265,194 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>-1861</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>4968501</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>-6917</x:v>
+        <x:v>-1861</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>-46</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>59748</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>2326917</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>-28160</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B29" s="1" t="s">
+      <x:c r="D29" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>39386</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>12</x:v>
@@ -1451,45 +1460,45 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>500346</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>600000</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>12</x:v>
@@ -1497,22 +1506,22 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B32" s="1" t="s">
+      <x:c r="D32" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C32" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>350000</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1520,22 +1529,22 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B33" s="1" t="s">
+      <x:c r="C33" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="C33" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>2359443</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>12</x:v>
@@ -1552,16 +1561,16 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>663879</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
@@ -1572,39 +1581,39 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>1183678</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>104555</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>12</x:v>
@@ -1618,19 +1627,19 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D37" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>2893782</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
@@ -1641,19 +1650,19 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>2845686</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
@@ -1664,154 +1673,154 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>1314739</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>663879</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>3576967</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>63297</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>500000</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>152762</x:v>
+        <x:v>3576967</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B45" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>4379246</x:v>
+        <x:v>63297</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>12</x:v>
@@ -1819,68 +1828,68 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>3985700</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>1183678</x:v>
+        <x:v>152762</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>4383749</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>12</x:v>
@@ -1888,22 +1897,22 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>149773</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -1917,39 +1926,39 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>1426379</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>104555</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>12</x:v>
@@ -1957,45 +1966,45 @@
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>579319</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>1524553</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -2003,22 +2012,22 @@
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>198972</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -2026,137 +2035,137 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>1870</x:v>
+        <x:v>1524553</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F56" s="1">
         <x:v>198972</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D57" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E57" s="1" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="D57" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E57" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="F57" s="1">
-        <x:v>253658</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>163756</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>14264</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>499161</x:v>
+        <x:v>163756</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>12</x:v>
@@ -2164,71 +2173,140 @@
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
         <x:v>102</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>60000</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>2000000</x:v>
+        <x:v>499161</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F63" s="1">
+        <x:v>60000</x:v>
+      </x:c>
+      <x:c r="G63" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:7">
+      <x:c r="A64" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B64" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C64" s="1" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D64" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E64" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F64" s="1">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="G64" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:7">
+      <x:c r="A65" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B65" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C65" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D65" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E65" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F65" s="1">
         <x:v>2326917</x:v>
       </x:c>
-      <x:c r="G63" s="1" t="s">
-        <x:v>51</x:v>
+      <x:c r="G65" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:7">
+      <x:c r="A66" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B66" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C66" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D66" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E66" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F66" s="1">
+        <x:v>181000</x:v>
+      </x:c>
+      <x:c r="G66" s="1" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2247,7 +2325,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E48"/>
+  <x:dimension ref="A1:E50"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2277,13 +2355,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>499161</x:v>
@@ -2294,13 +2372,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>63297</x:v>
@@ -2311,13 +2389,13 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>60000</x:v>
@@ -2328,33 +2406,33 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>152762</x:v>
+        <x:v>153095</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>12</x:v>
@@ -2362,13 +2440,13 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>-28160</x:v>
@@ -2379,33 +2457,33 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>382</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>12</x:v>
@@ -2413,16 +2491,16 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>6739071</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>12</x:v>
@@ -2430,152 +2508,152 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>-9678</x:v>
+        <x:v>8758871</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>59748</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>4968501</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>1327758</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>6879864</x:v>
+        <x:v>1327758</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>2367356</x:v>
+        <x:v>7971780</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>2741118</x:v>
+        <x:v>2367356</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>209110</x:v>
+        <x:v>2852758</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>149773</x:v>
+        <x:v>209110</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>12</x:v>
@@ -2583,16 +2661,16 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>7729781</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>12</x:v>
@@ -2600,67 +2678,67 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>-6917</x:v>
+        <x:v>9267843</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>3575106</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>579319</x:v>
+        <x:v>3575106</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>1524935</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>12</x:v>
@@ -2668,16 +2746,16 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>2538</x:v>
+        <x:v>1524935</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>12</x:v>
@@ -2685,16 +2763,16 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>382</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -2702,16 +2780,16 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>12</x:v>
@@ -2719,50 +2797,50 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>2651</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>12</x:v>
@@ -2770,50 +2848,50 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>938</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>12</x:v>
@@ -2821,16 +2899,16 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>1974</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>12</x:v>
@@ -2838,16 +2916,16 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>382</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>12</x:v>
@@ -2855,115 +2933,115 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>253658</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>2326917</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D40" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>382</x:v>
@@ -2974,10 +3052,10 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
         <x:v>11</x:v>
@@ -2991,86 +3069,120 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D44" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D45" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D46" s="1">
-        <x:v>14264</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D47" s="1">
-        <x:v>164138</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D48" s="1">
+        <x:v>164138</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:5">
+      <x:c r="A49" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D49" s="1">
+        <x:v>181000</x:v>
+      </x:c>
+      <x:c r="E49" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:5">
+      <x:c r="A50" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D50" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="E48" s="1" t="s">
+      <x:c r="E50" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -3090,7 +3202,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D43"/>
+  <x:dimension ref="A1:D45"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3116,10 +3228,10 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>499161</x:v>
@@ -3130,10 +3242,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>63297</x:v>
@@ -3144,10 +3256,10 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>60000</x:v>
@@ -3158,27 +3270,27 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>152762</x:v>
+        <x:v>153095</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>12</x:v>
@@ -3186,10 +3298,10 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>-28160</x:v>
@@ -3200,27 +3312,27 @@
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>382</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>12</x:v>
@@ -3228,13 +3340,13 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>6739071</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
         <x:v>12</x:v>
@@ -3242,139 +3354,139 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>50070</x:v>
+        <x:v>8758871</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>4968501</x:v>
+        <x:v>50070</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>1327758</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>6879864</x:v>
+        <x:v>1327758</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>5108474</x:v>
+        <x:v>7971780</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>8088664</x:v>
+        <x:v>5220114</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>-6917</x:v>
+        <x:v>9626726</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>3575106</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>579319</x:v>
+        <x:v>3575106</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>1524935</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>12</x:v>
@@ -3382,13 +3494,13 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>2538</x:v>
+        <x:v>1524935</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>12</x:v>
@@ -3396,13 +3508,13 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>382</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -3410,13 +3522,13 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>12</x:v>
@@ -3424,41 +3536,41 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>2651</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>12</x:v>
@@ -3466,41 +3578,41 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>938</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
         <x:v>12</x:v>
@@ -3508,13 +3620,13 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>2356</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
         <x:v>12</x:v>
@@ -3522,94 +3634,94 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>2326917</x:v>
+        <x:v>2356</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>253658</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>2326917</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>382</x:v>
@@ -3620,7 +3732,7 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
         <x:v>11</x:v>
@@ -3634,71 +3746,99 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>14264</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>164138</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C43" s="1">
+        <x:v>164138</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:4">
+      <x:c r="A44" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C44" s="1">
+        <x:v>181000</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:4">
+      <x:c r="A45" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C45" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="D43" s="1" t="s">
+      <x:c r="D45" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -3718,7 +3858,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C25"/>
+  <x:dimension ref="A1:C26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3740,21 +3880,21 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>2500000</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>747060</x:v>
+        <x:v>747726</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>12</x:v>
@@ -3762,10 +3902,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>382</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>12</x:v>
@@ -3773,21 +3913,21 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>6486302</x:v>
+        <x:v>6597942</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>26676100</x:v>
+        <x:v>31325878</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>12</x:v>
@@ -3795,29 +3935,29 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>3575106</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>579319</x:v>
@@ -3828,7 +3968,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>1524935</x:v>
@@ -3839,7 +3979,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>2920</x:v>
@@ -3850,7 +3990,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>2649</x:v>
@@ -3861,18 +4001,18 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>-22643</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>602651</x:v>
@@ -3883,18 +4023,18 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>198972</x:v>
@@ -3905,7 +4045,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>3294</x:v>
@@ -3916,18 +4056,18 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>4653834</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>662099</x:v>
@@ -3938,18 +4078,18 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>382</x:v>
@@ -3971,18 +4111,18 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>14218</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>203524</x:v>
@@ -3993,12 +4133,23 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B25" s="1">
+        <x:v>181000</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:3">
+      <x:c r="A26" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B26" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="C25" s="1" t="s">
+      <x:c r="C26" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -4018,7 +4169,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B18"/>
+  <x:dimension ref="A1:B19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4036,31 +4187,31 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>3247060</x:v>
+        <x:v>3247726</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>382</x:v>
+        <x:v>715</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>33162402</x:v>
+        <x:v>37923820</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>-6917</x:v>
@@ -4068,7 +4219,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>4154425</x:v>
@@ -4076,7 +4227,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>1524935</x:v>
@@ -4084,7 +4235,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>2920</x:v>
@@ -4092,7 +4243,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>2649</x:v>
@@ -4100,7 +4251,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>-22643</x:v>
@@ -4108,7 +4259,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>602651</x:v>
@@ -4116,7 +4267,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>399814</x:v>
@@ -4124,7 +4275,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>3294</x:v>
@@ -4132,7 +4283,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>5315933</x:v>
@@ -4140,7 +4291,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>-30671</x:v>
@@ -4156,7 +4307,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>217742</x:v>
@@ -4164,9 +4315,17 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B18" s="1">
+        <x:v>181000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:2">
+      <x:c r="A19" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B19" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>
@@ -4186,7 +4345,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C36"/>
+  <x:dimension ref="A1:C37"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4208,10 +4367,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>499161</x:v>
@@ -4222,18 +4381,18 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>2500000</x:v>
+        <x:v>2500666</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>216059</x:v>
@@ -4241,10 +4400,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>60000</x:v>
@@ -4252,10 +4411,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>-28160</x:v>
@@ -4266,29 +4425,29 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>382</x:v>
+        <x:v>715</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>6738689</x:v>
+        <x:v>8758489</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>3904224</x:v>
@@ -4299,7 +4458,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>764</x:v>
@@ -4307,10 +4466,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>500346</x:v>
@@ -4318,21 +4477,21 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>16850035</x:v>
+        <x:v>19591653</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>149773</x:v>
@@ -4340,10 +4499,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>5018571</x:v>
@@ -4351,10 +4510,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>-6917</x:v>
@@ -4362,10 +4521,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>4154425</x:v>
@@ -4376,7 +4535,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>382</x:v>
@@ -4384,10 +4543,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1524553</x:v>
@@ -4398,7 +4557,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>2920</x:v>
@@ -4409,7 +4568,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>2649</x:v>
@@ -4417,10 +4576,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>-22643</x:v>
@@ -4428,10 +4587,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>600000</x:v>
@@ -4442,7 +4601,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>2651</x:v>
@@ -4453,7 +4612,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>1870</x:v>
@@ -4461,10 +4620,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>397944</x:v>
@@ -4475,7 +4634,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>3294</x:v>
@@ -4483,10 +4642,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>603658</x:v>
@@ -4497,7 +4656,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>58441</x:v>
@@ -4505,10 +4664,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>4653834</x:v>
@@ -4519,7 +4678,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>382</x:v>
@@ -4527,10 +4686,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>-31053</x:v>
@@ -4552,7 +4711,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>178402</x:v>
@@ -4560,10 +4719,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>39386</x:v>
@@ -4571,10 +4730,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>-46</x:v>
@@ -4582,12 +4741,23 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C36" s="1">
+        <x:v>181000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:3">
+      <x:c r="A37" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B36" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C36" s="1">
+      <x:c r="B37" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C37" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2050,7 +2050,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>1524553</x:v>
+        <x:v>2811685</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>12</x:v>
@@ -2755,7 +2755,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>1524935</x:v>
+        <x:v>2812067</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>12</x:v>
@@ -3500,7 +3500,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>1524935</x:v>
+        <x:v>2812067</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>12</x:v>
@@ -3971,7 +3971,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>1524935</x:v>
+        <x:v>2812067</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>12</x:v>
@@ -4230,7 +4230,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>1524935</x:v>
+        <x:v>2812067</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -4549,7 +4549,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>1524553</x:v>
+        <x:v>2811685</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -413,8 +413,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G66" totalsRowShown="0">
-  <x:autoFilter ref="A1:G66"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G67" totalsRowShown="0">
+  <x:autoFilter ref="A1:G67"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -479,8 +479,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C37" totalsRowShown="0">
-  <x:autoFilter ref="A1:C37"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C38" totalsRowShown="0">
+  <x:autoFilter ref="A1:C38"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -778,7 +778,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G66"/>
+  <x:dimension ref="A1:G67"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2306,6 +2306,29 @@
         <x:v>181000</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:7">
+      <x:c r="A67" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B67" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C67" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D67" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E67" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F67" s="1">
+        <x:v>2464275</x:v>
+      </x:c>
+      <x:c r="G67" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -2772,7 +2795,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>2538</x:v>
+        <x:v>2466813</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -3514,7 +3537,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>2538</x:v>
+        <x:v>2466813</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -3982,7 +4005,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>2920</x:v>
+        <x:v>2467195</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -4238,7 +4261,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>2920</x:v>
+        <x:v>2467195</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -4345,7 +4368,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C37"/>
+  <x:dimension ref="A1:C38"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4565,46 +4588,46 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>2649</x:v>
+        <x:v>2464275</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>600000</x:v>
+        <x:v>-22643</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>2651</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -4612,98 +4635,98 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>1870</x:v>
+        <x:v>2651</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>99</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>397944</x:v>
+        <x:v>1870</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>3294</x:v>
+        <x:v>397944</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>603658</x:v>
+        <x:v>3294</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>58441</x:v>
+        <x:v>603658</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>4653834</x:v>
+        <x:v>58441</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>382</x:v>
+        <x:v>4653834</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>-31053</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>764</x:v>
+        <x:v>-31053</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
@@ -4711,53 +4734,64 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>178402</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>39386</x:v>
+        <x:v>178402</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>-46</x:v>
+        <x:v>39386</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>181000</x:v>
+        <x:v>-46</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C37" s="1">
+        <x:v>181000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:3">
+      <x:c r="A38" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B37" s="1" t="s">
+      <x:c r="B38" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C37" s="1">
+      <x:c r="C38" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2050,7 +2050,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>2811685</x:v>
+        <x:v>2913324</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>12</x:v>
@@ -2778,7 +2778,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>2812067</x:v>
+        <x:v>2913706</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>12</x:v>
@@ -3523,7 +3523,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>2812067</x:v>
+        <x:v>2913706</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>12</x:v>
@@ -3994,7 +3994,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>2812067</x:v>
+        <x:v>2913706</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>12</x:v>
@@ -4253,7 +4253,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>2812067</x:v>
+        <x:v>2913706</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -4572,7 +4572,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>2811685</x:v>
+        <x:v>2913324</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -225,6 +225,9 @@
     <x:t>FRIEDMAN, JASON</x:t>
   </x:si>
   <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
     <x:t>MALINOWSKI, TOM</x:t>
   </x:si>
   <x:si>
@@ -310,9 +313,6 @@
   </x:si>
   <x:si>
     <x:t>VILLEGAS, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALLREIN, ED</x:t>
   </x:si>
   <x:si>
     <x:t>POWELL, DENISE</x:t>
@@ -413,8 +413,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G67" totalsRowShown="0">
-  <x:autoFilter ref="A1:G67"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G68" totalsRowShown="0">
+  <x:autoFilter ref="A1:G68"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -778,7 +778,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G67"/>
+  <x:dimension ref="A1:G68"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1314,7 +1314,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>-1861</x:v>
+        <x:v>1239981</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>56</x:v>
@@ -1423,16 +1423,16 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>2326917</x:v>
+        <x:v>219149</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
@@ -1446,16 +1446,16 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>-28160</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
@@ -1466,62 +1466,62 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>-22643</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B31" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C31" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="E31" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="F31" s="1">
-        <x:v>39386</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>149773</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1529,22 +1529,22 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="B33" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C33" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D33" s="1" t="s">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>500346</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>12</x:v>
@@ -1552,22 +1552,22 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="B34" s="1" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="C34" s="1" t="s">
-        <x:v>84</x:v>
-      </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>600000</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1575,22 +1575,22 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>350000</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>12</x:v>
@@ -1598,22 +1598,22 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>4379243</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>12</x:v>
@@ -1621,45 +1621,45 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B37" s="1" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>663879</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>90</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>1183678</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>56</x:v>
@@ -1667,45 +1667,45 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>91</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>104555</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="B40" s="1" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C40" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>3985698</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>12</x:v>
@@ -1713,22 +1713,22 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>4383748</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1736,45 +1736,45 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>1426379</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>663879</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>56</x:v>
@@ -1782,22 +1782,22 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>3576967</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>56</x:v>
@@ -1805,59 +1805,59 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>63297</x:v>
+        <x:v>2335126</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="D46" s="1" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>500000</x:v>
+        <x:v>63297</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
         <x:v>14</x:v>
@@ -1866,30 +1866,30 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>152762</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>4379246</x:v>
+        <x:v>152762</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>12</x:v>
@@ -1897,22 +1897,22 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>3985700</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -1920,114 +1920,114 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>1183678</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>4383749</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>1426379</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>104555</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>579319</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -2041,16 +2041,16 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>2913324</x:v>
+        <x:v>360170</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>12</x:v>
@@ -2058,22 +2058,22 @@
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>198972</x:v>
+        <x:v>2913324</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>12</x:v>
@@ -2081,13 +2081,13 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
         <x:v>22</x:v>
@@ -2096,18 +2096,18 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>1870</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
         <x:v>100</x:v>
@@ -2119,7 +2119,7 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>198972</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
         <x:v>56</x:v>
@@ -2127,45 +2127,45 @@
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>253658</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>163756</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>12</x:v>
@@ -2179,7 +2179,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
         <x:v>38</x:v>
@@ -2188,53 +2188,53 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>14264</x:v>
+        <x:v>163756</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>499161</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>60000</x:v>
+        <x:v>499161</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
         <x:v>12</x:v>
@@ -2242,45 +2242,45 @@
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>2000000</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>2326917</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>56</x:v>
@@ -2288,47 +2288,70 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>181000</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B67" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C67" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D67" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E67" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F67" s="1">
+        <x:v>181000</x:v>
+      </x:c>
+      <x:c r="G67" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:7">
+      <x:c r="A68" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B67" s="1" t="s">
+      <x:c r="B68" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C67" s="1" t="s">
+      <x:c r="C68" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D67" s="1" t="s">
+      <x:c r="D68" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="E67" s="1" t="s">
+      <x:c r="E68" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F67" s="1">
+      <x:c r="F68" s="1">
         <x:v>2464275</x:v>
       </x:c>
-      <x:c r="G67" s="1" t="s">
+      <x:c r="G68" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -2395,10 +2418,10 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>15</x:v>
@@ -2429,7 +2452,7 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>14</x:v>
@@ -2463,10 +2486,10 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>15</x:v>
@@ -2599,7 +2622,7 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>19</x:v>
@@ -2633,10 +2656,10 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>23</x:v>
@@ -2650,10 +2673,10 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>23</x:v>
@@ -2667,10 +2690,10 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>23</x:v>
@@ -2684,10 +2707,10 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>23</x:v>
@@ -2701,10 +2724,10 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>23</x:v>
@@ -2744,7 +2767,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>3575106</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>56</x:v>
@@ -2752,7 +2775,7 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>60</x:v>
@@ -2837,13 +2860,13 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>-22643</x:v>
@@ -2871,7 +2894,7 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>60</x:v>
@@ -2973,7 +2996,7 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
         <x:v>55</x:v>
@@ -3007,7 +3030,7 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
         <x:v>29</x:v>
@@ -3126,10 +3149,10 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>39</x:v>
@@ -3265,7 +3288,7 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>15</x:v>
@@ -3321,7 +3344,7 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>15</x:v>
@@ -3447,7 +3470,7 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>23</x:v>
@@ -3461,7 +3484,7 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>23</x:v>
@@ -3495,7 +3518,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>3575106</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
         <x:v>56</x:v>
@@ -3576,7 +3599,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>-22643</x:v>
@@ -3797,7 +3820,7 @@
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
         <x:v>39</x:v>
@@ -3972,7 +3995,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>3575106</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>56</x:v>
@@ -4024,7 +4047,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>-22643</x:v>
@@ -4245,7 +4268,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>4154425</x:v>
+        <x:v>4154426</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
@@ -4274,7 +4297,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>-22643</x:v>
@@ -4390,7 +4413,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>15</x:v>
@@ -4412,7 +4435,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>15</x:v>
@@ -4423,7 +4446,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>15</x:v>
@@ -4456,7 +4479,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>23</x:v>
@@ -4467,7 +4490,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>23</x:v>
@@ -4489,7 +4512,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>23</x:v>
@@ -4500,7 +4523,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>23</x:v>
@@ -4511,7 +4534,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>23</x:v>
@@ -4550,7 +4573,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>4154425</x:v>
+        <x:v>4154426</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -4613,7 +4636,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>-22643</x:v>
@@ -4621,7 +4644,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>51</x:v>
@@ -4654,7 +4677,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
         <x:v>99</x:v>
@@ -4676,7 +4699,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>32</x:v>
@@ -4753,7 +4776,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>39</x:v>
@@ -4775,7 +4798,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
         <x:v>107</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2073,7 +2073,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>2913324</x:v>
+        <x:v>2926736</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>12</x:v>
@@ -2801,7 +2801,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>2913706</x:v>
+        <x:v>2927118</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>12</x:v>
@@ -3546,7 +3546,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>2913706</x:v>
+        <x:v>2927118</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>12</x:v>
@@ -4017,7 +4017,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>2913706</x:v>
+        <x:v>2927118</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>12</x:v>
@@ -4276,7 +4276,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>2913706</x:v>
+        <x:v>2927118</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -4595,7 +4595,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>2913324</x:v>
+        <x:v>2926736</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2073,7 +2073,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>2926736</x:v>
+        <x:v>5434539</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>12</x:v>
@@ -2349,7 +2349,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>2464275</x:v>
+        <x:v>4905805</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
         <x:v>12</x:v>
@@ -2801,7 +2801,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>2927118</x:v>
+        <x:v>5434921</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>12</x:v>
@@ -2818,7 +2818,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>2466813</x:v>
+        <x:v>4908343</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -3546,7 +3546,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>2927118</x:v>
+        <x:v>5434921</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>12</x:v>
@@ -3560,7 +3560,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>2466813</x:v>
+        <x:v>4908343</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -4017,7 +4017,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>2927118</x:v>
+        <x:v>5434921</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>12</x:v>
@@ -4028,7 +4028,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>2467195</x:v>
+        <x:v>4908725</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -4276,7 +4276,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>2927118</x:v>
+        <x:v>5434921</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -4284,7 +4284,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>2467195</x:v>
+        <x:v>4908725</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -4595,7 +4595,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>2926736</x:v>
+        <x:v>5434539</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -4617,7 +4617,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>2464275</x:v>
+        <x:v>4905805</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2073,7 +2073,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>5434539</x:v>
+        <x:v>5734014</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>12</x:v>
@@ -2326,7 +2326,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>181000</x:v>
+        <x:v>186455</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
         <x:v>12</x:v>
@@ -2349,7 +2349,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>4905805</x:v>
+        <x:v>4923593</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
         <x:v>12</x:v>
@@ -2801,7 +2801,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>5434921</x:v>
+        <x:v>5734396</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>12</x:v>
@@ -2818,7 +2818,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>4908343</x:v>
+        <x:v>4926131</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -3209,7 +3209,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="D49" s="1">
-        <x:v>181000</x:v>
+        <x:v>186455</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>12</x:v>
@@ -3546,7 +3546,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>5434921</x:v>
+        <x:v>5734396</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>12</x:v>
@@ -3560,7 +3560,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>4908343</x:v>
+        <x:v>4926131</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -3868,7 +3868,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="C44" s="1">
-        <x:v>181000</x:v>
+        <x:v>186455</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
         <x:v>12</x:v>
@@ -4017,7 +4017,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>5434921</x:v>
+        <x:v>5734396</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>12</x:v>
@@ -4028,7 +4028,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>4908725</x:v>
+        <x:v>4926513</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -4182,7 +4182,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B25" s="1">
-        <x:v>181000</x:v>
+        <x:v>186455</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>12</x:v>
@@ -4276,7 +4276,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>5434921</x:v>
+        <x:v>5734396</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -4284,7 +4284,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>4908725</x:v>
+        <x:v>4926513</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -4364,7 +4364,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>181000</x:v>
+        <x:v>186455</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
@@ -4595,7 +4595,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>5434539</x:v>
+        <x:v>5734014</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
@@ -4617,7 +4617,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>4905805</x:v>
+        <x:v>4923593</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -4804,7 +4804,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>181000</x:v>
+        <x:v>186455</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -279,6 +279,9 @@
     <x:t>FOUSHEE, VALERIE</x:t>
   </x:si>
   <x:si>
+    <x:t>THOMPSON, MIKE MR.</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00935049</x:t>
   </x:si>
   <x:si>
@@ -328,9 +331,6 @@
   </x:si>
   <x:si>
     <x:t>GALINDO, MAUREEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THOMPSON, MIKE MR.</x:t>
   </x:si>
   <x:si>
     <x:t>WIENER, SCOTT</x:t>
@@ -413,8 +413,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G68" totalsRowShown="0">
-  <x:autoFilter ref="A1:G68"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G69" totalsRowShown="0">
+  <x:autoFilter ref="A1:G69"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -778,7 +778,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G68"/>
+  <x:dimension ref="A1:G69"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1621,22 +1621,22 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="B37" s="1" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C37" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>4379243</x:v>
+        <x:v>30801</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>12</x:v>
@@ -1644,45 +1644,45 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B38" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>663879</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>91</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>1183678</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>56</x:v>
@@ -1690,10 +1690,10 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>92</x:v>
@@ -1705,30 +1705,30 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>104555</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="B41" s="1" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C41" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>3985698</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1736,22 +1736,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>4383748</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1759,13 +1759,13 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
         <x:v>79</x:v>
@@ -1774,30 +1774,30 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>1426379</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>663879</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>56</x:v>
@@ -1805,22 +1805,22 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>2335126</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>56</x:v>
@@ -1828,59 +1828,59 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>63297</x:v>
+        <x:v>2335126</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="D47" s="1" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>500000</x:v>
+        <x:v>63297</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
         <x:v>14</x:v>
@@ -1889,30 +1889,30 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>152762</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>4379246</x:v>
+        <x:v>152762</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -1920,22 +1920,22 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>3985700</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>12</x:v>
@@ -1943,36 +1943,36 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>1183678</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
         <x:v>79</x:v>
@@ -1981,21 +1981,21 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>4383749</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
         <x:v>79</x:v>
@@ -2004,21 +2004,21 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>1426379</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
         <x:v>79</x:v>
@@ -2027,30 +2027,30 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>104555</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>360170</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>12</x:v>
@@ -2064,16 +2064,16 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>5734014</x:v>
+        <x:v>360170</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>12</x:v>
@@ -2081,22 +2081,22 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>198972</x:v>
+        <x:v>5734014</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>12</x:v>
@@ -2104,45 +2104,45 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>1870</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>198972</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>56</x:v>
@@ -2150,45 +2150,45 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>253658</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>163756</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>12</x:v>
@@ -2202,7 +2202,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
         <x:v>38</x:v>
@@ -2211,53 +2211,53 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>14264</x:v>
+        <x:v>163756</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>499161</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>60000</x:v>
+        <x:v>468360</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>12</x:v>
@@ -2265,45 +2265,45 @@
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>2000000</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>2326917</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>56</x:v>
@@ -2311,47 +2311,70 @@
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>186455</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B68" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C68" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D68" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E68" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F68" s="1">
+        <x:v>186455</x:v>
+      </x:c>
+      <x:c r="G68" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:7">
+      <x:c r="A69" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B68" s="1" t="s">
+      <x:c r="B69" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C68" s="1" t="s">
+      <x:c r="C69" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D68" s="1" t="s">
+      <x:c r="D69" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="E68" s="1" t="s">
+      <x:c r="E69" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F68" s="1">
+      <x:c r="F69" s="1">
         <x:v>4923593</x:v>
       </x:c>
-      <x:c r="G68" s="1" t="s">
+      <x:c r="G69" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -2401,7 +2424,7 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>60</x:v>
@@ -2418,10 +2441,10 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>15</x:v>
@@ -2452,7 +2475,7 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>14</x:v>
@@ -2622,7 +2645,7 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>19</x:v>
@@ -2656,7 +2679,7 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>79</x:v>
@@ -2690,7 +2713,7 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>79</x:v>
@@ -2911,13 +2934,13 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>200842</x:v>
@@ -2928,13 +2951,13 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>198972</x:v>
@@ -3013,7 +3036,7 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
         <x:v>55</x:v>
@@ -3166,7 +3189,7 @@
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
         <x:v>38</x:v>
@@ -3288,7 +3311,7 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>15</x:v>
@@ -3641,7 +3664,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>200842</x:v>
@@ -3655,7 +3678,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>198972</x:v>
@@ -4069,7 +4092,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>200842</x:v>
@@ -4080,7 +4103,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>198972</x:v>
@@ -4313,7 +4336,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>399814</x:v>
@@ -4479,7 +4502,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>23</x:v>
@@ -4490,7 +4513,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>23</x:v>
@@ -4523,7 +4546,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>23</x:v>
@@ -4669,7 +4692,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>1870</x:v>
@@ -4680,7 +4703,7 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>397944</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2349,7 +2349,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>186455</x:v>
+        <x:v>195838</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
         <x:v>12</x:v>
@@ -3232,7 +3232,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="D49" s="1">
-        <x:v>186455</x:v>
+        <x:v>195838</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>12</x:v>
@@ -3891,7 +3891,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="C44" s="1">
-        <x:v>186455</x:v>
+        <x:v>195838</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
         <x:v>12</x:v>
@@ -4205,7 +4205,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B25" s="1">
-        <x:v>186455</x:v>
+        <x:v>195838</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>12</x:v>
@@ -4387,7 +4387,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>186455</x:v>
+        <x:v>195838</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
@@ -4827,7 +4827,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>186455</x:v>
+        <x:v>195838</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -325,6 +325,9 @@
   </x:si>
   <x:si>
     <x:t>CAVANAUGH, JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SHAHEEN, STEFANY</x:t>
   </x:si>
   <x:si>
     <x:t>BENNETT, REBECCA</x:t>
@@ -413,8 +416,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G69" totalsRowShown="0">
-  <x:autoFilter ref="A1:G69"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G70" totalsRowShown="0">
+  <x:autoFilter ref="A1:G70"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -429,8 +432,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E50" totalsRowShown="0">
-  <x:autoFilter ref="A1:E50"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E51" totalsRowShown="0">
+  <x:autoFilter ref="A1:E51"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -479,8 +482,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C38" totalsRowShown="0">
-  <x:autoFilter ref="A1:C38"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C39" totalsRowShown="0">
+  <x:autoFilter ref="A1:C39"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -778,7 +781,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G69"/>
+  <x:dimension ref="A1:G70"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2182,13 +2185,13 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>253658</x:v>
+        <x:v>80291</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>12</x:v>
@@ -2196,22 +2199,22 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>163756</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>12</x:v>
@@ -2225,7 +2228,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
         <x:v>38</x:v>
@@ -2234,53 +2237,53 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>14264</x:v>
+        <x:v>163756</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>468360</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>60000</x:v>
+        <x:v>468360</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>12</x:v>
@@ -2288,45 +2291,45 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>2000000</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>2326917</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
         <x:v>56</x:v>
@@ -2334,47 +2337,70 @@
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>195838</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B69" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C69" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D69" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E69" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="F69" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+      <x:c r="G69" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:7">
+      <x:c r="A70" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B69" s="1" t="s">
+      <x:c r="B70" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C69" s="1" t="s">
+      <x:c r="C70" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D69" s="1" t="s">
+      <x:c r="D70" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="E69" s="1" t="s">
+      <x:c r="E70" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F69" s="1">
-        <x:v>4923593</x:v>
-      </x:c>
-      <x:c r="G69" s="1" t="s">
+      <x:c r="F70" s="1">
+        <x:v>7354888</x:v>
+      </x:c>
+      <x:c r="G70" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -2394,7 +2420,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E50"/>
+  <x:dimension ref="A1:E51"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2458,7 +2484,7 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>29</x:v>
@@ -2526,7 +2552,7 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>17</x:v>
@@ -2841,7 +2867,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>4926131</x:v>
+        <x:v>7357426</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -3002,7 +3028,7 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
         <x:v>43</x:v>
@@ -3011,7 +3037,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>382</x:v>
+        <x:v>80291</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>12</x:v>
@@ -3019,24 +3045,24 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
         <x:v>55</x:v>
@@ -3045,32 +3071,32 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>253658</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>2326917</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
         <x:v>29</x:v>
@@ -3079,55 +3105,55 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D40" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="D42" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>382</x:v>
@@ -3138,10 +3164,10 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>11</x:v>
@@ -3155,58 +3181,58 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D45" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D46" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D47" s="1">
-        <x:v>14264</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
         <x:v>38</x:v>
@@ -3215,24 +3241,24 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D48" s="1">
-        <x:v>164138</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D49" s="1">
-        <x:v>195838</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>12</x:v>
@@ -3240,18 +3266,35 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D50" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:5">
+      <x:c r="A51" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B50" s="1" t="s">
+      <x:c r="B51" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C50" s="1" t="s">
+      <x:c r="C51" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D50" s="1">
+      <x:c r="D51" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="E50" s="1" t="s">
+      <x:c r="E51" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -3583,7 +3626,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>4926131</x:v>
+        <x:v>7357426</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -3709,7 +3752,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>2356</x:v>
+        <x:v>82647</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>12</x:v>
@@ -3888,7 +3931,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>195838</x:v>
@@ -4051,7 +4094,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>4926513</x:v>
+        <x:v>7357808</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -4117,7 +4160,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>3294</x:v>
+        <x:v>83585</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>12</x:v>
@@ -4202,7 +4245,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>195838</x:v>
@@ -4307,7 +4350,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>4926513</x:v>
+        <x:v>7357808</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -4347,7 +4390,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>3294</x:v>
+        <x:v>83585</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -4384,7 +4427,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>195838</x:v>
@@ -4414,7 +4457,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C38"/>
+  <x:dimension ref="A1:C39"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4640,7 +4683,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>4923593</x:v>
+        <x:v>7354888</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -4711,79 +4754,79 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>3294</x:v>
+        <x:v>80291</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>603658</x:v>
+        <x:v>3294</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>58441</x:v>
+        <x:v>603658</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>4653834</x:v>
+        <x:v>58441</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>382</x:v>
+        <x:v>4653834</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>-31053</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>764</x:v>
+        <x:v>-31053</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
@@ -4791,53 +4834,64 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>178402</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>39386</x:v>
+        <x:v>178402</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>-46</x:v>
+        <x:v>39386</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>195838</x:v>
+        <x:v>-46</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C38" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:3">
+      <x:c r="A39" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B38" s="1" t="s">
+      <x:c r="B39" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C38" s="1">
+      <x:c r="C39" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -114,6 +114,15 @@
     <x:t>MI</x:t>
   </x:si>
   <x:si>
+    <x:t>CAVANAUGH, JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
     <x:t>WAY, TAHESHA</x:t>
   </x:si>
   <x:si>
@@ -147,6 +156,9 @@
     <x:t>VA</x:t>
   </x:si>
   <x:si>
+    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
+  </x:si>
+  <x:si>
     <x:t>SULLIVAN, MAURA CORBY</x:t>
   </x:si>
   <x:si>
@@ -189,9 +201,6 @@
     <x:t>07</x:t>
   </x:si>
   <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
     <x:t>BOWMAN, JAMAAL</x:t>
   </x:si>
   <x:si>
@@ -270,6 +279,9 @@
     <x:t>FINE, LAURA</x:t>
   </x:si>
   <x:si>
+    <x:t>POWELL, DENISE</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00931774</x:t>
   </x:si>
   <x:si>
@@ -318,15 +330,6 @@
     <x:t>VILLEGAS, RANDY</x:t>
   </x:si>
   <x:si>
-    <x:t>POWELL, DENISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAVANAUGH, JOHN</x:t>
-  </x:si>
-  <x:si>
     <x:t>SHAHEEN, STEFANY</x:t>
   </x:si>
   <x:si>
@@ -337,9 +340,6 @@
   </x:si>
   <x:si>
     <x:t>WIENER, SCOTT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
   </x:si>
   <x:si>
     <x:t>MCADAMS, BEN</x:t>
@@ -416,8 +416,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G70" totalsRowShown="0">
-  <x:autoFilter ref="A1:G70"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G71" totalsRowShown="0">
+  <x:autoFilter ref="A1:G71"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -781,7 +781,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G70"/>
+  <x:dimension ref="A1:G71"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1012,16 +1012,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>58441</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
@@ -1032,16 +1032,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>382</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
         <x:v>12</x:v>
@@ -1058,10 +1058,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F12" s="1">
         <x:v>382</x:v>
@@ -1078,13 +1078,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F13" s="1">
         <x:v>382</x:v>
@@ -1104,10 +1104,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F14" s="1">
         <x:v>382</x:v>
@@ -1124,10 +1124,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>44</x:v>
@@ -1150,16 +1150,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>1974</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
@@ -1176,10 +1176,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>2538</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1193,16 +1193,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>2649</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>12</x:v>
@@ -1219,13 +1219,13 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>2651</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>12</x:v>
@@ -1239,16 +1239,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>938</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>12</x:v>
@@ -1256,229 +1256,229 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="F21" s="1">
-        <x:v>-9678</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>-31053</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>1239981</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>4968501</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>19</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>-6917</x:v>
+        <x:v>1239981</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>-46</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E27" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="F27" s="1">
-        <x:v>59748</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>219149</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>2326917</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>-28160</x:v>
+        <x:v>219149</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>12</x:v>
@@ -1486,45 +1486,45 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B32" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C32" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>39386</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1532,45 +1532,45 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C33" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>149773</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B34" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C34" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D34" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>500346</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1578,22 +1578,22 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>600000</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>12</x:v>
@@ -1607,16 +1607,16 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>350000</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>12</x:v>
@@ -1633,13 +1633,13 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>30801</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>12</x:v>
@@ -1647,91 +1647,91 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>4379243</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="B39" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C39" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>663879</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>1183678</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C41" s="1" t="s">
-        <x:v>93</x:v>
-      </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>104555</x:v>
+        <x:v>30801</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1739,22 +1739,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>3985698</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1762,114 +1762,114 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="B43" s="1" t="s">
+      <x:c r="C43" s="1" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="C43" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>4383748</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="B44" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>1426379</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>663879</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>2335126</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>63297</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>12</x:v>
@@ -1877,91 +1877,91 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>500000</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>152762</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>4379246</x:v>
+        <x:v>2335126</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>3985700</x:v>
+        <x:v>63297</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>12</x:v>
@@ -1969,45 +1969,45 @@
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>1183678</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>4383749</x:v>
+        <x:v>152762</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -2015,45 +2015,45 @@
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>1426379</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>104555</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>12</x:v>
@@ -2061,45 +2061,45 @@
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>360170</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>5734014</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>12</x:v>
@@ -2107,91 +2107,91 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C58" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="C58" s="1" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>198972</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>1870</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>198972</x:v>
+        <x:v>360170</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>80291</x:v>
+        <x:v>5734014</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>12</x:v>
@@ -2199,22 +2199,22 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>253658</x:v>
+        <x:v>80291</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>12</x:v>
@@ -2222,22 +2222,22 @@
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>163756</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
         <x:v>12</x:v>
@@ -2251,62 +2251,62 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>14264</x:v>
+        <x:v>163756</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>468360</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>60000</x:v>
+        <x:v>468360</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>12</x:v>
@@ -2314,93 +2314,116 @@
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
         <x:v>106</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>2000000</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>2326917</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>195838</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="F70" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+      <x:c r="G70" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:7">
+      <x:c r="A71" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B71" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C71" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D71" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E71" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F70" s="1">
+      <x:c r="F71" s="1">
         <x:v>7354888</x:v>
       </x:c>
-      <x:c r="G70" s="1" t="s">
+      <x:c r="G71" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -2450,10 +2473,10 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
         <x:v>15</x:v>
@@ -2467,10 +2490,10 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>15</x:v>
@@ -2484,7 +2507,7 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>29</x:v>
@@ -2501,7 +2524,7 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>14</x:v>
@@ -2513,7 +2536,7 @@
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
@@ -2535,10 +2558,10 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>15</x:v>
@@ -2552,7 +2575,7 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>17</x:v>
@@ -2564,7 +2587,7 @@
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
@@ -2620,10 +2643,10 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>23</x:v>
@@ -2632,15 +2655,15 @@
         <x:v>-9678</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>23</x:v>
@@ -2649,15 +2672,15 @@
         <x:v>59748</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>23</x:v>
@@ -2671,7 +2694,7 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>19</x:v>
@@ -2683,7 +2706,7 @@
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
@@ -2705,10 +2728,10 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>23</x:v>
@@ -2717,15 +2740,15 @@
         <x:v>2367356</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>23</x:v>
@@ -2734,15 +2757,15 @@
         <x:v>2852758</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>23</x:v>
@@ -2756,10 +2779,10 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>23</x:v>
@@ -2773,10 +2796,10 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="B21" s="1" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>23</x:v>
@@ -2790,47 +2813,47 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>3575107</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>579319</x:v>
@@ -2858,10 +2881,10 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>30</x:v>
@@ -2892,13 +2915,13 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>2649</x:v>
@@ -2909,30 +2932,30 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>-22643</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>2651</x:v>
@@ -2943,13 +2966,13 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>600000</x:v>
@@ -2960,30 +2983,30 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>198972</x:v>
@@ -2994,13 +3017,13 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>938</x:v>
@@ -3011,13 +3034,13 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>1974</x:v>
@@ -3028,13 +3051,13 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>80291</x:v>
@@ -3045,13 +3068,13 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>382</x:v>
@@ -3062,30 +3085,30 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>253658</x:v>
@@ -3096,30 +3119,30 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>408441</x:v>
@@ -3130,30 +3153,30 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>382</x:v>
@@ -3164,7 +3187,7 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>19</x:v>
@@ -3198,30 +3221,30 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>39386</x:v>
@@ -3232,30 +3255,30 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>164138</x:v>
@@ -3269,7 +3292,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
         <x:v>108</x:v>
@@ -3283,13 +3306,13 @@
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>382</x:v>
@@ -3340,7 +3363,7 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>15</x:v>
@@ -3354,7 +3377,7 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>15</x:v>
@@ -3391,7 +3414,7 @@
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
@@ -3410,7 +3433,7 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>15</x:v>
@@ -3433,7 +3456,7 @@
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
@@ -3480,7 +3503,7 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>23</x:v>
@@ -3489,12 +3512,12 @@
         <x:v>50070</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>23</x:v>
@@ -3517,7 +3540,7 @@
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
@@ -3536,7 +3559,7 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>23</x:v>
@@ -3545,12 +3568,12 @@
         <x:v>5220114</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>23</x:v>
@@ -3567,35 +3590,35 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>3575107</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>579319</x:v>
@@ -3620,7 +3643,7 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>30</x:v>
@@ -3648,10 +3671,10 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>2649</x:v>
@@ -3662,24 +3685,24 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>-22643</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>2651</x:v>
@@ -3690,10 +3713,10 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>600000</x:v>
@@ -3707,13 +3730,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
@@ -3721,7 +3744,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>198972</x:v>
@@ -3732,10 +3755,10 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>938</x:v>
@@ -3746,10 +3769,10 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>82647</x:v>
@@ -3760,24 +3783,24 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>253658</x:v>
@@ -3791,13 +3814,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
@@ -3805,7 +3828,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>408441</x:v>
@@ -3816,24 +3839,24 @@
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>382</x:v>
@@ -3872,24 +3895,24 @@
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>39386</x:v>
@@ -3900,24 +3923,24 @@
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>164138</x:v>
@@ -3928,7 +3951,7 @@
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>108</x:v>
@@ -3945,7 +3968,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>382</x:v>
@@ -3998,7 +4021,7 @@
         <x:v>2500000</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -4031,7 +4054,7 @@
         <x:v>6597942</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -4047,29 +4070,29 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>3575107</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>579319</x:v>
@@ -4102,7 +4125,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>2649</x:v>
@@ -4113,18 +4136,18 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>-22643</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>602651</x:v>
@@ -4135,18 +4158,18 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>198972</x:v>
@@ -4157,7 +4180,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>83585</x:v>
@@ -4168,18 +4191,18 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>4653834</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>662099</x:v>
@@ -4190,18 +4213,18 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>382</x:v>
@@ -4223,18 +4246,18 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>14218</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>203524</x:v>
@@ -4256,7 +4279,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>382</x:v>
@@ -4323,7 +4346,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>-6917</x:v>
@@ -4331,7 +4354,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>4154426</x:v>
@@ -4355,7 +4378,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>2649</x:v>
@@ -4363,7 +4386,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>-22643</x:v>
@@ -4371,7 +4394,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>602651</x:v>
@@ -4379,7 +4402,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>399814</x:v>
@@ -4387,7 +4410,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>83585</x:v>
@@ -4395,7 +4418,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>5315933</x:v>
@@ -4403,7 +4426,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>-30671</x:v>
@@ -4419,7 +4442,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>217742</x:v>
@@ -4435,7 +4458,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>382</x:v>
@@ -4479,7 +4502,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>15</x:v>
@@ -4501,7 +4524,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>15</x:v>
@@ -4512,7 +4535,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>15</x:v>
@@ -4523,7 +4546,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>15</x:v>
@@ -4545,7 +4568,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>23</x:v>
@@ -4556,7 +4579,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>23</x:v>
@@ -4578,7 +4601,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>23</x:v>
@@ -4589,7 +4612,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>23</x:v>
@@ -4600,7 +4623,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>23</x:v>
@@ -4611,7 +4634,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>23</x:v>
@@ -4622,10 +4645,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>-6917</x:v>
@@ -4633,10 +4656,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>4154426</x:v>
@@ -4655,7 +4678,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>27</x:v>
@@ -4677,7 +4700,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>30</x:v>
@@ -4691,7 +4714,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>2649</x:v>
@@ -4699,10 +4722,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>-22643</x:v>
@@ -4710,10 +4733,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>600000</x:v>
@@ -4724,7 +4747,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>2651</x:v>
@@ -4735,7 +4758,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>1870</x:v>
@@ -4743,10 +4766,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>397944</x:v>
@@ -4754,10 +4777,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>80291</x:v>
@@ -4768,7 +4791,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>3294</x:v>
@@ -4776,10 +4799,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>603658</x:v>
@@ -4790,7 +4813,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>58441</x:v>
@@ -4798,10 +4821,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>4653834</x:v>
@@ -4812,7 +4835,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>382</x:v>
@@ -4820,10 +4843,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>-31053</x:v>
@@ -4845,7 +4868,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>178402</x:v>
@@ -4853,10 +4876,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>39386</x:v>
@@ -4864,10 +4887,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>-46</x:v>
@@ -4875,7 +4898,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
         <x:v>108</x:v>
@@ -4889,7 +4912,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>382</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2214,7 +2214,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>80291</x:v>
+        <x:v>130183</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>12</x:v>
@@ -3060,7 +3060,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>80291</x:v>
+        <x:v>130183</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>12</x:v>
@@ -3775,7 +3775,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>82647</x:v>
+        <x:v>132539</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>12</x:v>
@@ -4183,7 +4183,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>83585</x:v>
+        <x:v>133477</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>12</x:v>
@@ -4413,7 +4413,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>83585</x:v>
+        <x:v>133477</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -4783,7 +4783,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>80291</x:v>
+        <x:v>130183</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -42,6 +42,39 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00528554</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RJC VICTORY FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MASSIE, THOMAS H.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRUMP, DONALD J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00710848</x:t>
   </x:si>
   <x:si>
@@ -57,9 +90,6 @@
     <x:t>PA</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
     <x:t>BAINS, JASMEET</x:t>
   </x:si>
   <x:si>
@@ -120,9 +150,6 @@
     <x:t>NE</x:t>
   </x:si>
   <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
     <x:t>WAY, TAHESHA</x:t>
   </x:si>
   <x:si>
@@ -174,9 +201,6 @@
     <x:t>STEVENS, HALEY</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
     <x:t>CRAIG, ANGIE</x:t>
   </x:si>
   <x:si>
@@ -207,15 +231,6 @@
     <x:t>16</x:t>
   </x:si>
   <x:si>
-    <x:t>MASSIE, THOMAS H.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
     <x:t>CONYEARS-ERVIN, MELISSA</x:t>
   </x:si>
   <x:si>
@@ -234,9 +249,6 @@
     <x:t>FRIEDMAN, JASON</x:t>
   </x:si>
   <x:si>
-    <x:t>GALLREIN, ED</x:t>
-  </x:si>
-  <x:si>
     <x:t>MALINOWSKI, TOM</x:t>
   </x:si>
   <x:si>
@@ -321,6 +333,15 @@
     <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
   </x:si>
   <x:si>
+    <x:t>C00684969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JDCA PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLDMAN, DANIEL</x:t>
+  </x:si>
+  <x:si>
     <x:t>BABB TOMLINSON, LAUREN</x:t>
   </x:si>
   <x:si>
@@ -346,6 +367,9 @@
   </x:si>
   <x:si>
     <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EL-SAYED, ABDUL</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -416,8 +440,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G71" totalsRowShown="0">
-  <x:autoFilter ref="A1:G71"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G78" totalsRowShown="0">
+  <x:autoFilter ref="A1:G78"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -432,8 +456,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E51" totalsRowShown="0">
-  <x:autoFilter ref="A1:E51"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E54" totalsRowShown="0">
+  <x:autoFilter ref="A1:E54"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -446,8 +470,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D45" totalsRowShown="0">
-  <x:autoFilter ref="A1:D45"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D48" totalsRowShown="0">
+  <x:autoFilter ref="A1:D48"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -459,8 +483,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C26" totalsRowShown="0">
-  <x:autoFilter ref="A1:C26"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C28" totalsRowShown="0">
+  <x:autoFilter ref="A1:C28"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -471,8 +495,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B19" totalsRowShown="0">
-  <x:autoFilter ref="A1:B19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B20" totalsRowShown="0">
+  <x:autoFilter ref="A1:B20"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -482,8 +506,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C39" totalsRowShown="0">
-  <x:autoFilter ref="A1:C39"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C42" totalsRowShown="0">
+  <x:autoFilter ref="A1:C42"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -781,7 +805,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G71"/>
+  <x:dimension ref="A1:G78"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -834,7 +858,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>382</x:v>
+        <x:v>362844</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -851,16 +875,16 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>333</x:v>
+        <x:v>3045615</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
@@ -871,223 +895,223 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
+      <x:c r="E4" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="F4" s="1">
-        <x:v>333</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>715</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>382</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>382</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>382</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>1870</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>58441</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F12" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>382</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>12</x:v>
@@ -1095,137 +1119,137 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>382</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F15" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>1000000</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F17" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>1974</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>2538</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>12</x:v>
@@ -1233,160 +1257,160 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>2651</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>938</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>-9678</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>-31053</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="F25" s="1">
-        <x:v>1239981</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>4968501</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>12</x:v>
@@ -1394,91 +1418,91 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>-6917</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>-46</x:v>
+        <x:v>1239981</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>59748</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>219149</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>12</x:v>
@@ -1486,45 +1510,45 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>2326917</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>-28160</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1532,45 +1556,45 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>-22643</x:v>
+        <x:v>219149</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>39386</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1578,45 +1602,45 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B35" s="1" t="s">
+      <x:c r="D35" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C35" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D35" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>149773</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>500346</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>12</x:v>
@@ -1624,48 +1648,48 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B37" s="1" t="s">
+      <x:c r="D37" s="1" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="C37" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D37" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>198972</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>198972</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
@@ -1679,16 +1703,16 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>600000</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
@@ -1699,19 +1723,19 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>350000</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
@@ -1722,16 +1746,16 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>30801</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1745,108 +1769,108 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>4379243</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>663879</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="C44" s="1" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>1183678</x:v>
+        <x:v>30801</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>104555</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="B46" s="1" t="s">
+      <x:c r="C46" s="1" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C46" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>3985698</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>12</x:v>
@@ -1854,22 +1878,22 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B47" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="B47" s="1" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>4383748</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>12</x:v>
@@ -1877,91 +1901,91 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="B48" s="1" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>1426379</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>663879</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>2335126</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>63297</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>12</x:v>
@@ -1969,45 +1993,45 @@
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>500000</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>152762</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -2015,22 +2039,22 @@
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>4379246</x:v>
+        <x:v>2335126</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -2038,68 +2062,68 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>3985700</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>1183678</x:v>
+        <x:v>63297</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>4383749</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>12</x:v>
@@ -2107,91 +2131,91 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>1426379</x:v>
+        <x:v>152762</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>104555</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>360170</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>5734014</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>12</x:v>
@@ -2199,45 +2223,45 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>130183</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>253658</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
         <x:v>12</x:v>
@@ -2245,25 +2269,25 @@
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>163756</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
@@ -2274,157 +2298,318 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>14264</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>468360</x:v>
+        <x:v>360170</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>60000</x:v>
+        <x:v>5734014</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>1000000</x:v>
+        <x:v>130183</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>2326917</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>195838</x:v>
+        <x:v>163756</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B71" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C71" s="1" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D71" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E71" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F71" s="1">
+        <x:v>14264</x:v>
+      </x:c>
+      <x:c r="G71" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:7">
+      <x:c r="A72" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B72" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C72" s="1" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D72" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E72" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F72" s="1">
+        <x:v>468360</x:v>
+      </x:c>
+      <x:c r="G72" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:7">
+      <x:c r="A73" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B73" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C73" s="1" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D73" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E73" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F73" s="1">
+        <x:v>60000</x:v>
+      </x:c>
+      <x:c r="G73" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:7">
+      <x:c r="A74" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B74" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C74" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D74" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E74" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F74" s="1">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="G74" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:7">
+      <x:c r="A75" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B75" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C75" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D75" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E75" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F75" s="1">
+        <x:v>2326917</x:v>
+      </x:c>
+      <x:c r="G75" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:7">
+      <x:c r="A76" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B76" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C76" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D76" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B71" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C71" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D71" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E71" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F71" s="1">
-        <x:v>7354888</x:v>
-      </x:c>
-      <x:c r="G71" s="1" t="s">
-        <x:v>12</x:v>
+      <x:c r="E76" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F76" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+      <x:c r="G76" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:7">
+      <x:c r="A77" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B77" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C77" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D77" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E77" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F77" s="1">
+        <x:v>2346358</x:v>
+      </x:c>
+      <x:c r="G77" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:7">
+      <x:c r="A78" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B78" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C78" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D78" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E78" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F78" s="1">
+        <x:v>8437450</x:v>
+      </x:c>
+      <x:c r="G78" s="1" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2443,7 +2628,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E51"/>
+  <x:dimension ref="A1:E54"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2473,424 +2658,424 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>499161</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>63297</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>60000</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>153095</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>-28160</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>333</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>715</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>8758871</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>-9678</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>59748</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>4968501</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>7971780</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>2367356</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>2852758</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>209110</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>149773</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>9267843</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>3575107</x:v>
+        <x:v>7170572</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>579319</x:v>
+        <x:v>7140550</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>5734396</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>7357426</x:v>
+        <x:v>2346358</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -2898,67 +3083,67 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>382</x:v>
+        <x:v>8439988</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>2651</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>12</x:v>
@@ -2966,50 +3151,50 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C31" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="D31" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>12</x:v>
@@ -3017,101 +3202,101 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>938</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>1974</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>130183</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>382</x:v>
+        <x:v>130183</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>253658</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>12</x:v>
@@ -3119,33 +3304,33 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D40" s="1">
-        <x:v>2326917</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>12</x:v>
@@ -3153,50 +3338,50 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D42" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D43" s="1">
-        <x:v>382</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D44" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>12</x:v>
@@ -3204,101 +3389,101 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D46" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D47" s="1">
-        <x:v>39386</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D48" s="1">
-        <x:v>14264</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D49" s="1">
-        <x:v>164138</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D50" s="1">
-        <x:v>195838</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>12</x:v>
@@ -3306,19 +3491,70 @@
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D51" s="1">
+        <x:v>164138</x:v>
+      </x:c>
+      <x:c r="E51" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:5">
+      <x:c r="A52" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B52" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C52" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D52" s="1">
+        <x:v>-62727</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:5">
+      <x:c r="A53" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B53" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C53" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D53" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+      <x:c r="E53" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:5">
+      <x:c r="A54" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B54" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C54" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D54" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="E51" s="1" t="s">
-        <x:v>12</x:v>
+      <x:c r="E54" s="1" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3337,7 +3573,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D45"/>
+  <x:dimension ref="A1:D48"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3363,293 +3599,293 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>499161</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>63297</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>60000</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>153095</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>-28160</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>333</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>715</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>8758871</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>50070</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>4968501</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>7971780</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>5220114</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>9626726</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>3575107</x:v>
+        <x:v>7170572</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>579319</x:v>
+        <x:v>7140550</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5734396</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>7357426</x:v>
+        <x:v>2346358</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -3657,55 +3893,55 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>382</x:v>
+        <x:v>8439988</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>2651</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>12</x:v>
@@ -3713,41 +3949,41 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B27" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="C27" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
         <x:v>12</x:v>
@@ -3755,55 +3991,55 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>938</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>132539</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>2326917</x:v>
+        <x:v>132539</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>253658</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
         <x:v>12</x:v>
@@ -3811,27 +4047,27 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>2326917</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
         <x:v>12</x:v>
@@ -3839,41 +4075,41 @@
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>382</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
         <x:v>12</x:v>
@@ -3881,83 +4117,83 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>39386</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>14264</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C43" s="1">
-        <x:v>164138</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C44" s="1">
-        <x:v>195838</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
         <x:v>12</x:v>
@@ -3965,16 +4201,58 @@
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C45" s="1">
+        <x:v>164138</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:4">
+      <x:c r="A46" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C46" s="1">
+        <x:v>-62727</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:4">
+      <x:c r="A47" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B47" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="C47" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:4">
+      <x:c r="A48" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C48" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="D45" s="1" t="s">
-        <x:v>12</x:v>
+      <x:c r="D48" s="1" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3993,7 +4271,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C26"/>
+  <x:dimension ref="A1:C28"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4015,109 +4293,109 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>2500000</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>747726</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>715</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>6597942</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>31325878</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>3575107</x:v>
+        <x:v>7170572</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>579319</x:v>
+        <x:v>7140550</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>5734396</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>7357808</x:v>
+        <x:v>2346358</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -4125,32 +4403,32 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>2649</x:v>
+        <x:v>8440370</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>602651</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>12</x:v>
@@ -4158,21 +4436,21 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>200842</x:v>
+        <x:v>602651</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>12</x:v>
@@ -4180,32 +4458,32 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>133477</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>4653834</x:v>
+        <x:v>133477</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>662099</x:v>
+        <x:v>4653834</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>12</x:v>
@@ -4213,21 +4491,21 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>-31053</x:v>
+        <x:v>662099</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B21" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>12</x:v>
@@ -4235,32 +4513,32 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B22" s="1">
-        <x:v>764</x:v>
+        <x:v>10382</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="1">
-        <x:v>14218</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B24" s="1">
-        <x:v>203524</x:v>
+        <x:v>14218</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>12</x:v>
@@ -4268,24 +4546,46 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B25" s="1">
-        <x:v>195838</x:v>
+        <x:v>203524</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B26" s="1">
+        <x:v>-62727</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:3">
+      <x:c r="A27" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B27" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:3">
+      <x:c r="A28" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B28" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="C26" s="1" t="s">
-        <x:v>12</x:v>
+      <x:c r="C28" s="1" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4304,7 +4604,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B19"/>
+  <x:dimension ref="A1:B20"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4322,7 +4622,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>3247726</x:v>
@@ -4330,7 +4630,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>715</x:v>
@@ -4338,7 +4638,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>37923820</x:v>
@@ -4346,7 +4646,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>-6917</x:v>
@@ -4354,15 +4654,15 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>4154426</x:v>
+        <x:v>14311122</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>5734396</x:v>
@@ -4370,15 +4670,15 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>7357808</x:v>
+        <x:v>10786728</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>2649</x:v>
@@ -4386,7 +4686,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>-22643</x:v>
@@ -4394,7 +4694,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>602651</x:v>
@@ -4402,7 +4702,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>399814</x:v>
@@ -4410,7 +4710,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>133477</x:v>
@@ -4418,7 +4718,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>5315933</x:v>
@@ -4426,15 +4726,15 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>-30671</x:v>
+        <x:v>-20671</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>764</x:v>
@@ -4442,7 +4742,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>217742</x:v>
@@ -4450,17 +4750,25 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>195838</x:v>
+        <x:v>-62727</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B19" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:2">
+      <x:c r="A20" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B20" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>
@@ -4480,7 +4788,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C39"/>
+  <x:dimension ref="A1:C42"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4502,10 +4810,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>499161</x:v>
@@ -4513,10 +4821,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>2500666</x:v>
@@ -4524,10 +4832,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>216059</x:v>
@@ -4535,10 +4843,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>60000</x:v>
@@ -4546,10 +4854,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>-28160</x:v>
@@ -4557,10 +4865,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>715</x:v>
@@ -4568,10 +4876,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>8758489</x:v>
@@ -4579,10 +4887,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>3904224</x:v>
@@ -4590,10 +4898,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>764</x:v>
@@ -4601,10 +4909,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>500346</x:v>
@@ -4612,10 +4920,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>19591653</x:v>
@@ -4623,10 +4931,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>149773</x:v>
@@ -4634,10 +4942,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>5018571</x:v>
@@ -4645,10 +4953,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>-6917</x:v>
@@ -4656,123 +4964,123 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>4154426</x:v>
+        <x:v>10156696</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>382</x:v>
+        <x:v>4154426</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>5734014</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>2920</x:v>
+        <x:v>5734014</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>7354888</x:v>
+        <x:v>2920</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>2649</x:v>
+        <x:v>10783808</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>600000</x:v>
+        <x:v>-22643</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>2651</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>1870</x:v>
+        <x:v>2651</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>397944</x:v>
+        <x:v>1870</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
@@ -4780,141 +5088,174 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>130183</x:v>
+        <x:v>397944</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>3294</x:v>
+        <x:v>130183</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>603658</x:v>
+        <x:v>3294</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>58441</x:v>
+        <x:v>603658</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>4653834</x:v>
+        <x:v>58441</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>382</x:v>
+        <x:v>4653834</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>-31053</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>764</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>178402</x:v>
+        <x:v>-31053</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>39386</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>-46</x:v>
+        <x:v>178402</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>195838</x:v>
+        <x:v>39386</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C39" s="1">
+        <x:v>-46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:3">
+      <x:c r="A40" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B39" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C39" s="1">
+      <x:c r="B40" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C40" s="1">
+        <x:v>-62727</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:3">
+      <x:c r="A41" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="C41" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:3">
+      <x:c r="A42" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B42" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C42" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -367,6 +367,9 @@
   </x:si>
   <x:si>
     <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCMORROW, MALLORY</x:t>
   </x:si>
   <x:si>
     <x:t>EL-SAYED, ABDUL</x:t>
@@ -440,8 +443,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G78" totalsRowShown="0">
-  <x:autoFilter ref="A1:G78"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G79" totalsRowShown="0">
+  <x:autoFilter ref="A1:G79"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -456,8 +459,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E54" totalsRowShown="0">
-  <x:autoFilter ref="A1:E54"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E55" totalsRowShown="0">
+  <x:autoFilter ref="A1:E55"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -506,8 +509,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C42" totalsRowShown="0">
-  <x:autoFilter ref="A1:C42"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C43" totalsRowShown="0">
+  <x:autoFilter ref="A1:C43"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -805,7 +808,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G78"/>
+  <x:dimension ref="A1:G79"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2568,10 +2571,10 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
         <x:v>116</x:v>
@@ -2583,10 +2586,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>2346358</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
@@ -2597,7 +2600,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
         <x:v>16</x:v>
@@ -2606,9 +2609,32 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="F78" s="1">
+        <x:v>2346358</x:v>
+      </x:c>
+      <x:c r="G78" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:7">
+      <x:c r="A79" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B79" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C79" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D79" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E79" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F79" s="1">
         <x:v>8437450</x:v>
       </x:c>
-      <x:c r="G78" s="1" t="s">
+      <x:c r="G79" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -2628,7 +2654,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E54"/>
+  <x:dimension ref="A1:E55"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3066,7 +3092,7 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
         <x:v>16</x:v>
@@ -3083,7 +3109,7 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>16</x:v>
@@ -3092,7 +3118,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>8439988</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
@@ -3100,16 +3126,16 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>382</x:v>
+        <x:v>8439988</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
@@ -3117,16 +3143,16 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>14</x:v>
@@ -3134,50 +3160,50 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>2651</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>14</x:v>
@@ -3185,24 +3211,24 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>32</x:v>
@@ -3211,24 +3237,24 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>938</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>14</x:v>
@@ -3239,13 +3265,13 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>1974</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>14</x:v>
@@ -3253,7 +3279,7 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
         <x:v>56</x:v>
@@ -3262,7 +3288,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>130183</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>14</x:v>
@@ -3270,7 +3296,7 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
         <x:v>56</x:v>
@@ -3279,7 +3305,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>382</x:v>
+        <x:v>130183</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>14</x:v>
@@ -3287,24 +3313,24 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
         <x:v>67</x:v>
@@ -3313,32 +3339,32 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="D40" s="1">
-        <x:v>253658</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>2326917</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
         <x:v>39</x:v>
@@ -3347,24 +3373,24 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="D42" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D43" s="1">
-        <x:v>10000</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>14</x:v>
@@ -3372,47 +3398,47 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="D44" s="1">
-        <x:v>-31053</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="D45" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>382</x:v>
@@ -3423,10 +3449,10 @@
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>22</x:v>
@@ -3440,58 +3466,58 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D48" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="D49" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="D50" s="1">
-        <x:v>14264</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
         <x:v>50</x:v>
@@ -3500,24 +3526,24 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="D51" s="1">
-        <x:v>164138</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D52" s="1">
-        <x:v>-62727</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
         <x:v>14</x:v>
@@ -3525,16 +3551,16 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D53" s="1">
-        <x:v>195838</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
         <x:v>14</x:v>
@@ -3542,18 +3568,35 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B54" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C54" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D54" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+      <x:c r="E54" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:5">
+      <x:c r="A55" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B54" s="1" t="s">
+      <x:c r="B55" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C54" s="1" t="s">
+      <x:c r="C55" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D54" s="1">
+      <x:c r="D55" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="E54" s="1" t="s">
+      <x:c r="E55" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -3899,7 +3942,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>8439988</x:v>
+        <x:v>8489988</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>14</x:v>
@@ -4406,7 +4449,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>8440370</x:v>
+        <x:v>8490370</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>14</x:v>
@@ -4673,7 +4716,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>10786728</x:v>
+        <x:v>10836728</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -4788,7 +4831,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C42"/>
+  <x:dimension ref="A1:C43"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -5019,57 +5062,57 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>10783808</x:v>
+        <x:v>50000</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>2649</x:v>
+        <x:v>10783808</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2649</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>600000</x:v>
+        <x:v>-22643</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>2651</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -5077,120 +5120,120 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>1870</x:v>
+        <x:v>2651</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>397944</x:v>
+        <x:v>1870</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>130183</x:v>
+        <x:v>397944</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>3294</x:v>
+        <x:v>130183</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>603658</x:v>
+        <x:v>3294</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>58441</x:v>
+        <x:v>603658</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>4653834</x:v>
+        <x:v>58441</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>382</x:v>
+        <x:v>4653834</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>10000</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>-31053</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>764</x:v>
+        <x:v>-31053</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
@@ -5198,64 +5241,75 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>178402</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>39386</x:v>
+        <x:v>178402</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>-46</x:v>
+        <x:v>39386</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>-62727</x:v>
+        <x:v>-46</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>195838</x:v>
+        <x:v>-62727</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B42" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="C42" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:3">
+      <x:c r="A43" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B42" s="1" t="s">
+      <x:c r="B43" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C42" s="1">
+      <x:c r="C43" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -340,6 +340,9 @@
   </x:si>
   <x:si>
     <x:t>GOLDMAN, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BELL, WESLEY</x:t>
   </x:si>
   <x:si>
     <x:t>BABB TOMLINSON, LAUREN</x:t>
@@ -443,8 +446,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G79" totalsRowShown="0">
-  <x:autoFilter ref="A1:G79"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G80" totalsRowShown="0">
+  <x:autoFilter ref="A1:G80"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -459,8 +462,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E55" totalsRowShown="0">
-  <x:autoFilter ref="A1:E55"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E56" totalsRowShown="0">
+  <x:autoFilter ref="A1:E56"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -473,8 +476,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D48" totalsRowShown="0">
-  <x:autoFilter ref="A1:D48"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D49" totalsRowShown="0">
+  <x:autoFilter ref="A1:D49"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -486,8 +489,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C28" totalsRowShown="0">
-  <x:autoFilter ref="A1:C28"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C29" totalsRowShown="0">
+  <x:autoFilter ref="A1:C29"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -808,7 +811,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G79"/>
+  <x:dimension ref="A1:G80"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2088,22 +2091,22 @@
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
         <x:v>107</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>63297</x:v>
+        <x:v>542439</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>14</x:v>
@@ -2111,36 +2114,36 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D57" s="1" t="s">
         <x:v>109</x:v>
-      </x:c>
-      <x:c r="D57" s="1" t="s">
-        <x:v>24</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>500000</x:v>
+        <x:v>63297</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
         <x:v>24</x:v>
@@ -2149,30 +2152,30 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>152762</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>4379246</x:v>
+        <x:v>152762</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>14</x:v>
@@ -2180,22 +2183,22 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>3985700</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>14</x:v>
@@ -2203,36 +2206,36 @@
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>1183678</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
         <x:v>86</x:v>
@@ -2241,10 +2244,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>4383749</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
@@ -2255,7 +2258,7 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
         <x:v>86</x:v>
@@ -2264,21 +2267,21 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>1426379</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
         <x:v>86</x:v>
@@ -2287,30 +2290,30 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>104555</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>3515616</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>14</x:v>
@@ -2318,10 +2321,10 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
         <x:v>13</x:v>
@@ -2333,7 +2336,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>360170</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>14</x:v>
@@ -2347,16 +2350,16 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>5734014</x:v>
+        <x:v>360170</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
         <x:v>14</x:v>
@@ -2364,22 +2367,22 @@
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>130183</x:v>
+        <x:v>5734014</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
         <x:v>14</x:v>
@@ -2396,13 +2399,13 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>253658</x:v>
+        <x:v>130183</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
         <x:v>14</x:v>
@@ -2410,22 +2413,22 @@
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>163756</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
         <x:v>14</x:v>
@@ -2439,7 +2442,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
         <x:v>50</x:v>
@@ -2448,53 +2451,53 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>14264</x:v>
+        <x:v>163756</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>468360</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>60000</x:v>
+        <x:v>468360</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
         <x:v>14</x:v>
@@ -2502,45 +2505,45 @@
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>1000000</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>2326917</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
         <x:v>12</x:v>
@@ -2548,45 +2551,45 @@
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>195838</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D77" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E77" s="1" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="D77" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E77" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="F77" s="1">
-        <x:v>50000</x:v>
+        <x:v>195838</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>14</x:v>
@@ -2594,10 +2597,10 @@
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
         <x:v>117</x:v>
@@ -2609,10 +2612,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>2346358</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
@@ -2623,7 +2626,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
         <x:v>16</x:v>
@@ -2632,9 +2635,32 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>8437450</x:v>
+        <x:v>2350379</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:7">
+      <x:c r="A80" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B80" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C80" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D80" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E80" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F80" s="1">
+        <x:v>8609875</x:v>
+      </x:c>
+      <x:c r="G80" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -2654,7 +2680,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E55"/>
+  <x:dimension ref="A1:E56"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2701,10 +2727,10 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>25</x:v>
@@ -2718,7 +2744,7 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>39</x:v>
@@ -2735,7 +2761,7 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>24</x:v>
@@ -3092,7 +3118,7 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
         <x:v>16</x:v>
@@ -3101,7 +3127,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>2346358</x:v>
+        <x:v>2350379</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -3109,7 +3135,7 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>16</x:v>
@@ -3135,7 +3161,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>8439988</x:v>
+        <x:v>8612413</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
@@ -3194,16 +3220,16 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>2651</x:v>
+        <x:v>542439</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>14</x:v>
@@ -3211,16 +3237,16 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>14</x:v>
@@ -3228,24 +3254,24 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>32</x:v>
@@ -3254,24 +3280,24 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>938</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>14</x:v>
@@ -3282,13 +3308,13 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>1974</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>14</x:v>
@@ -3296,7 +3322,7 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
         <x:v>56</x:v>
@@ -3305,7 +3331,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>130183</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>14</x:v>
@@ -3313,7 +3339,7 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
         <x:v>56</x:v>
@@ -3322,7 +3348,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>382</x:v>
+        <x:v>130183</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>14</x:v>
@@ -3330,24 +3356,24 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D40" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
         <x:v>67</x:v>
@@ -3356,32 +3382,32 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>253658</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="D42" s="1">
-        <x:v>2326917</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
         <x:v>39</x:v>
@@ -3390,24 +3416,24 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="D43" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D44" s="1">
-        <x:v>10000</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>14</x:v>
@@ -3415,47 +3441,47 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="D45" s="1">
-        <x:v>-31053</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="D46" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>382</x:v>
@@ -3466,10 +3492,10 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>22</x:v>
@@ -3483,58 +3509,58 @@
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D49" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="D50" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="D51" s="1">
-        <x:v>14264</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
         <x:v>50</x:v>
@@ -3543,24 +3569,24 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="D52" s="1">
-        <x:v>164138</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D53" s="1">
-        <x:v>-62727</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
         <x:v>14</x:v>
@@ -3568,16 +3594,16 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D54" s="1">
-        <x:v>195838</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
         <x:v>14</x:v>
@@ -3585,18 +3611,35 @@
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B55" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C55" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D55" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+      <x:c r="E55" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:5">
+      <x:c r="A56" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B55" s="1" t="s">
+      <x:c r="B56" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C55" s="1" t="s">
+      <x:c r="C56" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D55" s="1">
+      <x:c r="D56" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="E55" s="1" t="s">
+      <x:c r="E56" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -3616,7 +3659,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D48"/>
+  <x:dimension ref="A1:D49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3656,7 +3699,7 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>25</x:v>
@@ -3928,7 +3971,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>2346358</x:v>
+        <x:v>2350379</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -3942,7 +3985,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>8489988</x:v>
+        <x:v>8662413</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>14</x:v>
@@ -3992,13 +4035,13 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>2651</x:v>
+        <x:v>542439</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>14</x:v>
@@ -4006,13 +4049,13 @@
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
         <x:v>14</x:v>
@@ -4020,16 +4063,16 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
@@ -4040,21 +4083,21 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>938</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>14</x:v>
@@ -4062,13 +4105,13 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>132539</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
         <x:v>14</x:v>
@@ -4076,16 +4119,16 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>2326917</x:v>
+        <x:v>132539</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
@@ -4096,24 +4139,24 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>253658</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>2326917</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
@@ -4124,21 +4167,21 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>10000</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
         <x:v>14</x:v>
@@ -4146,38 +4189,38 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>-31053</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>382</x:v>
@@ -4188,7 +4231,7 @@
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
         <x:v>22</x:v>
@@ -4202,44 +4245,44 @@
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="C43" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="C44" s="1">
-        <x:v>14264</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
@@ -4250,21 +4293,21 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C45" s="1">
-        <x:v>164138</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C46" s="1">
-        <x:v>-62727</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
         <x:v>14</x:v>
@@ -4272,13 +4315,13 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C47" s="1">
-        <x:v>195838</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
         <x:v>14</x:v>
@@ -4286,15 +4329,29 @@
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C48" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:4">
+      <x:c r="A49" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B48" s="1" t="s">
+      <x:c r="B49" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C48" s="1">
+      <x:c r="C49" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="D48" s="1" t="s">
+      <x:c r="D49" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -4314,7 +4371,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C28"/>
+  <x:dimension ref="A1:C29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4438,7 +4495,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>2346358</x:v>
+        <x:v>2350379</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -4449,7 +4506,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>8490370</x:v>
+        <x:v>8662795</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>14</x:v>
@@ -4479,10 +4536,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>602651</x:v>
+        <x:v>542439</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>14</x:v>
@@ -4490,13 +4547,13 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>200842</x:v>
+        <x:v>602651</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -4504,18 +4561,18 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>133477</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>14</x:v>
@@ -4523,13 +4580,13 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>4653834</x:v>
+        <x:v>133477</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -4537,21 +4594,21 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>662099</x:v>
+        <x:v>4653834</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B21" s="1">
-        <x:v>-31053</x:v>
+        <x:v>662099</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
@@ -4559,18 +4616,18 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B22" s="1">
-        <x:v>10382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B23" s="1">
-        <x:v>764</x:v>
+        <x:v>10382</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>14</x:v>
@@ -4578,13 +4635,13 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B24" s="1">
-        <x:v>14218</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -4592,18 +4649,18 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B25" s="1">
-        <x:v>203524</x:v>
+        <x:v>14218</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B26" s="1">
-        <x:v>-62727</x:v>
+        <x:v>203524</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>14</x:v>
@@ -4611,10 +4668,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B27" s="1">
-        <x:v>195838</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>14</x:v>
@@ -4622,12 +4679,23 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B28" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:3">
+      <x:c r="A29" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B28" s="1">
+      <x:c r="B29" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="C28" s="1" t="s">
+      <x:c r="C29" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -4716,7 +4784,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>10836728</x:v>
+        <x:v>11013174</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -4732,7 +4800,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>-22643</x:v>
+        <x:v>519796</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -4801,7 +4869,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>195838</x:v>
@@ -5079,7 +5147,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>10783808</x:v>
+        <x:v>10960254</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -5101,7 +5169,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>-22643</x:v>
+        <x:v>519796</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -5296,7 +5364,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>195838</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -282,6 +282,9 @@
     <x:t>09</x:t>
   </x:si>
   <x:si>
+    <x:t>WIENER, SCOTT</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00863472</x:t>
   </x:si>
   <x:si>
@@ -361,9 +364,6 @@
   </x:si>
   <x:si>
     <x:t>GALINDO, MAUREEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WIENER, SCOTT</x:t>
   </x:si>
   <x:si>
     <x:t>MCADAMS, BEN</x:t>
@@ -1700,22 +1700,22 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B39" s="1" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C39" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>500346</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>14</x:v>
@@ -1723,22 +1723,22 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>90</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>198972</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>14</x:v>
@@ -1746,13 +1746,13 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
         <x:v>32</x:v>
@@ -1764,50 +1764,50 @@
         <x:v>198972</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>600000</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>350000</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>14</x:v>
@@ -1815,22 +1815,22 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>30801</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>14</x:v>
@@ -1838,22 +1838,22 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="B45" s="1" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C45" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>4379243</x:v>
+        <x:v>30801</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>14</x:v>
@@ -1861,45 +1861,45 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="B46" s="1" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>663879</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>1183678</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>12</x:v>
@@ -1907,10 +1907,10 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>101</x:v>
@@ -1922,30 +1922,30 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>104555</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="B49" s="1" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C49" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>3985698</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>14</x:v>
@@ -1953,22 +1953,22 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>4383748</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>14</x:v>
@@ -1976,13 +1976,13 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
         <x:v>86</x:v>
@@ -1991,30 +1991,30 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>1426379</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>663879</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>12</x:v>
@@ -2022,22 +2022,22 @@
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>3232621</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -2045,10 +2045,10 @@
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
         <x:v>9</x:v>
@@ -2060,7 +2060,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>2335126</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -2068,45 +2068,45 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>10000</x:v>
+        <x:v>2335126</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
         <x:v>107</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>542439</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>14</x:v>
@@ -2114,22 +2114,22 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
         <x:v>108</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>63297</x:v>
+        <x:v>542439</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>14</x:v>
@@ -2137,36 +2137,36 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D58" s="1" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="D58" s="1" t="s">
-        <x:v>24</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>500000</x:v>
+        <x:v>63297</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
         <x:v>24</x:v>
@@ -2175,30 +2175,30 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>152762</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>4379246</x:v>
+        <x:v>152762</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>14</x:v>
@@ -2206,22 +2206,22 @@
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>3985700</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>14</x:v>
@@ -2229,36 +2229,36 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>1183678</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
         <x:v>86</x:v>
@@ -2267,21 +2267,21 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>4383749</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
         <x:v>86</x:v>
@@ -2290,21 +2290,21 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>1426379</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
         <x:v>86</x:v>
@@ -2313,30 +2313,30 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>104555</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>3515616</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>14</x:v>
@@ -2344,10 +2344,10 @@
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
         <x:v>13</x:v>
@@ -2359,7 +2359,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>360170</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
         <x:v>14</x:v>
@@ -2373,16 +2373,16 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>5734014</x:v>
+        <x:v>360170</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
         <x:v>14</x:v>
@@ -2390,22 +2390,22 @@
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>130183</x:v>
+        <x:v>5734014</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
         <x:v>14</x:v>
@@ -2413,22 +2413,22 @@
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
         <x:v>112</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>253658</x:v>
+        <x:v>130183</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
         <x:v>14</x:v>
@@ -2436,22 +2436,22 @@
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>163756</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>14</x:v>
@@ -2465,7 +2465,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
         <x:v>50</x:v>
@@ -2474,53 +2474,53 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>14264</x:v>
+        <x:v>163756</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>468360</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>60000</x:v>
+        <x:v>468360</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
         <x:v>14</x:v>
@@ -2574,10 +2574,10 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
         <x:v>115</x:v>
@@ -2710,7 +2710,7 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>10</x:v>
@@ -2727,10 +2727,10 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>25</x:v>
@@ -2744,7 +2744,7 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>39</x:v>
@@ -2761,7 +2761,7 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>24</x:v>
@@ -2931,7 +2931,7 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>29</x:v>
@@ -2965,7 +2965,7 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>86</x:v>
@@ -2999,7 +2999,7 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>86</x:v>
@@ -3033,7 +3033,7 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>86</x:v>
@@ -3220,7 +3220,7 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>56</x:v>
@@ -3254,7 +3254,7 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>10</x:v>
@@ -3288,7 +3288,7 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
         <x:v>32</x:v>
@@ -3339,7 +3339,7 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
         <x:v>56</x:v>
@@ -3390,7 +3390,7 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
         <x:v>67</x:v>
@@ -3441,7 +3441,7 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
         <x:v>21</x:v>
@@ -3560,7 +3560,7 @@
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
         <x:v>50</x:v>
@@ -3699,7 +3699,7 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>25</x:v>
@@ -4921,7 +4921,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>25</x:v>
@@ -4943,7 +4943,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>25</x:v>
@@ -4987,7 +4987,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>33</x:v>
@@ -4998,7 +4998,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>33</x:v>
@@ -5020,7 +5020,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>33</x:v>
@@ -5031,7 +5031,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>33</x:v>
@@ -5174,7 +5174,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>63</x:v>
@@ -5207,7 +5207,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>42</x:v>
@@ -5218,7 +5218,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>57</x:v>
@@ -5240,7 +5240,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>44</x:v>
@@ -5284,7 +5284,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>47</x:v>
@@ -5361,7 +5361,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
         <x:v>116</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2658,7 +2658,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>8609875</x:v>
+        <x:v>9232574</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
         <x:v>14</x:v>
@@ -3161,7 +3161,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>8612413</x:v>
+        <x:v>9235112</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
@@ -3985,7 +3985,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>8662413</x:v>
+        <x:v>9285112</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>14</x:v>
@@ -4506,7 +4506,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>8662795</x:v>
+        <x:v>9285494</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>14</x:v>
@@ -4784,7 +4784,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>11013174</x:v>
+        <x:v>11635873</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -5147,7 +5147,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>10960254</x:v>
+        <x:v>11582953</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2428,7 +2428,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>130183</x:v>
+        <x:v>180941</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
         <x:v>14</x:v>
@@ -2635,7 +2635,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>2350379</x:v>
+        <x:v>5654811</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
         <x:v>12</x:v>
@@ -3127,7 +3127,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>2350379</x:v>
+        <x:v>5654811</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -3348,7 +3348,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>130183</x:v>
+        <x:v>180941</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>14</x:v>
@@ -3971,7 +3971,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>2350379</x:v>
+        <x:v>5654811</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -4125,7 +4125,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>132539</x:v>
+        <x:v>183297</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
         <x:v>14</x:v>
@@ -4495,7 +4495,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>2350379</x:v>
+        <x:v>5654811</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -4583,7 +4583,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>133477</x:v>
+        <x:v>184235</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>14</x:v>
@@ -4784,7 +4784,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>11635873</x:v>
+        <x:v>14940305</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -4824,7 +4824,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>133477</x:v>
+        <x:v>184235</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -5147,7 +5147,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>11582953</x:v>
+        <x:v>14887385</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -5224,7 +5224,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>130183</x:v>
+        <x:v>180941</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -446,8 +446,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G80" totalsRowShown="0">
-  <x:autoFilter ref="A1:G80"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G81" totalsRowShown="0">
+  <x:autoFilter ref="A1:G81"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -811,7 +811,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G80"/>
+  <x:dimension ref="A1:G81"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2129,7 +2129,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>542439</x:v>
+        <x:v>628944</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>14</x:v>
@@ -2557,16 +2557,16 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>2326917</x:v>
+        <x:v>510074</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>12</x:v>
@@ -2574,45 +2574,45 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>195838</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>50000</x:v>
+        <x:v>195838</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
         <x:v>14</x:v>
@@ -2620,13 +2620,13 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
         <x:v>16</x:v>
@@ -2635,10 +2635,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>5654811</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
@@ -2649,7 +2649,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
         <x:v>16</x:v>
@@ -2658,9 +2658,32 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>9232574</x:v>
+        <x:v>5709131</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:7">
+      <x:c r="A81" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B81" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C81" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D81" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E81" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F81" s="1">
+        <x:v>9262703</x:v>
+      </x:c>
+      <x:c r="G81" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -3127,7 +3150,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>5654811</x:v>
+        <x:v>5709131</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -3161,7 +3184,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>9235112</x:v>
+        <x:v>9265241</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
@@ -3212,7 +3235,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>-22643</x:v>
+        <x:v>487431</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>12</x:v>
@@ -3229,7 +3252,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>542439</x:v>
+        <x:v>628944</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>14</x:v>
@@ -3971,7 +3994,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>5654811</x:v>
+        <x:v>5709131</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -3985,7 +4008,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>9285112</x:v>
+        <x:v>9315241</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>14</x:v>
@@ -4027,7 +4050,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>-22643</x:v>
+        <x:v>487431</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>12</x:v>
@@ -4041,7 +4064,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>542439</x:v>
+        <x:v>628944</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>14</x:v>
@@ -4495,7 +4518,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>5654811</x:v>
+        <x:v>5709131</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -4506,7 +4529,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>9285494</x:v>
+        <x:v>9315623</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>14</x:v>
@@ -4528,7 +4551,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>-22643</x:v>
+        <x:v>487431</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>12</x:v>
@@ -4539,7 +4562,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>542439</x:v>
+        <x:v>628944</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>14</x:v>
@@ -4784,7 +4807,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>14940305</x:v>
+        <x:v>15024754</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -4800,7 +4823,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>519796</x:v>
+        <x:v>1116375</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -5147,7 +5170,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>14887385</x:v>
+        <x:v>14971834</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -5169,7 +5192,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>519796</x:v>
+        <x:v>1116375</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -446,8 +446,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G81" totalsRowShown="0">
-  <x:autoFilter ref="A1:G81"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G80" totalsRowShown="0">
+  <x:autoFilter ref="A1:G80"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -811,7 +811,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G81"/>
+  <x:dimension ref="A1:G80"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1462,7 +1462,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>1239981</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>12</x:v>
@@ -1577,7 +1577,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>219149</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>14</x:v>
@@ -1591,19 +1591,19 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>2326917</x:v>
+        <x:v>1238800</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
@@ -1614,19 +1614,19 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>-28160</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
@@ -1637,42 +1637,42 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>-22643</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>39386</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
@@ -1683,16 +1683,16 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>149773</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>14</x:v>
@@ -1706,16 +1706,16 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>60000</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>14</x:v>
@@ -1723,22 +1723,22 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>500346</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>14</x:v>
@@ -1752,16 +1752,16 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>198972</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>14</x:v>
@@ -1775,7 +1775,7 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
         <x:v>32</x:v>
@@ -1787,30 +1787,30 @@
         <x:v>198972</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>600000</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
@@ -1821,16 +1821,16 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>350000</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>14</x:v>
@@ -1844,16 +1844,16 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>30801</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>14</x:v>
@@ -1861,22 +1861,22 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>4379243</x:v>
+        <x:v>30801</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>14</x:v>
@@ -1884,25 +1884,25 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>663879</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
@@ -1913,16 +1913,16 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>1183678</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>12</x:v>
@@ -1936,7 +1936,7 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
         <x:v>86</x:v>
@@ -1945,30 +1945,30 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>104555</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>3985698</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>14</x:v>
@@ -1982,16 +1982,16 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>4383748</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>14</x:v>
@@ -2005,7 +2005,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
         <x:v>86</x:v>
@@ -2014,30 +2014,30 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>1426379</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>663879</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -2045,22 +2045,22 @@
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>3232621</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -2068,10 +2068,10 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
         <x:v>9</x:v>
@@ -2083,7 +2083,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>2335126</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>12</x:v>
@@ -2373,16 +2373,16 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>360170</x:v>
+        <x:v>4495214</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
         <x:v>14</x:v>
@@ -2390,22 +2390,22 @@
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>5734014</x:v>
+        <x:v>227823</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
         <x:v>14</x:v>
@@ -2419,16 +2419,16 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>180941</x:v>
+        <x:v>253658</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
         <x:v>14</x:v>
@@ -2436,22 +2436,22 @@
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>253658</x:v>
+        <x:v>163756</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>14</x:v>
@@ -2465,7 +2465,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
         <x:v>50</x:v>
@@ -2474,76 +2474,76 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>163756</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>14264</x:v>
+        <x:v>468360</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>468360</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>1000000</x:v>
+        <x:v>510074</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
         <x:v>12</x:v>
@@ -2557,16 +2557,16 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>510074</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>12</x:v>
@@ -2574,45 +2574,45 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>2326917</x:v>
+        <x:v>195838</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>195838</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
         <x:v>14</x:v>
@@ -2620,13 +2620,13 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
         <x:v>16</x:v>
@@ -2635,10 +2635,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>50000</x:v>
+        <x:v>5709131</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
@@ -2649,7 +2649,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
         <x:v>16</x:v>
@@ -2658,32 +2658,9 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>5709131</x:v>
+        <x:v>9262703</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" spans="1:7">
-      <x:c r="A81" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B81" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C81" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D81" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E81" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F81" s="1">
-        <x:v>9262703</x:v>
-      </x:c>
-      <x:c r="G81" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -3371,7 +3348,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>180941</x:v>
+        <x:v>227823</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>14</x:v>
@@ -4148,7 +4125,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>183297</x:v>
+        <x:v>230179</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
         <x:v>14</x:v>
@@ -4606,7 +4583,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>184235</x:v>
+        <x:v>231117</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>14</x:v>
@@ -4847,7 +4824,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>184235</x:v>
+        <x:v>231117</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -5247,7 +5224,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>180941</x:v>
+        <x:v>227823</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -446,8 +446,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G80" totalsRowShown="0">
-  <x:autoFilter ref="A1:G80"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G81" totalsRowShown="0">
+  <x:autoFilter ref="A1:G81"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -811,7 +811,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G80"/>
+  <x:dimension ref="A1:G81"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2543,7 +2543,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>510074</x:v>
+        <x:v>1116191</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
         <x:v>12</x:v>
@@ -2635,7 +2635,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>5709131</x:v>
+        <x:v>9696759</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
         <x:v>12</x:v>
@@ -2643,10 +2643,10 @@
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
         <x:v>59</x:v>
@@ -2658,9 +2658,32 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>9262703</x:v>
+        <x:v>31115</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:7">
+      <x:c r="A81" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B81" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C81" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D81" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E81" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F81" s="1">
+        <x:v>9772366</x:v>
+      </x:c>
+      <x:c r="G81" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -3127,7 +3150,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>5709131</x:v>
+        <x:v>9696759</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -3161,7 +3184,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>9265241</x:v>
+        <x:v>9806019</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
@@ -3212,7 +3235,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>487431</x:v>
+        <x:v>1093548</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>12</x:v>
@@ -3971,7 +3994,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>5709131</x:v>
+        <x:v>9696759</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -3985,7 +4008,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>9315241</x:v>
+        <x:v>9856019</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>14</x:v>
@@ -4027,7 +4050,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>487431</x:v>
+        <x:v>1093548</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>12</x:v>
@@ -4495,7 +4518,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>5709131</x:v>
+        <x:v>9696759</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -4506,7 +4529,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>9315623</x:v>
+        <x:v>9856401</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>14</x:v>
@@ -4528,7 +4551,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>487431</x:v>
+        <x:v>1093548</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>12</x:v>
@@ -4784,7 +4807,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>15024754</x:v>
+        <x:v>19553160</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -4800,7 +4823,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>1116375</x:v>
+        <x:v>1722492</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -5125,7 +5148,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>2920</x:v>
+        <x:v>34035</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -5147,7 +5170,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>14971834</x:v>
+        <x:v>19469125</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -5169,7 +5192,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>1116375</x:v>
+        <x:v>1722492</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -446,8 +446,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G81" totalsRowShown="0">
-  <x:autoFilter ref="A1:G81"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G82" totalsRowShown="0">
+  <x:autoFilter ref="A1:G82"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -512,8 +512,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C43" totalsRowShown="0">
-  <x:autoFilter ref="A1:C43"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C44" totalsRowShown="0">
+  <x:autoFilter ref="A1:C44"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -811,7 +811,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G81"/>
+  <x:dimension ref="A1:G82"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2405,7 +2405,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>227823</x:v>
+        <x:v>409773</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
         <x:v>14</x:v>
@@ -2543,7 +2543,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>1116191</x:v>
+        <x:v>1177753</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
         <x:v>12</x:v>
@@ -2635,7 +2635,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>9696759</x:v>
+        <x:v>9760810</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
         <x:v>12</x:v>
@@ -2643,10 +2643,10 @@
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
         <x:v>59</x:v>
@@ -2658,7 +2658,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>31115</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
         <x:v>14</x:v>
@@ -2666,10 +2666,10 @@
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
         <x:v>59</x:v>
@@ -2681,9 +2681,32 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>9772366</x:v>
+        <x:v>31115</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:7">
+      <x:c r="A82" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B82" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C82" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D82" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E82" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F82" s="1">
+        <x:v>9888936</x:v>
+      </x:c>
+      <x:c r="G82" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -3150,7 +3173,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>9696759</x:v>
+        <x:v>9760810</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -3184,7 +3207,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>9806019</x:v>
+        <x:v>9932589</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
@@ -3235,7 +3258,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>1093548</x:v>
+        <x:v>1155110</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>12</x:v>
@@ -3371,7 +3394,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>227823</x:v>
+        <x:v>409773</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>14</x:v>
@@ -3994,7 +4017,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>9696759</x:v>
+        <x:v>9760810</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -4008,7 +4031,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>9856019</x:v>
+        <x:v>9982589</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>14</x:v>
@@ -4050,7 +4073,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>1093548</x:v>
+        <x:v>1155110</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>12</x:v>
@@ -4148,7 +4171,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>230179</x:v>
+        <x:v>412129</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
         <x:v>14</x:v>
@@ -4518,7 +4541,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>9696759</x:v>
+        <x:v>9760810</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -4529,7 +4552,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>9856401</x:v>
+        <x:v>9982971</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>14</x:v>
@@ -4551,7 +4574,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>1093548</x:v>
+        <x:v>1155110</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>12</x:v>
@@ -4606,7 +4629,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>231117</x:v>
+        <x:v>413067</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>14</x:v>
@@ -4807,7 +4830,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>19553160</x:v>
+        <x:v>19743781</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -4823,7 +4846,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>1722492</x:v>
+        <x:v>1784054</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -4847,7 +4870,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>231117</x:v>
+        <x:v>413067</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -4922,7 +4945,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C43"/>
+  <x:dimension ref="A1:C44"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -5164,57 +5187,57 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>19469125</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>2649</x:v>
+        <x:v>19649746</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>1722492</x:v>
+        <x:v>2649</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>600000</x:v>
+        <x:v>1784054</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>2651</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
@@ -5222,120 +5245,120 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>1870</x:v>
+        <x:v>2651</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>397944</x:v>
+        <x:v>1870</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>227823</x:v>
+        <x:v>397944</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>3294</x:v>
+        <x:v>409773</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>603658</x:v>
+        <x:v>3294</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>58441</x:v>
+        <x:v>603658</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>4653834</x:v>
+        <x:v>58441</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>382</x:v>
+        <x:v>4653834</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>10000</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>-31053</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>764</x:v>
+        <x:v>-31053</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
@@ -5343,64 +5366,75 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>178402</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>39386</x:v>
+        <x:v>178402</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>-46</x:v>
+        <x:v>39386</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>-62727</x:v>
+        <x:v>-46</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>195838</x:v>
+        <x:v>-62727</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C43" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:3">
+      <x:c r="A44" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B43" s="1" t="s">
+      <x:c r="B44" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C43" s="1">
+      <x:c r="C44" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -90,15 +90,18 @@
     <x:t>PA</x:t>
   </x:si>
   <x:si>
+    <x:t>VILLEGAS, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
     <x:t>BAINS, JASMEET</x:t>
   </x:si>
   <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
     <x:t>VON WILPERT, MARNI</x:t>
   </x:si>
   <x:si>
@@ -177,6 +180,9 @@
     <x:t>TX</x:t>
   </x:si>
   <x:si>
+    <x:t>GALINDO, MAUREEN</x:t>
+  </x:si>
+  <x:si>
     <x:t>LURIA, ELAINE</x:t>
   </x:si>
   <x:si>
@@ -291,6 +297,12 @@
     <x:t>EDW ACTION FUND</x:t>
   </x:si>
   <x:si>
+    <x:t>BABB TOMLINSON, LAUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
     <x:t>FINE, LAURA</x:t>
   </x:si>
   <x:si>
@@ -306,6 +318,9 @@
     <x:t>FOUSHEE, VALERIE</x:t>
   </x:si>
   <x:si>
+    <x:t>BENNETT, REBECCA</x:t>
+  </x:si>
+  <x:si>
     <x:t>THOMPSON, MIKE MR.</x:t>
   </x:si>
   <x:si>
@@ -348,22 +363,7 @@
     <x:t>BELL, WESLEY</x:t>
   </x:si>
   <x:si>
-    <x:t>BABB TOMLINSON, LAUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VILLEGAS, RANDY</x:t>
-  </x:si>
-  <x:si>
     <x:t>SHAHEEN, STEFANY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BENNETT, REBECCA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALINDO, MAUREEN</x:t>
   </x:si>
   <x:si>
     <x:t>MCADAMS, BEN</x:t>
@@ -446,8 +446,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G82" totalsRowShown="0">
-  <x:autoFilter ref="A1:G82"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G79" totalsRowShown="0">
+  <x:autoFilter ref="A1:G79"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -811,7 +811,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G82"/>
+  <x:dimension ref="A1:G79"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -956,10 +956,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>333</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
@@ -973,7 +973,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>25</x:v>
@@ -993,16 +993,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>715</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
         <x:v>14</x:v>
@@ -1016,16 +1016,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="F9" s="1">
-        <x:v>382</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>14</x:v>
@@ -1039,13 +1039,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
         <x:v>34</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>382</x:v>
@@ -1065,10 +1065,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>382</x:v>
@@ -1085,13 +1085,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="F12" s="1">
         <x:v>382</x:v>
@@ -1108,19 +1108,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="F13" s="1">
-        <x:v>1870</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
@@ -1131,19 +1131,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="F14" s="1">
-        <x:v>58441</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
@@ -1154,16 +1154,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="F15" s="1">
-        <x:v>382</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>14</x:v>
@@ -1177,13 +1177,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>22</x:v>
       </x:c>
       <x:c r="F16" s="1">
         <x:v>382</x:v>
@@ -1203,10 +1203,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F17" s="1">
         <x:v>382</x:v>
@@ -1223,16 +1223,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="F18" s="1">
-        <x:v>382</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>14</x:v>
@@ -1246,16 +1246,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>1000000</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>12</x:v>
@@ -1269,13 +1269,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="F20" s="1">
         <x:v>382</x:v>
@@ -1292,19 +1292,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>1974</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
@@ -1315,16 +1315,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="F22" s="1">
-        <x:v>2538</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>14</x:v>
@@ -1341,13 +1341,13 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>2649</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>14</x:v>
@@ -1361,16 +1361,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>2651</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>14</x:v>
@@ -1384,16 +1384,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>938</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>14</x:v>
@@ -1401,68 +1401,68 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B26" s="1" t="s">
+      <x:c r="D26" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="C26" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="F26" s="1">
-        <x:v>-9678</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>-31053</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>3575107</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>12</x:v>
@@ -1470,45 +1470,45 @@
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>4968501</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>-6917</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>12</x:v>
@@ -1516,45 +1516,45 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>-46</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>59748</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1562,91 +1562,91 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>579319</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>1238800</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>2326917</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>-28160</x:v>
+        <x:v>1238800</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>14</x:v>
@@ -1654,22 +1654,22 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>-22643</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>12</x:v>
@@ -1677,22 +1677,22 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>39386</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>14</x:v>
@@ -1700,45 +1700,45 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="B39" s="1" t="s">
+      <x:c r="D39" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E39" s="1" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="C39" s="1" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D39" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="E39" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="F39" s="1">
-        <x:v>149773</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>60000</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>14</x:v>
@@ -1746,22 +1746,22 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B41" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C41" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D41" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>500346</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>14</x:v>
@@ -1769,22 +1769,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C42" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>198972</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>14</x:v>
@@ -1792,45 +1792,45 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>198972</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>600000</x:v>
+        <x:v>152765</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>14</x:v>
@@ -1838,22 +1838,22 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>350000</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>14</x:v>
@@ -1861,22 +1861,22 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>95</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>30801</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>14</x:v>
@@ -1884,91 +1884,91 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>4379243</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="B48" s="1" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C48" s="1" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>663879</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C49" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>1183678</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>104555</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>14</x:v>
@@ -1976,22 +1976,22 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>3985698</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>14</x:v>
@@ -1999,22 +1999,22 @@
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>4383748</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>14</x:v>
@@ -2028,16 +2028,16 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>1426379</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -2045,22 +2045,22 @@
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>663879</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -2068,45 +2068,45 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>3232621</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>10000</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>14</x:v>
@@ -2114,22 +2114,22 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>628944</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>14</x:v>
@@ -2137,45 +2137,45 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B58" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C58" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D58" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B58" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C58" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="D58" s="1" t="s">
-        <x:v>110</x:v>
-      </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>63297</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>500000</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>12</x:v>
@@ -2183,45 +2183,45 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>152762</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>4379246</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>14</x:v>
@@ -2229,22 +2229,22 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>3985700</x:v>
+        <x:v>628944</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>14</x:v>
@@ -2252,45 +2252,45 @@
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>1183678</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>4383749</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>14</x:v>
@@ -2304,16 +2304,16 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>1426379</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>12</x:v>
@@ -2321,22 +2321,22 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>104555</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>14</x:v>
@@ -2344,45 +2344,45 @@
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>3515616</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>4495214</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
         <x:v>14</x:v>
@@ -2390,22 +2390,22 @@
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>409773</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
         <x:v>14</x:v>
@@ -2413,22 +2413,22 @@
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>253658</x:v>
+        <x:v>4495214</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
         <x:v>14</x:v>
@@ -2436,22 +2436,22 @@
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>163756</x:v>
+        <x:v>409773</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>14</x:v>
@@ -2459,22 +2459,22 @@
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>14264</x:v>
+        <x:v>1177753</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>12</x:v>
@@ -2482,91 +2482,91 @@
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>468360</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>1000000</x:v>
+        <x:v>195838</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>1177753</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>2326917</x:v>
+        <x:v>9760810</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>12</x:v>
@@ -2574,22 +2574,22 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>195838</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>14</x:v>
@@ -2597,22 +2597,22 @@
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>50000</x:v>
+        <x:v>31115</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
         <x:v>14</x:v>
@@ -2620,93 +2620,24 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>9760810</x:v>
+        <x:v>9888936</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" spans="1:7">
-      <x:c r="A80" s="1" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="B80" s="1" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="C80" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D80" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E80" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F80" s="1">
-        <x:v>10000</x:v>
-      </x:c>
-      <x:c r="G80" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" spans="1:7">
-      <x:c r="A81" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B81" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C81" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D81" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E81" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F81" s="1">
-        <x:v>31115</x:v>
-      </x:c>
-      <x:c r="G81" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" spans="1:7">
-      <x:c r="A82" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B82" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C82" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D82" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E82" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F82" s="1">
-        <x:v>9888936</x:v>
-      </x:c>
-      <x:c r="G82" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -2756,7 +2687,7 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>10</x:v>
@@ -2765,7 +2696,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D2" s="1">
-        <x:v>499161</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
         <x:v>14</x:v>
@@ -2773,16 +2704,16 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D3" s="1">
-        <x:v>63297</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
         <x:v>14</x:v>
@@ -2790,10 +2721,10 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>25</x:v>
@@ -2807,7 +2738,7 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>24</x:v>
@@ -2824,7 +2755,7 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>24</x:v>
@@ -2833,7 +2764,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>153095</x:v>
+        <x:v>153098</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>14</x:v>
@@ -2841,10 +2772,10 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>25</x:v>
@@ -2858,10 +2789,10 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>25</x:v>
@@ -2875,10 +2806,10 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>25</x:v>
@@ -2892,13 +2823,13 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>715</x:v>
@@ -2909,13 +2840,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>8758871</x:v>
@@ -2926,13 +2857,13 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>-9678</x:v>
@@ -2943,13 +2874,13 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>59748</x:v>
@@ -2960,13 +2891,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>4968501</x:v>
@@ -2977,13 +2908,13 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>1327758</x:v>
@@ -2994,13 +2925,13 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
         <x:v>34</x:v>
-      </x:c>
-      <x:c r="B16" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>7971780</x:v>
@@ -3011,13 +2942,13 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>2367356</x:v>
@@ -3028,13 +2959,13 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>2852758</x:v>
@@ -3045,13 +2976,13 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>209110</x:v>
@@ -3062,13 +2993,13 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>149773</x:v>
@@ -3079,13 +3010,13 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>9267843</x:v>
@@ -3096,13 +3027,13 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>-6917</x:v>
@@ -3147,13 +3078,13 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>5734396</x:v>
@@ -3170,7 +3101,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>9760810</x:v>
@@ -3187,7 +3118,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>50000</x:v>
@@ -3198,13 +3129,13 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>9932589</x:v>
@@ -3215,13 +3146,13 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>382</x:v>
@@ -3232,13 +3163,13 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>2649</x:v>
@@ -3249,13 +3180,13 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>1155110</x:v>
@@ -3266,13 +3197,13 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>628944</x:v>
@@ -3283,13 +3214,13 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>2651</x:v>
@@ -3300,13 +3231,13 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>600000</x:v>
@@ -3317,13 +3248,13 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>200842</x:v>
@@ -3334,13 +3265,13 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>198972</x:v>
@@ -3351,13 +3282,13 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>938</x:v>
@@ -3368,13 +3299,13 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B38" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>1974</x:v>
@@ -3385,13 +3316,13 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>409773</x:v>
@@ -3402,13 +3333,13 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>382</x:v>
@@ -3419,13 +3350,13 @@
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>2326917</x:v>
@@ -3436,16 +3367,16 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D42" s="1">
-        <x:v>253658</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>14</x:v>
@@ -3453,13 +3384,13 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>2326917</x:v>
@@ -3470,13 +3401,13 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>408441</x:v>
@@ -3487,13 +3418,13 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>10000</x:v>
@@ -3504,13 +3435,13 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>-31053</x:v>
@@ -3521,13 +3452,13 @@
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>382</x:v>
@@ -3538,10 +3469,10 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>22</x:v>
@@ -3572,13 +3503,13 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>-46</x:v>
@@ -3589,13 +3520,13 @@
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>39386</x:v>
@@ -3606,13 +3537,13 @@
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>14264</x:v>
@@ -3623,13 +3554,13 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>164138</x:v>
@@ -3660,7 +3591,7 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
         <x:v>116</x:v>
@@ -3674,13 +3605,13 @@
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>382</x:v>
@@ -3737,7 +3668,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>499161</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
         <x:v>14</x:v>
@@ -3745,13 +3676,13 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>63297</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
         <x:v>14</x:v>
@@ -3759,7 +3690,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>25</x:v>
@@ -3793,7 +3724,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>153095</x:v>
+        <x:v>153098</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>14</x:v>
@@ -3801,7 +3732,7 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>25</x:v>
@@ -3815,7 +3746,7 @@
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>25</x:v>
@@ -3829,7 +3760,7 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>25</x:v>
@@ -3843,10 +3774,10 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>715</x:v>
@@ -3857,10 +3788,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>8758871</x:v>
@@ -3871,10 +3802,10 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>50070</x:v>
@@ -3885,10 +3816,10 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>4968501</x:v>
@@ -3899,10 +3830,10 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>1327758</x:v>
@@ -3913,10 +3844,10 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>7971780</x:v>
@@ -3927,10 +3858,10 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>5220114</x:v>
@@ -3941,10 +3872,10 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>9626726</x:v>
@@ -3955,10 +3886,10 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>-6917</x:v>
@@ -3997,10 +3928,10 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5734396</x:v>
@@ -4014,7 +3945,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>9760810</x:v>
@@ -4028,7 +3959,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>9982589</x:v>
@@ -4039,10 +3970,10 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>382</x:v>
@@ -4056,7 +3987,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>2649</x:v>
@@ -4067,10 +3998,10 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>1155110</x:v>
@@ -4081,10 +4012,10 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>628944</x:v>
@@ -4098,7 +4029,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>2651</x:v>
@@ -4112,7 +4043,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>600000</x:v>
@@ -4123,10 +4054,10 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>200842</x:v>
@@ -4137,10 +4068,10 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>198972</x:v>
@@ -4154,7 +4085,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>938</x:v>
@@ -4165,10 +4096,10 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>412129</x:v>
@@ -4179,10 +4110,10 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>2326917</x:v>
@@ -4193,13 +4124,13 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>253658</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
         <x:v>14</x:v>
@@ -4207,10 +4138,10 @@
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>2326917</x:v>
@@ -4221,10 +4152,10 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>408441</x:v>
@@ -4238,7 +4169,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>10000</x:v>
@@ -4249,10 +4180,10 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>-31053</x:v>
@@ -4263,10 +4194,10 @@
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>382</x:v>
@@ -4277,7 +4208,7 @@
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
         <x:v>22</x:v>
@@ -4305,10 +4236,10 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>-46</x:v>
@@ -4319,10 +4250,10 @@
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>39386</x:v>
@@ -4333,10 +4264,10 @@
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>14264</x:v>
@@ -4347,10 +4278,10 @@
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>164138</x:v>
@@ -4375,7 +4306,7 @@
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
         <x:v>116</x:v>
@@ -4389,10 +4320,10 @@
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>382</x:v>
@@ -4453,7 +4384,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>747726</x:v>
+        <x:v>747729</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>14</x:v>
@@ -4461,7 +4392,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>715</x:v>
@@ -4472,7 +4403,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>6597942</x:v>
@@ -4483,7 +4414,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>31325878</x:v>
@@ -4494,7 +4425,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>-6917</x:v>
@@ -4527,7 +4458,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>5734396</x:v>
@@ -4538,7 +4469,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>9760810</x:v>
@@ -4549,7 +4480,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>9982971</x:v>
@@ -4560,7 +4491,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>2649</x:v>
@@ -4571,7 +4502,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>1155110</x:v>
@@ -4582,7 +4513,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>628944</x:v>
@@ -4593,7 +4524,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>602651</x:v>
@@ -4604,7 +4535,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>200842</x:v>
@@ -4615,7 +4546,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>198972</x:v>
@@ -4626,7 +4557,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>413067</x:v>
@@ -4637,7 +4568,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>4653834</x:v>
@@ -4648,10 +4579,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B21" s="1">
-        <x:v>662099</x:v>
+        <x:v>662097</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>14</x:v>
@@ -4659,7 +4590,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>-31053</x:v>
@@ -4670,7 +4601,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>10382</x:v>
@@ -4692,7 +4623,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>14218</x:v>
@@ -4703,7 +4634,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>203524</x:v>
@@ -4736,7 +4667,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>382</x:v>
@@ -4782,12 +4713,12 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>3247726</x:v>
+        <x:v>3247729</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>715</x:v>
@@ -4795,7 +4726,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>37923820</x:v>
@@ -4803,7 +4734,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>-6917</x:v>
@@ -4819,7 +4750,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>5734396</x:v>
@@ -4827,7 +4758,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>19743781</x:v>
@@ -4835,7 +4766,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>2649</x:v>
@@ -4843,7 +4774,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>1784054</x:v>
@@ -4851,7 +4782,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>602651</x:v>
@@ -4859,7 +4790,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>399814</x:v>
@@ -4867,7 +4798,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>413067</x:v>
@@ -4875,15 +4806,15 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>5315933</x:v>
+        <x:v>5315931</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>-20671</x:v>
@@ -4899,7 +4830,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>217742</x:v>
@@ -4923,7 +4854,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>382</x:v>
@@ -4967,13 +4898,13 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>499161</x:v>
+        <x:v>499160</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -4989,18 +4920,18 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>216059</x:v>
+        <x:v>216063</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>25</x:v>
@@ -5011,7 +4942,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>25</x:v>
@@ -5025,7 +4956,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>715</x:v>
@@ -5033,10 +4964,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>8758489</x:v>
@@ -5044,10 +4975,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>3904224</x:v>
@@ -5058,7 +4989,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>764</x:v>
@@ -5066,10 +4997,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>500346</x:v>
@@ -5077,10 +5008,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>19591653</x:v>
@@ -5088,10 +5019,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>149773</x:v>
@@ -5099,10 +5030,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>5018571</x:v>
@@ -5110,10 +5041,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>-6917</x:v>
@@ -5132,7 +5063,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>11</x:v>
@@ -5146,7 +5077,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>382</x:v>
@@ -5154,10 +5085,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>5734014</x:v>
@@ -5168,7 +5099,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>34035</x:v>
@@ -5176,10 +5107,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>50000</x:v>
@@ -5187,10 +5118,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>10000</x:v>
@@ -5198,10 +5129,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>19649746</x:v>
@@ -5212,7 +5143,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>2649</x:v>
@@ -5220,10 +5151,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>1784054</x:v>
@@ -5231,10 +5162,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>600000</x:v>
@@ -5245,7 +5176,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>2651</x:v>
@@ -5256,7 +5187,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>1870</x:v>
@@ -5264,10 +5195,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>397944</x:v>
@@ -5275,10 +5206,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>409773</x:v>
@@ -5289,7 +5220,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>3294</x:v>
@@ -5297,13 +5228,13 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>603658</x:v>
+        <x:v>603656</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
@@ -5311,7 +5242,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>58441</x:v>
@@ -5319,10 +5250,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>4653834</x:v>
@@ -5333,7 +5264,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>382</x:v>
@@ -5341,10 +5272,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>10000</x:v>
@@ -5352,10 +5283,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>-31053</x:v>
@@ -5377,7 +5308,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>178402</x:v>
@@ -5385,10 +5316,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>39386</x:v>
@@ -5396,10 +5327,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>-46</x:v>
@@ -5418,7 +5349,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
         <x:v>116</x:v>
@@ -5432,7 +5363,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>382</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2474,7 +2474,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>1177753</x:v>
+        <x:v>1239979</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>12</x:v>
@@ -2566,7 +2566,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>9760810</x:v>
+        <x:v>10036911</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>12</x:v>
@@ -3104,7 +3104,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>9760810</x:v>
+        <x:v>10036911</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -3189,7 +3189,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>1155110</x:v>
+        <x:v>1217336</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>12</x:v>
@@ -3948,7 +3948,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>9760810</x:v>
+        <x:v>10036911</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -4004,7 +4004,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>1155110</x:v>
+        <x:v>1217336</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>12</x:v>
@@ -4472,7 +4472,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>9760810</x:v>
+        <x:v>10036911</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -4505,7 +4505,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>1155110</x:v>
+        <x:v>1217336</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>12</x:v>
@@ -4761,7 +4761,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>19743781</x:v>
+        <x:v>20019882</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -4777,7 +4777,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>1784054</x:v>
+        <x:v>1846280</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -5135,7 +5135,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>19649746</x:v>
+        <x:v>19925847</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -5157,7 +5157,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>1784054</x:v>
+        <x:v>1846280</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2451,7 +2451,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>409773</x:v>
+        <x:v>465686</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>14</x:v>
@@ -2474,7 +2474,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>1239979</x:v>
+        <x:v>1901377</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>12</x:v>
@@ -2566,7 +2566,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>10036911</x:v>
+        <x:v>14760156</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>12</x:v>
@@ -2635,7 +2635,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>9888936</x:v>
+        <x:v>10036699</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
         <x:v>14</x:v>
@@ -3104,7 +3104,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>10036911</x:v>
+        <x:v>14760156</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -3138,7 +3138,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>9932589</x:v>
+        <x:v>10080352</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
@@ -3189,7 +3189,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>1217336</x:v>
+        <x:v>1878734</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>12</x:v>
@@ -3325,7 +3325,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>409773</x:v>
+        <x:v>465686</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>14</x:v>
@@ -3948,7 +3948,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>10036911</x:v>
+        <x:v>14760156</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -3962,7 +3962,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>9982589</x:v>
+        <x:v>10130352</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>14</x:v>
@@ -4004,7 +4004,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>1217336</x:v>
+        <x:v>1878734</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>12</x:v>
@@ -4102,7 +4102,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>412129</x:v>
+        <x:v>468042</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
         <x:v>14</x:v>
@@ -4472,7 +4472,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>10036911</x:v>
+        <x:v>14760156</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -4483,7 +4483,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>9982971</x:v>
+        <x:v>10130734</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>14</x:v>
@@ -4505,7 +4505,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>1217336</x:v>
+        <x:v>1878734</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>12</x:v>
@@ -4560,7 +4560,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>413067</x:v>
+        <x:v>468980</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>14</x:v>
@@ -4761,7 +4761,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>20019882</x:v>
+        <x:v>24890890</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -4777,7 +4777,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>1846280</x:v>
+        <x:v>2507678</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -4801,7 +4801,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>413067</x:v>
+        <x:v>468980</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -5135,7 +5135,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>19925847</x:v>
+        <x:v>24796855</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -5157,7 +5157,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>1846280</x:v>
+        <x:v>2507678</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -5212,7 +5212,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>409773</x:v>
+        <x:v>465686</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2244,7 +2244,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>628944</x:v>
+        <x:v>654844</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>14</x:v>
@@ -2474,7 +2474,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>1901377</x:v>
+        <x:v>1927277</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>12</x:v>
@@ -2566,7 +2566,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>14760156</x:v>
+        <x:v>14808128</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>12</x:v>
@@ -2635,7 +2635,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>10036699</x:v>
+        <x:v>10154402</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
         <x:v>14</x:v>
@@ -3104,7 +3104,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>14760156</x:v>
+        <x:v>14808128</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -3138,7 +3138,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>10080352</x:v>
+        <x:v>10198055</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
@@ -3189,7 +3189,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>1878734</x:v>
+        <x:v>1904634</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>12</x:v>
@@ -3206,7 +3206,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>628944</x:v>
+        <x:v>654844</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>14</x:v>
@@ -3948,7 +3948,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>14760156</x:v>
+        <x:v>14808128</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -3962,7 +3962,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>10130352</x:v>
+        <x:v>10248055</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>14</x:v>
@@ -4004,7 +4004,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>1878734</x:v>
+        <x:v>1904634</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>12</x:v>
@@ -4018,7 +4018,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>628944</x:v>
+        <x:v>654844</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>14</x:v>
@@ -4472,7 +4472,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>14760156</x:v>
+        <x:v>14808128</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -4483,7 +4483,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>10130734</x:v>
+        <x:v>10248437</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>14</x:v>
@@ -4505,7 +4505,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>1878734</x:v>
+        <x:v>1904634</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>12</x:v>
@@ -4516,7 +4516,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>628944</x:v>
+        <x:v>654844</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>14</x:v>
@@ -4761,7 +4761,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>24890890</x:v>
+        <x:v>25056565</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -4777,7 +4777,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>2507678</x:v>
+        <x:v>2559478</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -5135,7 +5135,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>24796855</x:v>
+        <x:v>24962530</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -5157,7 +5157,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>2507678</x:v>
+        <x:v>2559478</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2474,7 +2474,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>1927277</x:v>
+        <x:v>1989796</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>12</x:v>
@@ -2566,7 +2566,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>14808128</x:v>
+        <x:v>15095965</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>12</x:v>
@@ -3104,7 +3104,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>14808128</x:v>
+        <x:v>15095965</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -3189,7 +3189,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>1904634</x:v>
+        <x:v>1967153</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>12</x:v>
@@ -3948,7 +3948,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>14808128</x:v>
+        <x:v>15095965</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -4004,7 +4004,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>1904634</x:v>
+        <x:v>1967153</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>12</x:v>
@@ -4472,7 +4472,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>14808128</x:v>
+        <x:v>15095965</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -4505,7 +4505,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>1904634</x:v>
+        <x:v>1967153</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>12</x:v>
@@ -4761,7 +4761,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>25056565</x:v>
+        <x:v>25344402</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -4777,7 +4777,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>2559478</x:v>
+        <x:v>2621997</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -5135,7 +5135,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>24962530</x:v>
+        <x:v>25250367</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -5157,7 +5157,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>2559478</x:v>
+        <x:v>2621997</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2451,7 +2451,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>465686</x:v>
+        <x:v>513656</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>14</x:v>
@@ -2474,7 +2474,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>1989796</x:v>
+        <x:v>2427007</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>12</x:v>
@@ -2566,7 +2566,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>15095965</x:v>
+        <x:v>20015158</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>12</x:v>
@@ -2635,7 +2635,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>10154402</x:v>
+        <x:v>10192938</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
         <x:v>14</x:v>
@@ -3104,7 +3104,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>15095965</x:v>
+        <x:v>20015158</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -3138,7 +3138,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>10198055</x:v>
+        <x:v>10236591</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
@@ -3189,7 +3189,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>1967153</x:v>
+        <x:v>2404364</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>12</x:v>
@@ -3325,7 +3325,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>465686</x:v>
+        <x:v>513656</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>14</x:v>
@@ -3948,7 +3948,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>15095965</x:v>
+        <x:v>20015158</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -3962,7 +3962,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>10248055</x:v>
+        <x:v>10286591</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>14</x:v>
@@ -4004,7 +4004,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>1967153</x:v>
+        <x:v>2404364</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>12</x:v>
@@ -4102,7 +4102,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>468042</x:v>
+        <x:v>516012</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
         <x:v>14</x:v>
@@ -4472,7 +4472,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>15095965</x:v>
+        <x:v>20015158</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -4483,7 +4483,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>10248437</x:v>
+        <x:v>10286973</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>14</x:v>
@@ -4505,7 +4505,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>1967153</x:v>
+        <x:v>2404364</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>12</x:v>
@@ -4560,7 +4560,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>468980</x:v>
+        <x:v>516950</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>14</x:v>
@@ -4761,7 +4761,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>25344402</x:v>
+        <x:v>30302131</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -4777,7 +4777,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>2621997</x:v>
+        <x:v>3059208</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -4801,7 +4801,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>468980</x:v>
+        <x:v>516950</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -5135,7 +5135,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>25250367</x:v>
+        <x:v>30208096</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -5157,7 +5157,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>2621997</x:v>
+        <x:v>3059208</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -5212,7 +5212,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>465686</x:v>
+        <x:v>513656</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2244,7 +2244,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>654844</x:v>
+        <x:v>685625</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>14</x:v>
@@ -2474,7 +2474,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>2427007</x:v>
+        <x:v>2457788</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>12</x:v>
@@ -2566,7 +2566,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>20015158</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>12</x:v>
@@ -2635,7 +2635,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>10192938</x:v>
+        <x:v>10498737</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
         <x:v>14</x:v>
@@ -3104,7 +3104,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>20015158</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -3138,7 +3138,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>10236591</x:v>
+        <x:v>10542390</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
@@ -3189,7 +3189,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>2404364</x:v>
+        <x:v>2435145</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>12</x:v>
@@ -3206,7 +3206,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>654844</x:v>
+        <x:v>685625</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>14</x:v>
@@ -3948,7 +3948,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>20015158</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -3962,7 +3962,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>10286591</x:v>
+        <x:v>10592390</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>14</x:v>
@@ -4004,7 +4004,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>2404364</x:v>
+        <x:v>2435145</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>12</x:v>
@@ -4018,7 +4018,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>654844</x:v>
+        <x:v>685625</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>14</x:v>
@@ -4472,7 +4472,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>20015158</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -4483,7 +4483,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>10286973</x:v>
+        <x:v>10592772</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>14</x:v>
@@ -4505,7 +4505,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>2404364</x:v>
+        <x:v>2435145</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>12</x:v>
@@ -4516,7 +4516,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>654844</x:v>
+        <x:v>685625</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>14</x:v>
@@ -4761,7 +4761,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>30302131</x:v>
+        <x:v>30732677</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -4777,7 +4777,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>3059208</x:v>
+        <x:v>3120770</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -5135,7 +5135,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>30208096</x:v>
+        <x:v>30638642</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -5157,7 +5157,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>3059208</x:v>
+        <x:v>3120770</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2451,7 +2451,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>513656</x:v>
+        <x:v>651086</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>14</x:v>
@@ -3325,7 +3325,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>513656</x:v>
+        <x:v>651086</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>14</x:v>
@@ -4102,7 +4102,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>516012</x:v>
+        <x:v>653442</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
         <x:v>14</x:v>
@@ -4560,7 +4560,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>516950</x:v>
+        <x:v>654380</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>14</x:v>
@@ -4801,7 +4801,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>516950</x:v>
+        <x:v>654380</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -5212,7 +5212,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>513656</x:v>
+        <x:v>651086</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -75,6 +75,21 @@
     <x:t>US</x:t>
   </x:si>
   <x:si>
+    <x:t>C00684969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JDCA PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLDMAN, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00710848</x:t>
   </x:si>
   <x:si>
@@ -84,9 +99,6 @@
     <x:t>STELSON, JANELLE</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
     <x:t>PA</x:t>
   </x:si>
   <x:si>
@@ -165,9 +177,6 @@
     <x:t>17</x:t>
   </x:si>
   <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
     <x:t>COGNETTI, PAIGE</x:t>
   </x:si>
   <x:si>
@@ -349,15 +358,6 @@
   </x:si>
   <x:si>
     <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00684969</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JDCA PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLDMAN, DANIEL</x:t>
   </x:si>
   <x:si>
     <x:t>BELL, WESLEY</x:t>
@@ -933,7 +933,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>382</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>14</x:v>
@@ -941,65 +941,65 @@
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>500000</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>333</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>333</x:v>
@@ -1010,22 +1010,22 @@
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="F9" s="1">
-        <x:v>715</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>14</x:v>
@@ -1033,22 +1033,22 @@
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>382</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>14</x:v>
@@ -1056,19 +1056,19 @@
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>382</x:v>
@@ -1079,16 +1079,16 @@
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>38</x:v>
@@ -1102,19 +1102,19 @@
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F13" s="1">
         <x:v>382</x:v>
@@ -1125,68 +1125,68 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>1870</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>58441</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>382</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>14</x:v>
@@ -1194,16 +1194,16 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>22</x:v>
@@ -1217,22 +1217,22 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>164138</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>14</x:v>
@@ -1240,114 +1240,114 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>14264</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>382</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>2000000</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>382</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>1974</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>14</x:v>
@@ -1355,22 +1355,22 @@
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="D24" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>2538</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>14</x:v>
@@ -1378,22 +1378,22 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>2649</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>14</x:v>
@@ -1401,22 +1401,22 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>2651</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>14</x:v>
@@ -1424,22 +1424,22 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>938</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>14</x:v>
@@ -1447,45 +1447,45 @@
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>-9678</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>-31053</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>12</x:v>
@@ -1493,22 +1493,22 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>3575107</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>12</x:v>
@@ -1516,68 +1516,68 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>4968501</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>-6917</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>-46</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>12</x:v>
@@ -1585,22 +1585,22 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>59748</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1608,45 +1608,45 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>579319</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>1238800</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>14</x:v>
@@ -1654,114 +1654,114 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>2326917</x:v>
+        <x:v>1238800</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>-28160</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>-22643</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="C40" s="1" t="s">
+      <x:c r="D40" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D40" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="E40" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="F40" s="1">
-        <x:v>39386</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>149773</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>14</x:v>
@@ -1769,22 +1769,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>60000</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>14</x:v>
@@ -1792,22 +1792,22 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>63298</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>14</x:v>
@@ -1815,22 +1815,22 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>152765</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>14</x:v>
@@ -1838,22 +1838,22 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>500346</x:v>
+        <x:v>152765</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>14</x:v>
@@ -1861,22 +1861,22 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C46" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D46" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>198972</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>14</x:v>
@@ -1884,68 +1884,68 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F47" s="1">
         <x:v>198972</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>600000</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>253656</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>14</x:v>
@@ -1953,22 +1953,22 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>350000</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>14</x:v>
@@ -1976,22 +1976,22 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>499160</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>14</x:v>
@@ -1999,22 +1999,22 @@
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>4379243</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>14</x:v>
@@ -2022,45 +2022,45 @@
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>663879</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>1183678</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -2068,45 +2068,45 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>104555</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>3985698</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>14</x:v>
@@ -2114,22 +2114,22 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>4383748</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>14</x:v>
@@ -2137,45 +2137,45 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>1426379</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>663879</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>12</x:v>
@@ -2183,22 +2183,22 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>3232621</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>12</x:v>
@@ -2206,42 +2206,42 @@
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>10000</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F62" s="1">
         <x:v>685625</x:v>
@@ -2252,19 +2252,19 @@
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F63" s="1">
         <x:v>4379246</x:v>
@@ -2275,19 +2275,19 @@
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F64" s="1">
         <x:v>3985700</x:v>
@@ -2298,19 +2298,19 @@
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F65" s="1">
         <x:v>1183678</x:v>
@@ -2321,19 +2321,19 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F66" s="1">
         <x:v>4383749</x:v>
@@ -2344,19 +2344,19 @@
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F67" s="1">
         <x:v>1426379</x:v>
@@ -2367,19 +2367,19 @@
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F68" s="1">
         <x:v>104555</x:v>
@@ -2413,19 +2413,19 @@
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F70" s="1">
         <x:v>4495214</x:v>
@@ -2436,19 +2436,19 @@
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
         <x:v>114</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F71" s="1">
         <x:v>651086</x:v>
@@ -2459,19 +2459,19 @@
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F72" s="1">
         <x:v>2457788</x:v>
@@ -2482,19 +2482,19 @@
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F73" s="1">
         <x:v>2326917</x:v>
@@ -2505,16 +2505,16 @@
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
         <x:v>116</x:v>
@@ -2528,10 +2528,10 @@
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
         <x:v>117</x:v>
@@ -2540,7 +2540,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F75" s="1">
         <x:v>50000</x:v>
@@ -2551,10 +2551,10 @@
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
         <x:v>118</x:v>
@@ -2563,7 +2563,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F76" s="1">
         <x:v>20139905</x:v>
@@ -2574,19 +2574,19 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F77" s="1">
         <x:v>10000</x:v>
@@ -2597,19 +2597,19 @@
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F78" s="1">
         <x:v>31115</x:v>
@@ -2620,19 +2620,19 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F79" s="1">
         <x:v>10498737</x:v>
@@ -2687,13 +2687,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>499160</x:v>
@@ -2704,13 +2704,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>63298</x:v>
@@ -2721,13 +2721,13 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>60000</x:v>
@@ -2738,13 +2738,13 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>500000</x:v>
@@ -2755,13 +2755,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>153098</x:v>
@@ -2772,13 +2772,13 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>-28160</x:v>
@@ -2789,13 +2789,13 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>2000000</x:v>
@@ -2806,13 +2806,13 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>333</x:v>
@@ -2823,13 +2823,13 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>715</x:v>
@@ -2840,13 +2840,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>8758871</x:v>
@@ -2857,13 +2857,13 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>-9678</x:v>
@@ -2874,13 +2874,13 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>59748</x:v>
@@ -2891,13 +2891,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>4968501</x:v>
@@ -2908,13 +2908,13 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>1327758</x:v>
@@ -2925,13 +2925,13 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>7971780</x:v>
@@ -2942,13 +2942,13 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>2367356</x:v>
@@ -2959,13 +2959,13 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>2852758</x:v>
@@ -2976,13 +2976,13 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>209110</x:v>
@@ -2993,13 +2993,13 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>149773</x:v>
@@ -3010,13 +3010,13 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>9267843</x:v>
@@ -3027,13 +3027,13 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>-6917</x:v>
@@ -3078,13 +3078,13 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>5734396</x:v>
@@ -3101,7 +3101,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>20139905</x:v>
@@ -3118,7 +3118,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>50000</x:v>
@@ -3129,13 +3129,13 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>10542390</x:v>
@@ -3146,13 +3146,13 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>382</x:v>
@@ -3163,13 +3163,13 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>2649</x:v>
@@ -3180,13 +3180,13 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>2435145</x:v>
@@ -3200,10 +3200,10 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>685625</x:v>
@@ -3214,13 +3214,13 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>2651</x:v>
@@ -3231,13 +3231,13 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>600000</x:v>
@@ -3248,13 +3248,13 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>200842</x:v>
@@ -3265,13 +3265,13 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>198972</x:v>
@@ -3282,13 +3282,13 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>938</x:v>
@@ -3299,13 +3299,13 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>1974</x:v>
@@ -3319,10 +3319,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>651086</x:v>
@@ -3333,13 +3333,13 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>382</x:v>
@@ -3350,13 +3350,13 @@
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>2326917</x:v>
@@ -3367,13 +3367,13 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>253656</x:v>
@@ -3384,13 +3384,13 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>2326917</x:v>
@@ -3401,13 +3401,13 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B44" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>408441</x:v>
@@ -3418,13 +3418,13 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>10000</x:v>
@@ -3435,13 +3435,13 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>-31053</x:v>
@@ -3452,13 +3452,13 @@
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>382</x:v>
@@ -3469,13 +3469,13 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>382</x:v>
@@ -3486,13 +3486,13 @@
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>382</x:v>
@@ -3503,13 +3503,13 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>-46</x:v>
@@ -3520,13 +3520,13 @@
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>39386</x:v>
@@ -3537,13 +3537,13 @@
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>14264</x:v>
@@ -3554,13 +3554,13 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>164138</x:v>
@@ -3591,7 +3591,7 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
         <x:v>116</x:v>
@@ -3605,13 +3605,13 @@
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>382</x:v>
@@ -3665,7 +3665,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>499160</x:v>
@@ -3676,10 +3676,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>63298</x:v>
@@ -3690,10 +3690,10 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>60000</x:v>
@@ -3704,10 +3704,10 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>500000</x:v>
@@ -3718,10 +3718,10 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>153098</x:v>
@@ -3732,10 +3732,10 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>-28160</x:v>
@@ -3746,10 +3746,10 @@
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>2000000</x:v>
@@ -3760,10 +3760,10 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>333</x:v>
@@ -3774,10 +3774,10 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>715</x:v>
@@ -3788,10 +3788,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>8758871</x:v>
@@ -3802,10 +3802,10 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>50070</x:v>
@@ -3816,10 +3816,10 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>4968501</x:v>
@@ -3830,10 +3830,10 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>1327758</x:v>
@@ -3844,10 +3844,10 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>7971780</x:v>
@@ -3858,10 +3858,10 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>5220114</x:v>
@@ -3872,10 +3872,10 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>9626726</x:v>
@@ -3886,10 +3886,10 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>-6917</x:v>
@@ -3928,10 +3928,10 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5734396</x:v>
@@ -3945,7 +3945,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>20139905</x:v>
@@ -3959,7 +3959,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>10592390</x:v>
@@ -3970,10 +3970,10 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>382</x:v>
@@ -3987,7 +3987,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>2649</x:v>
@@ -3998,10 +3998,10 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>2435145</x:v>
@@ -4012,10 +4012,10 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>685625</x:v>
@@ -4029,7 +4029,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>2651</x:v>
@@ -4043,7 +4043,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>600000</x:v>
@@ -4054,10 +4054,10 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>200842</x:v>
@@ -4068,10 +4068,10 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>198972</x:v>
@@ -4085,7 +4085,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>938</x:v>
@@ -4096,10 +4096,10 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>653442</x:v>
@@ -4110,10 +4110,10 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>2326917</x:v>
@@ -4124,10 +4124,10 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>253656</x:v>
@@ -4138,10 +4138,10 @@
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>2326917</x:v>
@@ -4152,10 +4152,10 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>408441</x:v>
@@ -4169,7 +4169,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>10000</x:v>
@@ -4180,10 +4180,10 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>-31053</x:v>
@@ -4194,10 +4194,10 @@
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>382</x:v>
@@ -4208,10 +4208,10 @@
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>382</x:v>
@@ -4225,7 +4225,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>382</x:v>
@@ -4236,10 +4236,10 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>-46</x:v>
@@ -4250,10 +4250,10 @@
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>39386</x:v>
@@ -4264,10 +4264,10 @@
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>14264</x:v>
@@ -4278,10 +4278,10 @@
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>164138</x:v>
@@ -4306,7 +4306,7 @@
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
         <x:v>116</x:v>
@@ -4320,10 +4320,10 @@
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>382</x:v>
@@ -4370,7 +4370,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>2500000</x:v>
@@ -4381,7 +4381,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>747729</x:v>
@@ -4392,7 +4392,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>715</x:v>
@@ -4403,7 +4403,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>6597942</x:v>
@@ -4414,7 +4414,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>31325878</x:v>
@@ -4425,7 +4425,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>-6917</x:v>
@@ -4458,7 +4458,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>5734396</x:v>
@@ -4469,7 +4469,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>20139905</x:v>
@@ -4480,7 +4480,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>10592772</x:v>
@@ -4491,7 +4491,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>2649</x:v>
@@ -4502,7 +4502,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>2435145</x:v>
@@ -4513,7 +4513,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>685625</x:v>
@@ -4524,7 +4524,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>602651</x:v>
@@ -4535,7 +4535,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>200842</x:v>
@@ -4546,7 +4546,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>198972</x:v>
@@ -4557,7 +4557,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>654380</x:v>
@@ -4568,7 +4568,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>4653834</x:v>
@@ -4579,7 +4579,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>662097</x:v>
@@ -4590,7 +4590,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>-31053</x:v>
@@ -4601,7 +4601,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>10382</x:v>
@@ -4612,7 +4612,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>764</x:v>
@@ -4623,7 +4623,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>14218</x:v>
@@ -4634,7 +4634,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>203524</x:v>
@@ -4667,7 +4667,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>382</x:v>
@@ -4710,7 +4710,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>3247729</x:v>
@@ -4718,7 +4718,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>715</x:v>
@@ -4726,7 +4726,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>37923820</x:v>
@@ -4734,7 +4734,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>-6917</x:v>
@@ -4750,7 +4750,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>5734396</x:v>
@@ -4758,7 +4758,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>30732677</x:v>
@@ -4766,7 +4766,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>2649</x:v>
@@ -4774,7 +4774,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>3120770</x:v>
@@ -4782,7 +4782,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>602651</x:v>
@@ -4790,7 +4790,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>399814</x:v>
@@ -4798,7 +4798,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>654380</x:v>
@@ -4806,7 +4806,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>5315931</x:v>
@@ -4814,7 +4814,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>-20671</x:v>
@@ -4822,7 +4822,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>764</x:v>
@@ -4830,7 +4830,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>217742</x:v>
@@ -4854,7 +4854,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>382</x:v>
@@ -4898,10 +4898,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>499160</x:v>
@@ -4909,10 +4909,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>2500666</x:v>
@@ -4920,10 +4920,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>216063</x:v>
@@ -4931,10 +4931,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>60000</x:v>
@@ -4942,10 +4942,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>-28160</x:v>
@@ -4953,10 +4953,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>715</x:v>
@@ -4964,10 +4964,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>8758489</x:v>
@@ -4975,10 +4975,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>3904224</x:v>
@@ -4986,10 +4986,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>764</x:v>
@@ -4997,10 +4997,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>500346</x:v>
@@ -5008,10 +5008,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>19591653</x:v>
@@ -5019,10 +5019,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>149773</x:v>
@@ -5030,10 +5030,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>5018571</x:v>
@@ -5041,10 +5041,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>-6917</x:v>
@@ -5063,7 +5063,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>11</x:v>
@@ -5074,10 +5074,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>382</x:v>
@@ -5085,10 +5085,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>5734014</x:v>
@@ -5096,10 +5096,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>34035</x:v>
@@ -5107,10 +5107,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>50000</x:v>
@@ -5118,10 +5118,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>10000</x:v>
@@ -5129,10 +5129,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>30638642</x:v>
@@ -5140,10 +5140,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>2649</x:v>
@@ -5151,10 +5151,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>3120770</x:v>
@@ -5162,10 +5162,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>600000</x:v>
@@ -5173,10 +5173,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>2651</x:v>
@@ -5184,10 +5184,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>1870</x:v>
@@ -5195,10 +5195,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>397944</x:v>
@@ -5206,10 +5206,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>651086</x:v>
@@ -5217,10 +5217,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>3294</x:v>
@@ -5228,10 +5228,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>603656</x:v>
@@ -5239,10 +5239,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>58441</x:v>
@@ -5250,10 +5250,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>4653834</x:v>
@@ -5261,10 +5261,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>382</x:v>
@@ -5272,10 +5272,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>10000</x:v>
@@ -5283,10 +5283,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>-31053</x:v>
@@ -5294,10 +5294,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>764</x:v>
@@ -5305,10 +5305,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>178402</x:v>
@@ -5316,10 +5316,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>39386</x:v>
@@ -5327,10 +5327,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>-46</x:v>
@@ -5349,7 +5349,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
         <x:v>116</x:v>
@@ -5360,10 +5360,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>382</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -360,7 +360,19 @@
     <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
   </x:si>
   <x:si>
+    <x:t>WAHAB, AISHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
     <x:t>BELL, WESLEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERNANDEZ, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
   </x:si>
   <x:si>
     <x:t>SHAHEEN, STEFANY</x:t>
@@ -446,8 +458,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G79" totalsRowShown="0">
-  <x:autoFilter ref="A1:G79"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G81" totalsRowShown="0">
+  <x:autoFilter ref="A1:G81"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -462,8 +474,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E56" totalsRowShown="0">
-  <x:autoFilter ref="A1:E56"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E58" totalsRowShown="0">
+  <x:autoFilter ref="A1:E58"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -476,8 +488,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D49" totalsRowShown="0">
-  <x:autoFilter ref="A1:D49"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D51" totalsRowShown="0">
+  <x:autoFilter ref="A1:D51"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -811,7 +823,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G79"/>
+  <x:dimension ref="A1:G81"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2183,22 +2195,22 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>663879</x:v>
+        <x:v>818769</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>12</x:v>
@@ -2206,22 +2218,22 @@
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>3232621</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>12</x:v>
@@ -2229,45 +2241,45 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>685625</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>4379246</x:v>
+        <x:v>685625</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
         <x:v>14</x:v>
@@ -2275,22 +2287,22 @@
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>3985700</x:v>
+        <x:v>384198</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>14</x:v>
@@ -2298,25 +2310,25 @@
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>1183678</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
@@ -2327,16 +2339,16 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>4383749</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>14</x:v>
@@ -2344,13 +2356,13 @@
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
         <x:v>91</x:v>
@@ -2359,7 +2371,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>1426379</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
         <x:v>12</x:v>
@@ -2367,13 +2379,13 @@
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
         <x:v>91</x:v>
@@ -2382,7 +2394,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>104555</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
         <x:v>14</x:v>
@@ -2390,45 +2402,45 @@
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>3515616</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>4495214</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
         <x:v>14</x:v>
@@ -2436,22 +2448,22 @@
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>651086</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>14</x:v>
@@ -2465,122 +2477,122 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>2457788</x:v>
+        <x:v>4495214</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>2326917</x:v>
+        <x:v>706754</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>195838</x:v>
+        <x:v>2457788</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>50000</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>20139905</x:v>
+        <x:v>195838</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
         <x:v>16</x:v>
@@ -2589,7 +2601,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>10000</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>14</x:v>
@@ -2597,13 +2609,13 @@
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
         <x:v>16</x:v>
@@ -2612,18 +2624,18 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>31115</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
         <x:v>64</x:v>
@@ -2635,9 +2647,55 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="F79" s="1">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="G79" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:7">
+      <x:c r="A80" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B80" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C80" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D80" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E80" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F80" s="1">
+        <x:v>31115</x:v>
+      </x:c>
+      <x:c r="G80" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:7">
+      <x:c r="A81" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B81" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C81" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D81" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E81" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F81" s="1">
         <x:v>10498737</x:v>
       </x:c>
-      <x:c r="G79" s="1" t="s">
+      <x:c r="G81" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -2657,7 +2715,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E56"/>
+  <x:dimension ref="A1:E58"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2738,84 +2796,84 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="1">
-        <x:v>500000</x:v>
+        <x:v>384198</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>153098</x:v>
+        <x:v>818769</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>-28160</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>2000000</x:v>
+        <x:v>153098</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>333</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>14</x:v>
@@ -2823,33 +2881,33 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>715</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>8758871</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
@@ -2857,41 +2915,41 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>-9678</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>59748</x:v>
+        <x:v>8758871</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>72</x:v>
@@ -2900,24 +2958,24 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>4968501</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>1327758</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>12</x:v>
@@ -2925,16 +2983,16 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>7971780</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>14</x:v>
@@ -2942,16 +3000,16 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>2367356</x:v>
+        <x:v>1327758</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>12</x:v>
@@ -2959,24 +3017,24 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>2852758</x:v>
+        <x:v>7971780</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>91</x:v>
@@ -2985,10 +3043,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>209110</x:v>
+        <x:v>2367356</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
@@ -3002,15 +3060,15 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>149773</x:v>
+        <x:v>2852758</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>91</x:v>
@@ -3019,7 +3077,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>9267843</x:v>
+        <x:v>209110</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>14</x:v>
@@ -3027,101 +3085,101 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>-6917</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>7170572</x:v>
+        <x:v>9267843</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>7140550</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>5734396</x:v>
+        <x:v>7170572</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>20139905</x:v>
+        <x:v>7140550</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>50000</x:v>
+        <x:v>5734396</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
@@ -3129,7 +3187,7 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>16</x:v>
@@ -3138,24 +3196,24 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>10542390</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>382</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>14</x:v>
@@ -3163,16 +3221,16 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>2649</x:v>
+        <x:v>10542390</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>14</x:v>
@@ -3180,33 +3238,33 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>2435145</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>685625</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>14</x:v>
@@ -3214,33 +3272,33 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>2651</x:v>
+        <x:v>2435145</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>600000</x:v>
+        <x:v>685625</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>14</x:v>
@@ -3248,33 +3306,33 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>200842</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>198972</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>14</x:v>
@@ -3282,33 +3340,33 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>938</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>1974</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>14</x:v>
@@ -3316,16 +3374,16 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>651086</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>14</x:v>
@@ -3333,7 +3391,7 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
         <x:v>61</x:v>
@@ -3342,7 +3400,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="D40" s="1">
-        <x:v>382</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>14</x:v>
@@ -3350,33 +3408,33 @@
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>2326917</x:v>
+        <x:v>706754</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D42" s="1">
-        <x:v>253656</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>14</x:v>
@@ -3387,7 +3445,7 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
         <x:v>49</x:v>
@@ -3401,16 +3459,16 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="D44" s="1">
-        <x:v>408441</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>14</x:v>
@@ -3418,50 +3476,50 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D45" s="1">
-        <x:v>10000</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D46" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D47" s="1">
-        <x:v>382</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>14</x:v>
@@ -3469,30 +3527,30 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D48" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>382</x:v>
@@ -3503,33 +3561,33 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D50" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D51" s="1">
-        <x:v>39386</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>14</x:v>
@@ -3537,16 +3595,16 @@
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D52" s="1">
-        <x:v>14264</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
         <x:v>12</x:v>
@@ -3554,16 +3612,16 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D53" s="1">
-        <x:v>164138</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
         <x:v>14</x:v>
@@ -3571,33 +3629,33 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D54" s="1">
-        <x:v>-62727</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D55" s="1">
-        <x:v>195838</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
         <x:v>14</x:v>
@@ -3605,18 +3663,52 @@
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B56" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C56" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D56" s="1">
+        <x:v>-62727</x:v>
+      </x:c>
+      <x:c r="E56" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:5">
+      <x:c r="A57" s="1" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B57" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C57" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D57" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+      <x:c r="E57" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:5">
+      <x:c r="A58" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B56" s="1" t="s">
+      <x:c r="B58" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C56" s="1" t="s">
+      <x:c r="C58" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D56" s="1">
+      <x:c r="D58" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="E56" s="1" t="s">
+      <x:c r="E58" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -3636,7 +3728,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D49"/>
+  <x:dimension ref="A1:D51"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3704,69 +3796,69 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>500000</x:v>
+        <x:v>384198</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>153098</x:v>
+        <x:v>818769</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>-28160</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>2000000</x:v>
+        <x:v>153098</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>333</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>14</x:v>
@@ -3774,27 +3866,27 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>715</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>8758871</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
         <x:v>14</x:v>
@@ -3802,27 +3894,27 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>50070</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>4968501</x:v>
+        <x:v>8758871</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>14</x:v>
@@ -3830,13 +3922,13 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>1327758</x:v>
+        <x:v>50070</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>12</x:v>
@@ -3844,13 +3936,13 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>7971780</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>14</x:v>
@@ -3858,13 +3950,13 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>5220114</x:v>
+        <x:v>1327758</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>12</x:v>
@@ -3872,13 +3964,13 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>9626726</x:v>
+        <x:v>7971780</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>14</x:v>
@@ -3886,13 +3978,13 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>-6917</x:v>
+        <x:v>5220114</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
         <x:v>12</x:v>
@@ -3900,69 +3992,69 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>7170572</x:v>
+        <x:v>9626726</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>7140550</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>5734396</x:v>
+        <x:v>7170572</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>20139905</x:v>
+        <x:v>7140550</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>10592390</x:v>
+        <x:v>5734396</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>14</x:v>
@@ -3970,16 +4062,16 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>382</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
@@ -3987,10 +4079,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>2649</x:v>
+        <x:v>10592390</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
         <x:v>14</x:v>
@@ -3998,27 +4090,27 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>2435145</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>685625</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>14</x:v>
@@ -4026,27 +4118,27 @@
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>2651</x:v>
+        <x:v>2435145</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>600000</x:v>
+        <x:v>685625</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
         <x:v>14</x:v>
@@ -4054,27 +4146,27 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>200842</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>198972</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>14</x:v>
@@ -4082,27 +4174,27 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>938</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>653442</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
         <x:v>14</x:v>
@@ -4110,27 +4202,27 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>2326917</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>253656</x:v>
+        <x:v>709110</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
         <x:v>14</x:v>
@@ -4138,7 +4230,7 @@
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
         <x:v>49</x:v>
@@ -4152,13 +4244,13 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>408441</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
         <x:v>14</x:v>
@@ -4166,41 +4258,41 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>10000</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>-31053</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>382</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
         <x:v>14</x:v>
@@ -4208,24 +4300,24 @@
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>382</x:v>
@@ -4236,27 +4328,27 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C43" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C44" s="1">
-        <x:v>39386</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
         <x:v>14</x:v>
@@ -4264,13 +4356,13 @@
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C45" s="1">
-        <x:v>14264</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
         <x:v>12</x:v>
@@ -4278,13 +4370,13 @@
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C46" s="1">
-        <x:v>164138</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
         <x:v>14</x:v>
@@ -4292,27 +4384,27 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C47" s="1">
-        <x:v>-62727</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C48" s="1">
-        <x:v>195838</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
         <x:v>14</x:v>
@@ -4320,15 +4412,43 @@
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C49" s="1">
+        <x:v>-62727</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:4">
+      <x:c r="A50" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C50" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:4">
+      <x:c r="A51" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B49" s="1" t="s">
+      <x:c r="B51" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C49" s="1">
+      <x:c r="C51" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="D49" s="1" t="s">
+      <x:c r="D51" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -4373,7 +4493,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>2500000</x:v>
+        <x:v>3318769</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
         <x:v>12</x:v>
@@ -4384,7 +4504,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>747729</x:v>
+        <x:v>1131927</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>14</x:v>
@@ -4560,7 +4680,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>654380</x:v>
+        <x:v>710048</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>14</x:v>
@@ -4656,7 +4776,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>195838</x:v>
@@ -4713,7 +4833,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>3247729</x:v>
+        <x:v>4450696</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -4801,7 +4921,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>654380</x:v>
+        <x:v>710048</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -4846,7 +4966,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>195838</x:v>
@@ -4948,7 +5068,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>-28160</x:v>
+        <x:v>1174807</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -5212,7 +5332,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>651086</x:v>
+        <x:v>706754</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
@@ -5352,7 +5472,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>195838</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2509,7 +2509,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>706754</x:v>
+        <x:v>766293</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
         <x:v>14</x:v>
@@ -3417,7 +3417,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>706754</x:v>
+        <x:v>766293</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>14</x:v>
@@ -4222,7 +4222,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>709110</x:v>
+        <x:v>768649</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
         <x:v>14</x:v>
@@ -4680,7 +4680,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>710048</x:v>
+        <x:v>769587</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>14</x:v>
@@ -4921,7 +4921,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>710048</x:v>
+        <x:v>769587</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -5332,7 +5332,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>706754</x:v>
+        <x:v>766293</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -899,7 +899,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>3045615</x:v>
+        <x:v>3515615</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>14</x:v>
@@ -3162,7 +3162,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>7140550</x:v>
+        <x:v>7610550</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
@@ -4040,7 +4040,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>7140550</x:v>
+        <x:v>7610550</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>14</x:v>
@@ -4570,7 +4570,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>7140550</x:v>
+        <x:v>7610550</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>14</x:v>
@@ -4865,7 +4865,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>14311122</x:v>
+        <x:v>14781122</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
@@ -5178,7 +5178,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>10156696</x:v>
+        <x:v>10626696</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2509,7 +2509,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>766293</x:v>
+        <x:v>825832</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
         <x:v>14</x:v>
@@ -3417,7 +3417,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>766293</x:v>
+        <x:v>825832</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>14</x:v>
@@ -4222,7 +4222,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>768649</x:v>
+        <x:v>828188</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
         <x:v>14</x:v>
@@ -4680,7 +4680,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>769587</x:v>
+        <x:v>829126</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>14</x:v>
@@ -4921,7 +4921,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>769587</x:v>
+        <x:v>829126</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -5332,7 +5332,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>766293</x:v>
+        <x:v>825832</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2210,7 +2210,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>818769</x:v>
+        <x:v>1642139</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>12</x:v>
@@ -2302,7 +2302,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>384198</x:v>
+        <x:v>825294</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>14</x:v>
@@ -2805,7 +2805,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="1">
-        <x:v>384198</x:v>
+        <x:v>825294</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>14</x:v>
@@ -2822,7 +2822,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>818769</x:v>
+        <x:v>1642139</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>12</x:v>
@@ -3802,7 +3802,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>384198</x:v>
+        <x:v>825294</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
         <x:v>14</x:v>
@@ -3816,7 +3816,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>818769</x:v>
+        <x:v>1642139</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>12</x:v>
@@ -4493,7 +4493,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>3318769</x:v>
+        <x:v>4142139</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
         <x:v>12</x:v>
@@ -4504,7 +4504,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>1131927</x:v>
+        <x:v>1573023</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>14</x:v>
@@ -4833,7 +4833,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>4450696</x:v>
+        <x:v>5715162</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -5068,7 +5068,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>1174807</x:v>
+        <x:v>2439273</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -458,8 +458,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G81" totalsRowShown="0">
-  <x:autoFilter ref="A1:G81"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G82" totalsRowShown="0">
+  <x:autoFilter ref="A1:G82"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -474,8 +474,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E58" totalsRowShown="0">
-  <x:autoFilter ref="A1:E58"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E59" totalsRowShown="0">
+  <x:autoFilter ref="A1:E59"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -488,8 +488,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D51" totalsRowShown="0">
-  <x:autoFilter ref="A1:D51"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D52" totalsRowShown="0">
+  <x:autoFilter ref="A1:D52"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -823,7 +823,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G81"/>
+  <x:dimension ref="A1:G82"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2218,45 +2218,45 @@
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>663879</x:v>
+        <x:v>108000</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>3232621</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>12</x:v>
@@ -2264,25 +2264,25 @@
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>685625</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
@@ -2293,16 +2293,16 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>825294</x:v>
+        <x:v>685625</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>14</x:v>
@@ -2310,22 +2310,22 @@
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>4379246</x:v>
+        <x:v>825294</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>14</x:v>
@@ -2333,22 +2333,22 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>3985700</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>14</x:v>
@@ -2356,36 +2356,36 @@
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>1183678</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
         <x:v>91</x:v>
@@ -2394,10 +2394,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>4383749</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
@@ -2408,7 +2408,7 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
         <x:v>91</x:v>
@@ -2417,21 +2417,21 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>1426379</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
         <x:v>91</x:v>
@@ -2440,30 +2440,30 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>104555</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>3515616</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>14</x:v>
@@ -2471,22 +2471,22 @@
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>4495214</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>14</x:v>
@@ -2494,22 +2494,22 @@
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>825832</x:v>
+        <x:v>4495214</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
         <x:v>14</x:v>
@@ -2517,25 +2517,25 @@
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>2457788</x:v>
+        <x:v>825832</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
@@ -2546,16 +2546,16 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>2326917</x:v>
+        <x:v>2457788</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
         <x:v>12</x:v>
@@ -2563,45 +2563,45 @@
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>195838</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>50000</x:v>
+        <x:v>195838</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>14</x:v>
@@ -2609,13 +2609,13 @@
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
         <x:v>16</x:v>
@@ -2624,21 +2624,21 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>20139905</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
         <x:v>16</x:v>
@@ -2647,18 +2647,18 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>10000</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
         <x:v>64</x:v>
@@ -2670,7 +2670,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>31115</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
         <x:v>14</x:v>
@@ -2678,10 +2678,10 @@
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
         <x:v>64</x:v>
@@ -2693,9 +2693,32 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="F81" s="1">
+        <x:v>31115</x:v>
+      </x:c>
+      <x:c r="G81" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:7">
+      <x:c r="A82" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B82" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C82" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D82" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E82" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F82" s="1">
         <x:v>10498737</x:v>
       </x:c>
-      <x:c r="G81" s="1" t="s">
+      <x:c r="G82" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -2715,7 +2738,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E58"/>
+  <x:dimension ref="A1:E59"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2830,24 +2853,24 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>500000</x:v>
+        <x:v>108000</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>28</x:v>
@@ -2856,24 +2879,24 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>153098</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>-28160</x:v>
+        <x:v>153098</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>14</x:v>
@@ -2881,24 +2904,24 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>2000000</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>32</x:v>
@@ -2907,24 +2930,24 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>333</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>715</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
@@ -2932,16 +2955,16 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>8758871</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
@@ -2949,24 +2972,24 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>-9678</x:v>
+        <x:v>8758871</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>72</x:v>
@@ -2975,7 +2998,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>59748</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>12</x:v>
@@ -2983,7 +3006,7 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>72</x:v>
@@ -2992,32 +3015,32 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>4968501</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>1327758</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>34</x:v>
@@ -3026,32 +3049,32 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>7971780</x:v>
+        <x:v>1327758</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>2367356</x:v>
+        <x:v>7971780</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>91</x:v>
@@ -3060,7 +3083,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>2852758</x:v>
+        <x:v>2367356</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>12</x:v>
@@ -3068,7 +3091,7 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>91</x:v>
@@ -3077,15 +3100,15 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>209110</x:v>
+        <x:v>2852758</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>91</x:v>
@@ -3094,7 +3117,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>149773</x:v>
+        <x:v>209110</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
@@ -3102,7 +3125,7 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>91</x:v>
@@ -3111,7 +3134,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>9267843</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>14</x:v>
@@ -3119,33 +3142,33 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>-6917</x:v>
+        <x:v>9267843</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>7170572</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>12</x:v>
@@ -3153,7 +3176,7 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
         <x:v>10</x:v>
@@ -3162,24 +3185,24 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>7610550</x:v>
+        <x:v>7170572</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>5734396</x:v>
+        <x:v>7610550</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
@@ -3187,24 +3210,24 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>20139905</x:v>
+        <x:v>5734396</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>16</x:v>
@@ -3213,15 +3236,15 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>50000</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>16</x:v>
@@ -3230,7 +3253,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>10542390</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>14</x:v>
@@ -3238,16 +3261,16 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>382</x:v>
+        <x:v>10542390</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>14</x:v>
@@ -3255,16 +3278,16 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>14</x:v>
@@ -3272,24 +3295,24 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>2435145</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>61</x:v>
@@ -3298,24 +3321,24 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>685625</x:v>
+        <x:v>2435145</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>2651</x:v>
+        <x:v>685625</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>14</x:v>
@@ -3323,16 +3346,16 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>14</x:v>
@@ -3340,24 +3363,24 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
         <x:v>37</x:v>
@@ -3366,24 +3389,24 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>938</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>14</x:v>
@@ -3394,13 +3417,13 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="D40" s="1">
-        <x:v>1974</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>14</x:v>
@@ -3408,7 +3431,7 @@
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
         <x:v>61</x:v>
@@ -3417,7 +3440,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>825832</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>14</x:v>
@@ -3425,7 +3448,7 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
         <x:v>61</x:v>
@@ -3434,7 +3457,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="D42" s="1">
-        <x:v>382</x:v>
+        <x:v>825832</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>14</x:v>
@@ -3442,24 +3465,24 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D43" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>72</x:v>
@@ -3468,32 +3491,32 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="D44" s="1">
-        <x:v>253656</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="D45" s="1">
-        <x:v>2326917</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
         <x:v>44</x:v>
@@ -3502,24 +3525,24 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="D46" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D47" s="1">
-        <x:v>10000</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>14</x:v>
@@ -3527,47 +3550,47 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D48" s="1">
-        <x:v>-31053</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D49" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>382</x:v>
@@ -3578,10 +3601,10 @@
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
         <x:v>26</x:v>
@@ -3595,58 +3618,58 @@
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D52" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D53" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D54" s="1">
-        <x:v>14264</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
         <x:v>54</x:v>
@@ -3655,24 +3678,24 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D55" s="1">
-        <x:v>164138</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D56" s="1">
-        <x:v>-62727</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
         <x:v>14</x:v>
@@ -3680,16 +3703,16 @@
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D57" s="1">
-        <x:v>195838</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
         <x:v>14</x:v>
@@ -3697,18 +3720,35 @@
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B58" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C58" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D58" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+      <x:c r="E58" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:5">
+      <x:c r="A59" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B58" s="1" t="s">
+      <x:c r="B59" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C58" s="1" t="s">
+      <x:c r="C59" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D58" s="1">
+      <x:c r="D59" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="E58" s="1" t="s">
+      <x:c r="E59" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -3728,7 +3768,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D51"/>
+  <x:dimension ref="A1:D52"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3824,16 +3864,16 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>500000</x:v>
+        <x:v>108000</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
@@ -3844,21 +3884,21 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>153098</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>-28160</x:v>
+        <x:v>153098</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>14</x:v>
@@ -3866,16 +3906,16 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>2000000</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
@@ -3886,21 +3926,21 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>333</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>715</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
         <x:v>14</x:v>
@@ -3908,13 +3948,13 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>8758871</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>14</x:v>
@@ -3922,16 +3962,16 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>50070</x:v>
+        <x:v>8758871</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
@@ -3942,24 +3982,24 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>4968501</x:v>
+        <x:v>50070</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>1327758</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
@@ -3970,24 +4010,24 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>7971780</x:v>
+        <x:v>1327758</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>5220114</x:v>
+        <x:v>7971780</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
@@ -3998,35 +4038,35 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>9626726</x:v>
+        <x:v>5220114</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>-6917</x:v>
+        <x:v>9626726</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>7170572</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>12</x:v>
@@ -4040,21 +4080,21 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>7610550</x:v>
+        <x:v>7170572</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>5734396</x:v>
+        <x:v>7610550</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
         <x:v>14</x:v>
@@ -4062,16 +4102,16 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>20139905</x:v>
+        <x:v>5734396</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
@@ -4082,21 +4122,21 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>10592390</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>382</x:v>
+        <x:v>10592390</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>14</x:v>
@@ -4104,13 +4144,13 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>14</x:v>
@@ -4118,16 +4158,16 @@
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>2435145</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
@@ -4138,21 +4178,21 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>685625</x:v>
+        <x:v>2435145</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>2651</x:v>
+        <x:v>685625</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
         <x:v>14</x:v>
@@ -4160,13 +4200,13 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>14</x:v>
@@ -4174,16 +4214,16 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
@@ -4194,21 +4234,21 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>938</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
         <x:v>14</x:v>
@@ -4216,13 +4256,13 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>828188</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
         <x:v>14</x:v>
@@ -4230,16 +4270,16 @@
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>2326917</x:v>
+        <x:v>828188</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
@@ -4250,24 +4290,24 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>253656</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>2326917</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
@@ -4278,21 +4318,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>10000</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
         <x:v>14</x:v>
@@ -4300,38 +4340,38 @@
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>-31053</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>382</x:v>
@@ -4342,7 +4382,7 @@
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>26</x:v>
@@ -4356,44 +4396,44 @@
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C45" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C46" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C47" s="1">
-        <x:v>14264</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
@@ -4404,21 +4444,21 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C48" s="1">
-        <x:v>164138</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C49" s="1">
-        <x:v>-62727</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
         <x:v>14</x:v>
@@ -4426,13 +4466,13 @@
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C50" s="1">
-        <x:v>195838</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
         <x:v>14</x:v>
@@ -4440,15 +4480,29 @@
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B51" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C51" s="1">
+        <x:v>195838</x:v>
+      </x:c>
+      <x:c r="D51" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:4">
+      <x:c r="A52" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B51" s="1" t="s">
+      <x:c r="B52" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C51" s="1">
+      <x:c r="C52" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="D51" s="1" t="s">
+      <x:c r="D52" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -4504,7 +4558,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>1573023</x:v>
+        <x:v>1681023</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>14</x:v>
@@ -4833,7 +4887,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>5715162</x:v>
+        <x:v>5823162</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -5057,7 +5111,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>60000</x:v>
+        <x:v>168000</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -279,6 +279,9 @@
     <x:t>MO</x:t>
   </x:si>
   <x:si>
+    <x:t>EL-SAYED, ABDUL</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00815753</x:t>
   </x:si>
   <x:si>
@@ -327,12 +330,21 @@
     <x:t>FOUSHEE, VALERIE</x:t>
   </x:si>
   <x:si>
+    <x:t>SHAHEEN, STEFANY</x:t>
+  </x:si>
+  <x:si>
     <x:t>BENNETT, REBECCA</x:t>
   </x:si>
   <x:si>
     <x:t>THOMPSON, MIKE MR.</x:t>
   </x:si>
   <x:si>
+    <x:t>MCADAMS, BEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00935049</x:t>
   </x:si>
   <x:si>
@@ -375,19 +387,13 @@
     <x:t>14</x:t>
   </x:si>
   <x:si>
-    <x:t>SHAHEEN, STEFANY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCADAMS, BEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
+    <x:t>PELTOLA, MARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
   </x:si>
   <x:si>
     <x:t>MCMORROW, MALLORY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EL-SAYED, ABDUL</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -458,8 +464,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G82" totalsRowShown="0">
-  <x:autoFilter ref="A1:G82"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G85" totalsRowShown="0">
+  <x:autoFilter ref="A1:G85"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -474,8 +480,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E59" totalsRowShown="0">
-  <x:autoFilter ref="A1:E59"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E60" totalsRowShown="0">
+  <x:autoFilter ref="A1:E60"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -488,8 +494,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D52" totalsRowShown="0">
-  <x:autoFilter ref="A1:D52"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D53" totalsRowShown="0">
+  <x:autoFilter ref="A1:D53"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -501,8 +507,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C29" totalsRowShown="0">
-  <x:autoFilter ref="A1:C29"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C30" totalsRowShown="0">
+  <x:autoFilter ref="A1:C30"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -513,8 +519,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B20" totalsRowShown="0">
-  <x:autoFilter ref="A1:B20"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B21" totalsRowShown="0">
+  <x:autoFilter ref="A1:B21"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -524,8 +530,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C44" totalsRowShown="0">
-  <x:autoFilter ref="A1:C44"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C45" totalsRowShown="0">
+  <x:autoFilter ref="A1:C45"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -823,7 +829,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G82"/>
+  <x:dimension ref="A1:G85"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1681,7 +1687,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>1238800</x:v>
+        <x:v>5734013</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>14</x:v>
@@ -1758,45 +1764,45 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="B41" s="1" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C41" s="1" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>39386</x:v>
+        <x:v>2346358</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>149773</x:v>
+        <x:v>8437450</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>14</x:v>
@@ -1804,22 +1810,22 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>60000</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>14</x:v>
@@ -1827,22 +1833,22 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>63298</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>14</x:v>
@@ -1850,22 +1856,22 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="B45" s="1" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C45" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>152765</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>14</x:v>
@@ -1873,22 +1879,22 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="D46" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>500346</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>14</x:v>
@@ -1896,22 +1902,22 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>198972</x:v>
+        <x:v>152765</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>14</x:v>
@@ -1919,45 +1925,45 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>198972</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="B49" s="1" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C49" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>600000</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>14</x:v>
@@ -1965,45 +1971,45 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>253656</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>350000</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>14</x:v>
@@ -2011,22 +2017,22 @@
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>499160</x:v>
+        <x:v>80291</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>14</x:v>
@@ -2034,22 +2040,22 @@
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B53" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C53" s="1" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="B53" s="1" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C53" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>4379243</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>14</x:v>
@@ -2057,68 +2063,68 @@
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>663879</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>1183678</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B56" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C56" s="1" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="B56" s="1" t="s">
+      <x:c r="D56" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E56" s="1" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C56" s="1" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D56" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E56" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="F56" s="1">
-        <x:v>104555</x:v>
+        <x:v>214831</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>14</x:v>
@@ -2126,22 +2132,22 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>3985698</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>14</x:v>
@@ -2149,45 +2155,45 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B58" s="1" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B58" s="1" t="s">
+      <x:c r="C58" s="1" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="C58" s="1" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>4383748</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B59" s="1" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B59" s="1" t="s">
-        <x:v>112</x:v>
-      </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>1426379</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>12</x:v>
@@ -2195,45 +2201,45 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>1642139</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>108000</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>14</x:v>
@@ -2241,45 +2247,45 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>663879</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>3232621</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
         <x:v>12</x:v>
@@ -2293,39 +2299,39 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>685625</x:v>
+        <x:v>1642139</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>825294</x:v>
+        <x:v>108000</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>14</x:v>
@@ -2333,91 +2339,91 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>4379246</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>3985700</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>1183678</x:v>
+        <x:v>685625</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>4383749</x:v>
+        <x:v>825294</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
         <x:v>14</x:v>
@@ -2425,45 +2431,45 @@
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>1426379</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>104555</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>14</x:v>
@@ -2471,45 +2477,45 @@
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>3515616</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>4495214</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
         <x:v>14</x:v>
@@ -2517,91 +2523,91 @@
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>825832</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>2457788</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>2326917</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>195838</x:v>
+        <x:v>803627</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>14</x:v>
@@ -2609,25 +2615,25 @@
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>50000</x:v>
+        <x:v>2457788</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
@@ -2638,16 +2644,16 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>20139905</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
         <x:v>12</x:v>
@@ -2655,22 +2661,22 @@
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>10000</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
         <x:v>14</x:v>
@@ -2678,13 +2684,13 @@
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
         <x:v>16</x:v>
@@ -2693,7 +2699,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>31115</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
         <x:v>14</x:v>
@@ -2707,7 +2713,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
         <x:v>16</x:v>
@@ -2716,9 +2722,78 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>10498737</x:v>
+        <x:v>17793547</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:7">
+      <x:c r="A83" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B83" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C83" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D83" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E83" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F83" s="1">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="G83" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:7">
+      <x:c r="A84" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B84" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C84" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D84" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E84" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F84" s="1">
+        <x:v>31115</x:v>
+      </x:c>
+      <x:c r="G84" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:7">
+      <x:c r="A85" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B85" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C85" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D85" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E85" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F85" s="1">
+        <x:v>2061287</x:v>
+      </x:c>
+      <x:c r="G85" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -2738,7 +2813,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E59"/>
+  <x:dimension ref="A1:E60"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2768,16 +2843,16 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D2" s="1">
-        <x:v>499160</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
         <x:v>14</x:v>
@@ -2785,16 +2860,16 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D3" s="1">
-        <x:v>63298</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
         <x:v>14</x:v>
@@ -2802,16 +2877,16 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D4" s="1">
-        <x:v>60000</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
         <x:v>14</x:v>
@@ -2819,16 +2894,16 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="1">
-        <x:v>825294</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>14</x:v>
@@ -2836,58 +2911,58 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>1642139</x:v>
+        <x:v>825294</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>108000</x:v>
+        <x:v>1642139</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>500000</x:v>
+        <x:v>108000</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>28</x:v>
@@ -2896,24 +2971,24 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D9" s="1">
-        <x:v>153098</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D10" s="1">
-        <x:v>-28160</x:v>
+        <x:v>153098</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
@@ -2921,24 +2996,24 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D11" s="1">
-        <x:v>2000000</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>32</x:v>
@@ -2947,24 +3022,24 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D12" s="1">
-        <x:v>333</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D13" s="1">
-        <x:v>715</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
@@ -2972,16 +3047,16 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D14" s="1">
-        <x:v>8758871</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
@@ -2989,24 +3064,24 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>-9678</x:v>
+        <x:v>8758871</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>72</x:v>
@@ -3015,7 +3090,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>59748</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>12</x:v>
@@ -3023,7 +3098,7 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>72</x:v>
@@ -3032,32 +3107,32 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>4968501</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>1327758</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>34</x:v>
@@ -3066,41 +3141,41 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>7971780</x:v>
+        <x:v>1327758</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>2367356</x:v>
+        <x:v>7971780</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>2852758</x:v>
+        <x:v>2367356</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>12</x:v>
@@ -3108,33 +3183,33 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>209110</x:v>
+        <x:v>2852758</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>149773</x:v>
+        <x:v>209110</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>14</x:v>
@@ -3142,16 +3217,16 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>9267843</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>14</x:v>
@@ -3159,33 +3234,33 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>-6917</x:v>
+        <x:v>9267843</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>7170572</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>12</x:v>
@@ -3193,7 +3268,7 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>10</x:v>
@@ -3202,24 +3277,24 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>7610550</x:v>
+        <x:v>7170572</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>5734396</x:v>
+        <x:v>7610550</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
@@ -3227,24 +3302,24 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>20139905</x:v>
+        <x:v>5734395</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>16</x:v>
@@ -3253,15 +3328,15 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>50000</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>16</x:v>
@@ -3270,7 +3345,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>10542390</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>14</x:v>
@@ -3278,16 +3353,16 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>382</x:v>
+        <x:v>10542390</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>14</x:v>
@@ -3295,16 +3370,16 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>14</x:v>
@@ -3312,24 +3387,24 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>2435145</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>61</x:v>
@@ -3338,24 +3413,24 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>685625</x:v>
+        <x:v>2435145</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>2651</x:v>
+        <x:v>685625</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>14</x:v>
@@ -3363,16 +3438,16 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>14</x:v>
@@ -3380,24 +3455,24 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
         <x:v>37</x:v>
@@ -3406,24 +3481,24 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D40" s="1">
-        <x:v>938</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>14</x:v>
@@ -3434,13 +3509,13 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>1974</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>14</x:v>
@@ -3448,7 +3523,7 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
         <x:v>61</x:v>
@@ -3457,7 +3532,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="D42" s="1">
-        <x:v>825832</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>14</x:v>
@@ -3465,7 +3540,7 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
         <x:v>61</x:v>
@@ -3474,7 +3549,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="D43" s="1">
-        <x:v>382</x:v>
+        <x:v>883918</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>14</x:v>
@@ -3482,24 +3557,24 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D44" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
         <x:v>72</x:v>
@@ -3508,32 +3583,32 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="D45" s="1">
-        <x:v>253656</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="D46" s="1">
-        <x:v>2326917</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
         <x:v>44</x:v>
@@ -3542,24 +3617,24 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="D47" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D48" s="1">
-        <x:v>10000</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>14</x:v>
@@ -3567,47 +3642,47 @@
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D49" s="1">
-        <x:v>-31053</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D50" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>382</x:v>
@@ -3618,10 +3693,10 @@
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
         <x:v>26</x:v>
@@ -3635,58 +3710,58 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D53" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D54" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="D55" s="1">
-        <x:v>14264</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
         <x:v>54</x:v>
@@ -3695,24 +3770,24 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D56" s="1">
-        <x:v>164138</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D57" s="1">
-        <x:v>-62727</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
         <x:v>14</x:v>
@@ -3720,16 +3795,16 @@
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D58" s="1">
-        <x:v>195838</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
         <x:v>14</x:v>
@@ -3737,18 +3812,35 @@
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B59" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C59" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D59" s="1">
+        <x:v>214831</x:v>
+      </x:c>
+      <x:c r="E59" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:5">
+      <x:c r="A60" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B59" s="1" t="s">
+      <x:c r="B60" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C59" s="1" t="s">
+      <x:c r="C60" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D59" s="1">
+      <x:c r="D60" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="E59" s="1" t="s">
+      <x:c r="E60" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -3768,7 +3860,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D52"/>
+  <x:dimension ref="A1:D53"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3794,13 +3886,13 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>499160</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
         <x:v>14</x:v>
@@ -3808,13 +3900,13 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>63298</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
         <x:v>14</x:v>
@@ -3822,13 +3914,13 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>60000</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
         <x:v>14</x:v>
@@ -3836,13 +3928,13 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>825294</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
         <x:v>14</x:v>
@@ -3850,44 +3942,44 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>1642139</x:v>
+        <x:v>825294</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>108000</x:v>
+        <x:v>1642139</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>500000</x:v>
+        <x:v>108000</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
@@ -3898,21 +3990,21 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>153098</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>-28160</x:v>
+        <x:v>153098</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
         <x:v>14</x:v>
@@ -3920,16 +4012,16 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>2000000</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
@@ -3940,21 +4032,21 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>333</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>715</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>14</x:v>
@@ -3962,13 +4054,13 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>8758871</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>14</x:v>
@@ -3976,16 +4068,16 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>50070</x:v>
+        <x:v>8758871</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
@@ -3996,24 +4088,24 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>4968501</x:v>
+        <x:v>50070</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>1327758</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
@@ -4024,63 +4116,63 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>7971780</x:v>
+        <x:v>1327758</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>5220114</x:v>
+        <x:v>7971780</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>9626726</x:v>
+        <x:v>5220114</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>-6917</x:v>
+        <x:v>9626726</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>7170572</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
         <x:v>12</x:v>
@@ -4094,21 +4186,21 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>7610550</x:v>
+        <x:v>7170572</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>5734396</x:v>
+        <x:v>7610550</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
         <x:v>14</x:v>
@@ -4116,16 +4208,16 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>20139905</x:v>
+        <x:v>5734395</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
@@ -4136,21 +4228,21 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>10592390</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>382</x:v>
+        <x:v>10592390</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>14</x:v>
@@ -4158,13 +4250,13 @@
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
         <x:v>14</x:v>
@@ -4172,16 +4264,16 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>2435145</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
@@ -4192,21 +4284,21 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>685625</x:v>
+        <x:v>2435145</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>2651</x:v>
+        <x:v>685625</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>14</x:v>
@@ -4214,13 +4306,13 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
         <x:v>14</x:v>
@@ -4228,16 +4320,16 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
@@ -4248,21 +4340,21 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>938</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
         <x:v>14</x:v>
@@ -4270,13 +4362,13 @@
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>828188</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
         <x:v>14</x:v>
@@ -4284,16 +4376,16 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>2326917</x:v>
+        <x:v>886274</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:4">
@@ -4304,24 +4396,24 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>253656</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>2326917</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
@@ -4332,21 +4424,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>10000</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
         <x:v>14</x:v>
@@ -4354,38 +4446,38 @@
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>-31053</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="C43" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>382</x:v>
@@ -4396,7 +4488,7 @@
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
         <x:v>26</x:v>
@@ -4410,44 +4502,44 @@
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C46" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C47" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C48" s="1">
-        <x:v>14264</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:4">
@@ -4458,21 +4550,21 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C49" s="1">
-        <x:v>164138</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C50" s="1">
-        <x:v>-62727</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
         <x:v>14</x:v>
@@ -4480,13 +4572,13 @@
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C51" s="1">
-        <x:v>195838</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
         <x:v>14</x:v>
@@ -4494,15 +4586,29 @@
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B52" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C52" s="1">
+        <x:v>214831</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:4">
+      <x:c r="A53" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B52" s="1" t="s">
+      <x:c r="B53" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C52" s="1">
+      <x:c r="C53" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="D52" s="1" t="s">
+      <x:c r="D53" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -4522,7 +4628,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C29"/>
+  <x:dimension ref="A1:C30"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4544,13 +4650,13 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>4142139</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -4558,18 +4664,18 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>1681023</x:v>
+        <x:v>4142139</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>715</x:v>
+        <x:v>1681023</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>14</x:v>
@@ -4577,13 +4683,13 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>6597942</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -4591,29 +4697,29 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>31325878</x:v>
+        <x:v>6597942</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>-6917</x:v>
+        <x:v>31325878</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>7170572</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>12</x:v>
@@ -4624,18 +4730,18 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>7610550</x:v>
+        <x:v>7170572</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>5734396</x:v>
+        <x:v>7610550</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>14</x:v>
@@ -4643,13 +4749,13 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>20139905</x:v>
+        <x:v>5734395</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -4657,18 +4763,18 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>10592772</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>2649</x:v>
+        <x:v>10592772</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>14</x:v>
@@ -4676,13 +4782,13 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>2435145</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -4690,18 +4796,18 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>685625</x:v>
+        <x:v>2435145</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>602651</x:v>
+        <x:v>685625</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>14</x:v>
@@ -4709,13 +4815,13 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>200842</x:v>
+        <x:v>602651</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -4723,18 +4829,18 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>829126</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>14</x:v>
@@ -4742,13 +4848,13 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>4653834</x:v>
+        <x:v>887212</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -4756,21 +4862,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B21" s="1">
-        <x:v>662097</x:v>
+        <x:v>4653834</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B22" s="1">
-        <x:v>-31053</x:v>
+        <x:v>662097</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -4778,18 +4884,18 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="1">
-        <x:v>10382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B24" s="1">
-        <x:v>764</x:v>
+        <x:v>10382</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>14</x:v>
@@ -4797,13 +4903,13 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B25" s="1">
-        <x:v>14218</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -4811,18 +4917,18 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B26" s="1">
-        <x:v>203524</x:v>
+        <x:v>14218</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B27" s="1">
-        <x:v>-62727</x:v>
+        <x:v>203524</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>14</x:v>
@@ -4830,10 +4936,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B28" s="1">
-        <x:v>195838</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>14</x:v>
@@ -4841,12 +4947,23 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B29" s="1">
+        <x:v>214831</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:3">
+      <x:c r="A30" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B29" s="1">
+      <x:c r="B30" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="C29" s="1" t="s">
+      <x:c r="C30" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -4866,7 +4983,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B20"/>
+  <x:dimension ref="A1:B21"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4884,153 +5001,161 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B2" s="1">
-        <x:v>5823162</x:v>
+        <x:v>253750</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>715</x:v>
+        <x:v>5823162</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>37923820</x:v>
+        <x:v>715</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>-6917</x:v>
+        <x:v>37923820</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>14781122</x:v>
+        <x:v>-6917</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>5734396</x:v>
+        <x:v>14781122</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>30732677</x:v>
+        <x:v>5734395</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>2649</x:v>
+        <x:v>30732677</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>3120770</x:v>
+        <x:v>2649</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>602651</x:v>
+        <x:v>3120770</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>399814</x:v>
+        <x:v>602651</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>829126</x:v>
+        <x:v>399814</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>5315931</x:v>
+        <x:v>887212</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>-20671</x:v>
+        <x:v>5315931</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>764</x:v>
+        <x:v>-20671</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>217742</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>-62727</x:v>
+        <x:v>217742</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>195838</x:v>
+        <x:v>-62727</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B20" s="1">
+        <x:v>214831</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:2">
+      <x:c r="A21" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B20" s="1">
+      <x:c r="B21" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>
@@ -5050,7 +5175,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C44"/>
+  <x:dimension ref="A1:C45"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -5072,145 +5197,145 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>499160</x:v>
+        <x:v>253750</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>2500666</x:v>
+        <x:v>499160</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>216063</x:v>
+        <x:v>2500666</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>168000</x:v>
+        <x:v>216063</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>2439273</x:v>
+        <x:v>168000</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>715</x:v>
+        <x:v>2439273</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>8758489</x:v>
+        <x:v>715</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>3904224</x:v>
+        <x:v>8758489</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>764</x:v>
+        <x:v>3904224</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>500346</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>19591653</x:v>
+        <x:v>500346</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>149773</x:v>
+        <x:v>19591653</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>5018571</x:v>
+        <x:v>149773</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -5218,142 +5343,142 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>-6917</x:v>
+        <x:v>5018571</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>10626696</x:v>
+        <x:v>-6917</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>4154426</x:v>
+        <x:v>10626696</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>382</x:v>
+        <x:v>4154426</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>5734014</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>34035</x:v>
+        <x:v>5734013</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>50000</x:v>
+        <x:v>34035</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>10000</x:v>
+        <x:v>50000</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>30638642</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>2649</x:v>
+        <x:v>30638642</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>3120770</x:v>
+        <x:v>2649</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>600000</x:v>
+        <x:v>3120770</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>2651</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
@@ -5361,120 +5486,120 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>1870</x:v>
+        <x:v>2651</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>397944</x:v>
+        <x:v>1870</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>825832</x:v>
+        <x:v>397944</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>3294</x:v>
+        <x:v>883918</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>603656</x:v>
+        <x:v>3294</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>58441</x:v>
+        <x:v>603656</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>4653834</x:v>
+        <x:v>58441</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>382</x:v>
+        <x:v>4653834</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>10000</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>-31053</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>764</x:v>
+        <x:v>-31053</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
@@ -5482,64 +5607,75 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>178402</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>39386</x:v>
+        <x:v>178402</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>-46</x:v>
+        <x:v>39386</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>-62727</x:v>
+        <x:v>-46</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C43" s="1">
-        <x:v>195838</x:v>
+        <x:v>-62727</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C44" s="1">
+        <x:v>214831</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:3">
+      <x:c r="A45" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B44" s="1" t="s">
+      <x:c r="B45" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C44" s="1">
+      <x:c r="C45" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2607,7 +2607,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>803627</x:v>
+        <x:v>859295</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>14</x:v>
@@ -3549,7 +3549,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="D43" s="1">
-        <x:v>883918</x:v>
+        <x:v>939586</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>14</x:v>
@@ -4382,7 +4382,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>886274</x:v>
+        <x:v>941942</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
         <x:v>14</x:v>
@@ -4851,7 +4851,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>887212</x:v>
+        <x:v>942880</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>14</x:v>
@@ -5100,7 +5100,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>887212</x:v>
+        <x:v>942880</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
@@ -5522,7 +5522,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>883918</x:v>
+        <x:v>939586</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -2607,7 +2607,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>859295</x:v>
+        <x:v>922241</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>14</x:v>
@@ -3549,7 +3549,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="D43" s="1">
-        <x:v>939586</x:v>
+        <x:v>1002532</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>14</x:v>
@@ -4382,7 +4382,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>941942</x:v>
+        <x:v>1004888</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
         <x:v>14</x:v>
@@ -4851,7 +4851,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>942880</x:v>
+        <x:v>1005826</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>14</x:v>
@@ -5100,7 +5100,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>942880</x:v>
+        <x:v>1005826</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
@@ -5522,7 +5522,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>939586</x:v>
+        <x:v>1002532</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -90,6 +90,12 @@
     <x:t>NY</x:t>
   </x:si>
   <x:si>
+    <x:t>STEVENS, HALEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00710848</x:t>
   </x:si>
   <x:si>
@@ -156,9 +162,6 @@
     <x:t>11</x:t>
   </x:si>
   <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
     <x:t>CAVANAUGH, JOHN</x:t>
   </x:si>
   <x:si>
@@ -211,9 +214,6 @@
   </x:si>
   <x:si>
     <x:t>PAPPAS, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEVENS, HALEY</x:t>
   </x:si>
   <x:si>
     <x:t>CRAIG, ANGIE</x:t>
@@ -951,7 +951,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>10000</x:v>
+        <x:v>11995</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>14</x:v>
@@ -959,22 +959,22 @@
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="F6" s="1">
-        <x:v>382</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
         <x:v>14</x:v>
@@ -982,65 +982,65 @@
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="F7" s="1">
-        <x:v>500000</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>333</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>333</x:v>
@@ -1051,10 +1051,10 @@
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>33</x:v>
@@ -1063,10 +1063,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>715</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>14</x:v>
@@ -1074,22 +1074,22 @@
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
+      <x:c r="E11" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="F11" s="1">
-        <x:v>382</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
         <x:v>14</x:v>
@@ -1097,19 +1097,19 @@
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F12" s="1">
         <x:v>382</x:v>
@@ -1120,19 +1120,19 @@
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="F13" s="1">
         <x:v>382</x:v>
@@ -1143,19 +1143,19 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="E14" s="1" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>45</x:v>
       </x:c>
       <x:c r="F14" s="1">
         <x:v>382</x:v>
@@ -1166,68 +1166,68 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="F15" s="1">
-        <x:v>1870</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="F16" s="1">
-        <x:v>58441</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="F17" s="1">
-        <x:v>382</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>14</x:v>
@@ -1235,19 +1235,19 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F18" s="1">
         <x:v>382</x:v>
@@ -1258,22 +1258,22 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>164138</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>14</x:v>
@@ -1281,114 +1281,114 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="F20" s="1">
-        <x:v>14264</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>382</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="F22" s="1">
-        <x:v>2000000</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>382</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D24" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="F24" s="1">
-        <x:v>1974</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>14</x:v>
@@ -1396,22 +1396,22 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>2538</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>14</x:v>
@@ -1419,22 +1419,22 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="B26" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C26" s="1" t="s">
-        <x:v>65</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>2649</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>14</x:v>
@@ -1442,22 +1442,22 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>2651</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>14</x:v>
@@ -1465,22 +1465,22 @@
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>938</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>14</x:v>
@@ -1488,25 +1488,25 @@
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>-9678</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
@@ -1517,16 +1517,16 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>-31053</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>12</x:v>
@@ -1540,16 +1540,16 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>3575107</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>12</x:v>
@@ -1563,19 +1563,19 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>4968501</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
@@ -1586,19 +1586,19 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>-6917</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
@@ -1609,16 +1609,16 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>-46</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1632,16 +1632,16 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>59748</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>12</x:v>
@@ -1655,19 +1655,19 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>579319</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
@@ -1678,16 +1678,16 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>5734013</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>14</x:v>
@@ -1701,19 +1701,19 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="E38" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="F38" s="1">
-        <x:v>2326917</x:v>
+        <x:v>5734013</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
@@ -1724,19 +1724,19 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>-28160</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
@@ -1747,19 +1747,19 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>-22643</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
@@ -1770,16 +1770,16 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>2346358</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1793,39 +1793,39 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>8437450</x:v>
+        <x:v>2346358</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>39386</x:v>
+        <x:v>8437450</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>14</x:v>
@@ -1839,16 +1839,16 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>149773</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>14</x:v>
@@ -1862,16 +1862,16 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>60000</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>14</x:v>
@@ -1879,22 +1879,22 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>63298</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>14</x:v>
@@ -1908,16 +1908,16 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>152765</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>14</x:v>
@@ -1931,16 +1931,16 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>500346</x:v>
+        <x:v>152765</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>14</x:v>
@@ -1954,16 +1954,16 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>198972</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>14</x:v>
@@ -1977,42 +1977,42 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F50" s="1">
         <x:v>198972</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>600000</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
@@ -2023,16 +2023,16 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>80291</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>14</x:v>
@@ -2046,16 +2046,16 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>253656</x:v>
+        <x:v>80291</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>14</x:v>
@@ -2069,16 +2069,16 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>350000</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>14</x:v>
@@ -2092,16 +2092,16 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>499160</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>14</x:v>
@@ -2115,16 +2115,16 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>214831</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>14</x:v>
@@ -2132,22 +2132,22 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>4379243</x:v>
+        <x:v>214831</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>14</x:v>
@@ -2155,25 +2155,25 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>663879</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
@@ -2184,16 +2184,16 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>1183678</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>12</x:v>
@@ -2207,39 +2207,39 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>104555</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>3985698</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>14</x:v>
@@ -2253,16 +2253,16 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>4383748</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>14</x:v>
@@ -2276,39 +2276,39 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>1426379</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>1642139</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>12</x:v>
@@ -2316,10 +2316,10 @@
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
         <x:v>117</x:v>
@@ -2328,56 +2328,56 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>108000</x:v>
+        <x:v>1642139</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>663879</x:v>
+        <x:v>108000</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>3232621</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
         <x:v>12</x:v>
@@ -2385,25 +2385,25 @@
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>685625</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
@@ -2414,16 +2414,16 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>825294</x:v>
+        <x:v>685625</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
         <x:v>14</x:v>
@@ -2431,22 +2431,22 @@
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>4379246</x:v>
+        <x:v>825294</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
         <x:v>14</x:v>
@@ -2454,22 +2454,22 @@
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D71" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D71" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>3985700</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>14</x:v>
@@ -2477,48 +2477,48 @@
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>1183678</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>4383749</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
@@ -2529,62 +2529,62 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>1426379</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>104555</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>3515616</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>14</x:v>
@@ -2592,22 +2592,22 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>922241</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>14</x:v>
@@ -2615,25 +2615,25 @@
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>2457788</x:v>
+        <x:v>922241</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
@@ -2644,16 +2644,16 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C79" 